--- a/sensitivity_results/legacy/Mobilenet_v3_Large_Correlation_matrices.xlsx
+++ b/sensitivity_results/legacy/Mobilenet_v3_Large_Correlation_matrices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\temp\ToGIT\Legacy\pearson_corelation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC033E55-E8DA-4F90-8266-0740C735A79A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C8D96D7-3A87-42D1-AFFD-52F717480BA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="70">
   <si>
     <t>features.0.0</t>
   </si>
@@ -244,6 +244,9 @@
   <si>
     <t/>
   </si>
+  <si>
+    <t>'</t>
+  </si>
 </sst>
 </file>
 
@@ -299,16 +302,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="5">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C5700"/>
@@ -634,7 +652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1116EB9B-6940-4A95-B0D5-6370D1EC4F27}">
-  <dimension ref="A1:BN55"/>
+  <dimension ref="A1:BN97"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
@@ -2664,6 +2682,9 @@
       <c r="B14" t="s">
         <v>14</v>
       </c>
+      <c r="D14" s="2" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="15" spans="1:66" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
@@ -2750,95 +2771,8673 @@
         <v>68</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:65" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:65" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:65" x14ac:dyDescent="0.35">
       <c r="B35" t="s">
         <v>68</v>
       </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <f>D35+1</f>
+        <v>1</v>
+      </c>
+      <c r="F35">
+        <f>E35+1</f>
+        <v>2</v>
+      </c>
+      <c r="G35">
+        <f>F35+1</f>
+        <v>3</v>
+      </c>
+      <c r="H35">
+        <f>G35+1</f>
+        <v>4</v>
+      </c>
+      <c r="I35">
+        <f>H35+1</f>
+        <v>5</v>
+      </c>
+      <c r="J35">
+        <f>I35+1</f>
+        <v>6</v>
+      </c>
+      <c r="K35">
+        <f>J35+1</f>
+        <v>7</v>
+      </c>
+      <c r="L35">
+        <f>K35+1</f>
+        <v>8</v>
+      </c>
+      <c r="M35">
+        <f>L35+1</f>
+        <v>9</v>
+      </c>
+      <c r="N35">
+        <f>M35+1</f>
+        <v>10</v>
+      </c>
+      <c r="O35">
+        <f>N35+1</f>
+        <v>11</v>
+      </c>
+      <c r="P35">
+        <f>O35+1</f>
+        <v>12</v>
+      </c>
+      <c r="Q35">
+        <f>P35+1</f>
+        <v>13</v>
+      </c>
+      <c r="R35">
+        <f>Q35+1</f>
+        <v>14</v>
+      </c>
+      <c r="S35">
+        <f>R35+1</f>
+        <v>15</v>
+      </c>
+      <c r="T35">
+        <f>S35+1</f>
+        <v>16</v>
+      </c>
+      <c r="U35">
+        <f>T35+1</f>
+        <v>17</v>
+      </c>
+      <c r="V35">
+        <f>U35+1</f>
+        <v>18</v>
+      </c>
+      <c r="W35">
+        <f>V35+1</f>
+        <v>19</v>
+      </c>
+      <c r="X35">
+        <f>W35+1</f>
+        <v>20</v>
+      </c>
+      <c r="Y35">
+        <f>X35+1</f>
+        <v>21</v>
+      </c>
+      <c r="Z35">
+        <f>Y35+1</f>
+        <v>22</v>
+      </c>
+      <c r="AA35">
+        <f>Z35+1</f>
+        <v>23</v>
+      </c>
+      <c r="AB35">
+        <f>AA35+1</f>
+        <v>24</v>
+      </c>
+      <c r="AC35">
+        <f>AB35+1</f>
+        <v>25</v>
+      </c>
+      <c r="AD35">
+        <f>AC35+1</f>
+        <v>26</v>
+      </c>
+      <c r="AE35">
+        <f>AD35+1</f>
+        <v>27</v>
+      </c>
+      <c r="AF35">
+        <f>AE35+1</f>
+        <v>28</v>
+      </c>
+      <c r="AG35">
+        <f>AF35+1</f>
+        <v>29</v>
+      </c>
+      <c r="AH35">
+        <f>AG35+1</f>
+        <v>30</v>
+      </c>
+      <c r="AI35">
+        <f>AH35+1</f>
+        <v>31</v>
+      </c>
+      <c r="AJ35">
+        <f>AI35+1</f>
+        <v>32</v>
+      </c>
+      <c r="AK35">
+        <f>AJ35+1</f>
+        <v>33</v>
+      </c>
+      <c r="AL35">
+        <f>AK35+1</f>
+        <v>34</v>
+      </c>
+      <c r="AM35">
+        <f>AL35+1</f>
+        <v>35</v>
+      </c>
+      <c r="AN35">
+        <f>AM35+1</f>
+        <v>36</v>
+      </c>
+      <c r="AO35">
+        <f>AN35+1</f>
+        <v>37</v>
+      </c>
+      <c r="AP35">
+        <f>AO35+1</f>
+        <v>38</v>
+      </c>
+      <c r="AQ35">
+        <f>AP35+1</f>
+        <v>39</v>
+      </c>
+      <c r="AR35">
+        <f>AQ35+1</f>
+        <v>40</v>
+      </c>
+      <c r="AS35">
+        <f>AR35+1</f>
+        <v>41</v>
+      </c>
+      <c r="AT35">
+        <f>AS35+1</f>
+        <v>42</v>
+      </c>
+      <c r="AU35">
+        <f>AT35+1</f>
+        <v>43</v>
+      </c>
+      <c r="AV35">
+        <f>AU35+1</f>
+        <v>44</v>
+      </c>
+      <c r="AW35">
+        <f>AV35+1</f>
+        <v>45</v>
+      </c>
+      <c r="AX35">
+        <f>AW35+1</f>
+        <v>46</v>
+      </c>
+      <c r="AY35">
+        <f>AX35+1</f>
+        <v>47</v>
+      </c>
+      <c r="AZ35">
+        <f>AY35+1</f>
+        <v>48</v>
+      </c>
+      <c r="BA35">
+        <f>AZ35+1</f>
+        <v>49</v>
+      </c>
+      <c r="BB35">
+        <f>BA35+1</f>
+        <v>50</v>
+      </c>
+      <c r="BC35">
+        <f>BB35+1</f>
+        <v>51</v>
+      </c>
+      <c r="BD35">
+        <f>BC35+1</f>
+        <v>52</v>
+      </c>
+      <c r="BE35">
+        <f>BD35+1</f>
+        <v>53</v>
+      </c>
+      <c r="BF35">
+        <f>BE35+1</f>
+        <v>54</v>
+      </c>
+      <c r="BG35">
+        <f>BF35+1</f>
+        <v>55</v>
+      </c>
+      <c r="BH35">
+        <f>BG35+1</f>
+        <v>56</v>
+      </c>
+      <c r="BI35">
+        <f>BH35+1</f>
+        <v>57</v>
+      </c>
+      <c r="BJ35">
+        <f>BI35+1</f>
+        <v>58</v>
+      </c>
+      <c r="BK35">
+        <f>BJ35+1</f>
+        <v>59</v>
+      </c>
+      <c r="BL35">
+        <f>BK35+1</f>
+        <v>60</v>
+      </c>
+      <c r="BM35">
+        <f>BL35+1</f>
+        <v>61</v>
+      </c>
     </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B36" t="s">
-        <v>68</v>
+    <row r="36" spans="2:65" x14ac:dyDescent="0.35">
+      <c r="B36" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36" t="str">
+        <f>IF(MIN(Class_0!B2,Class_1!B2,Class_2!B2)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
       </c>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B37" t="s">
-        <v>68</v>
+    <row r="37" spans="2:65" x14ac:dyDescent="0.35">
+      <c r="B37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37">
+        <f>C36+1</f>
+        <v>1</v>
+      </c>
+      <c r="D37" t="str">
+        <f>IF(MIN(Class_0!B3,Class_1!B3,Class_2!B3)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="E37" t="str">
+        <f>IF(MIN(Class_0!C3,Class_1!C3,Class_2!C3)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AT37" t="str">
+        <f>IF(MIN(Class_0!AR3,Class_1!AR3,Class_2!AR3)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
       </c>
     </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B38" t="s">
-        <v>68</v>
+    <row r="38" spans="2:65" x14ac:dyDescent="0.35">
+      <c r="B38" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38">
+        <f t="shared" ref="C38:C97" si="7">C37+1</f>
+        <v>2</v>
+      </c>
+      <c r="D38" t="str">
+        <f>IF(MIN(Class_0!B4,Class_1!B4,Class_2!B4)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E38" t="str">
+        <f>IF(MIN(Class_0!C4,Class_1!C4,Class_2!C4)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F38" t="str">
+        <f>IF(MIN(Class_0!D4,Class_1!D4,Class_2!D4)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
       </c>
     </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B39" t="s">
-        <v>68</v>
+    <row r="39" spans="2:65" x14ac:dyDescent="0.35">
+      <c r="B39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C39">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="D39" t="str">
+        <f>IF(MIN(Class_0!B5,Class_1!B5,Class_2!B5)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="E39" t="str">
+        <f>IF(MIN(Class_0!C5,Class_1!C5,Class_2!C5)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F39" t="str">
+        <f>IF(MIN(Class_0!D5,Class_1!D5,Class_2!D5)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G39" t="str">
+        <f>IF(MIN(Class_0!E5,Class_1!E5,Class_2!E5)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
       </c>
     </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B46" t="s">
-        <v>68</v>
+    <row r="40" spans="2:65" x14ac:dyDescent="0.35">
+      <c r="B40" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C40">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="D40" t="str">
+        <f>IF(MIN(Class_0!B6,Class_1!B6,Class_2!B6)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="E40" t="str">
+        <f>IF(MIN(Class_0!C6,Class_1!C6,Class_2!C6)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F40" t="str">
+        <f>IF(MIN(Class_0!D6,Class_1!D6,Class_2!D6)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G40" t="str">
+        <f>IF(MIN(Class_0!E6,Class_1!E6,Class_2!E6)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H40" t="str">
+        <f>IF(MIN(Class_0!F6,Class_1!F6,Class_2!F6)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Z40" t="str">
+        <f>IF(MIN(Class_0!X6,Class_1!X6,Class_2!X6)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
       </c>
     </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B47" t="s">
-        <v>68</v>
+    <row r="41" spans="2:65" x14ac:dyDescent="0.35">
+      <c r="B41" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="D41" t="str">
+        <f>IF(MIN(Class_0!B7,Class_1!B7,Class_2!B7)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="E41" t="str">
+        <f>IF(MIN(Class_0!C7,Class_1!C7,Class_2!C7)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F41" t="str">
+        <f>IF(MIN(Class_0!D7,Class_1!D7,Class_2!D7)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G41" t="str">
+        <f>IF(MIN(Class_0!E7,Class_1!E7,Class_2!E7)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H41" t="str">
+        <f>IF(MIN(Class_0!F7,Class_1!F7,Class_2!F7)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="I41" t="str">
+        <f>IF(MIN(Class_0!G7,Class_1!G7,Class_2!G7)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
       </c>
     </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B48" t="s">
-        <v>68</v>
+    <row r="42" spans="2:65" x14ac:dyDescent="0.35">
+      <c r="B42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="D42" t="str">
+        <f>IF(MIN(Class_0!B8,Class_1!B8,Class_2!B8)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E42" t="str">
+        <f>IF(MIN(Class_0!C8,Class_1!C8,Class_2!C8)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F42" t="str">
+        <f>IF(MIN(Class_0!D8,Class_1!D8,Class_2!D8)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G42" t="str">
+        <f>IF(MIN(Class_0!E8,Class_1!E8,Class_2!E8)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H42" t="str">
+        <f>IF(MIN(Class_0!F8,Class_1!F8,Class_2!F8)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I42" t="str">
+        <f>IF(MIN(Class_0!G8,Class_1!G8,Class_2!G8)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J42" t="str">
+        <f>IF(MIN(Class_0!H8,Class_1!H8,Class_2!H8)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
       </c>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B51" t="s">
-        <v>68</v>
+    <row r="43" spans="2:65" x14ac:dyDescent="0.35">
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="D43" t="str">
+        <f>IF(MIN(Class_0!B9,Class_1!B9,Class_2!B9)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="E43" t="str">
+        <f>IF(MIN(Class_0!C9,Class_1!C9,Class_2!C9)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F43" t="str">
+        <f>IF(MIN(Class_0!D9,Class_1!D9,Class_2!D9)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G43" t="str">
+        <f>IF(MIN(Class_0!E9,Class_1!E9,Class_2!E9)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H43" t="str">
+        <f>IF(MIN(Class_0!F9,Class_1!F9,Class_2!F9)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I43" t="str">
+        <f>IF(MIN(Class_0!G9,Class_1!G9,Class_2!G9)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="J43" t="str">
+        <f>IF(MIN(Class_0!H9,Class_1!H9,Class_2!H9)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="K43" t="str">
+        <f>IF(MIN(Class_0!I9,Class_1!I9,Class_2!I9)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
       </c>
     </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B52" t="s">
-        <v>68</v>
+    <row r="44" spans="2:65" x14ac:dyDescent="0.35">
+      <c r="B44" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="D44" t="str">
+        <f>IF(MIN(Class_0!B10,Class_1!B10,Class_2!B10)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="E44" t="str">
+        <f>IF(MIN(Class_0!C10,Class_1!C10,Class_2!C10)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F44" t="str">
+        <f>IF(MIN(Class_0!D10,Class_1!D10,Class_2!D10)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G44" t="str">
+        <f>IF(MIN(Class_0!E10,Class_1!E10,Class_2!E10)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H44" t="str">
+        <f>IF(MIN(Class_0!F10,Class_1!F10,Class_2!F10)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I44" t="str">
+        <f>IF(MIN(Class_0!G10,Class_1!G10,Class_2!G10)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J44" t="str">
+        <f>IF(MIN(Class_0!H10,Class_1!H10,Class_2!H10)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="K44" t="str">
+        <f>IF(MIN(Class_0!I10,Class_1!I10,Class_2!I10)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="L44" t="str">
+        <f>IF(MIN(Class_0!J10,Class_1!J10,Class_2!J10)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
       </c>
     </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B53" t="s">
-        <v>68</v>
+    <row r="45" spans="2:65" x14ac:dyDescent="0.35">
+      <c r="B45" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C45">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="D45" t="str">
+        <f>IF(MIN(Class_0!B11,Class_1!B11,Class_2!B11)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="E45" t="str">
+        <f>IF(MIN(Class_0!C11,Class_1!C11,Class_2!C11)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F45" t="str">
+        <f>IF(MIN(Class_0!D11,Class_1!D11,Class_2!D11)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G45" t="str">
+        <f>IF(MIN(Class_0!E11,Class_1!E11,Class_2!E11)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H45" t="str">
+        <f>IF(MIN(Class_0!F11,Class_1!F11,Class_2!F11)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="I45" t="str">
+        <f>IF(MIN(Class_0!G11,Class_1!G11,Class_2!G11)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="J45" t="str">
+        <f>IF(MIN(Class_0!H11,Class_1!H11,Class_2!H11)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K45" t="str">
+        <f>IF(MIN(Class_0!I11,Class_1!I11,Class_2!I11)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L45" t="str">
+        <f>IF(MIN(Class_0!J11,Class_1!J11,Class_2!J11)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M45" t="str">
+        <f>IF(MIN(Class_0!K11,Class_1!K11,Class_2!K11)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
       </c>
     </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B54" t="s">
-        <v>68</v>
+    <row r="46" spans="2:65" x14ac:dyDescent="0.35">
+      <c r="B46" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46">
+        <f t="shared" si="7"/>
+        <v>10</v>
+      </c>
+      <c r="D46" t="str">
+        <f>IF(MIN(Class_0!B12,Class_1!B12,Class_2!B12)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="E46" t="str">
+        <f>IF(MIN(Class_0!C12,Class_1!C12,Class_2!C12)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F46" t="str">
+        <f>IF(MIN(Class_0!D12,Class_1!D12,Class_2!D12)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G46" t="str">
+        <f>IF(MIN(Class_0!E12,Class_1!E12,Class_2!E12)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H46" t="str">
+        <f>IF(MIN(Class_0!F12,Class_1!F12,Class_2!F12)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="I46" t="str">
+        <f>IF(MIN(Class_0!G12,Class_1!G12,Class_2!G12)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="J46" t="str">
+        <f>IF(MIN(Class_0!H12,Class_1!H12,Class_2!H12)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K46" t="str">
+        <f>IF(MIN(Class_0!I12,Class_1!I12,Class_2!I12)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L46" t="str">
+        <f>IF(MIN(Class_0!J12,Class_1!J12,Class_2!J12)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M46" t="str">
+        <f>IF(MIN(Class_0!K12,Class_1!K12,Class_2!K12)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N46" t="str">
+        <f>IF(MIN(Class_0!L12,Class_1!L12,Class_2!L12)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
       </c>
     </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B55" t="s">
-        <v>68</v>
+    <row r="47" spans="2:65" x14ac:dyDescent="0.35">
+      <c r="B47" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C47">
+        <f t="shared" si="7"/>
+        <v>11</v>
+      </c>
+      <c r="D47" t="str">
+        <f>IF(MIN(Class_0!B13,Class_1!B13,Class_2!B13)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="E47" t="str">
+        <f>IF(MIN(Class_0!C13,Class_1!C13,Class_2!C13)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F47" t="str">
+        <f>IF(MIN(Class_0!D13,Class_1!D13,Class_2!D13)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G47" t="str">
+        <f>IF(MIN(Class_0!E13,Class_1!E13,Class_2!E13)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H47" t="str">
+        <f>IF(MIN(Class_0!F13,Class_1!F13,Class_2!F13)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="I47" t="str">
+        <f>IF(MIN(Class_0!G13,Class_1!G13,Class_2!G13)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J47" t="str">
+        <f>IF(MIN(Class_0!H13,Class_1!H13,Class_2!H13)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K47" t="str">
+        <f>IF(MIN(Class_0!I13,Class_1!I13,Class_2!I13)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L47" t="str">
+        <f>IF(MIN(Class_0!J13,Class_1!J13,Class_2!J13)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M47" t="str">
+        <f>IF(MIN(Class_0!K13,Class_1!K13,Class_2!K13)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N47" t="str">
+        <f>IF(MIN(Class_0!L13,Class_1!L13,Class_2!L13)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O47" t="str">
+        <f>IF(MIN(Class_0!M13,Class_1!M13,Class_2!M13)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="48" spans="2:65" x14ac:dyDescent="0.35">
+      <c r="B48" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48">
+        <f t="shared" si="7"/>
+        <v>12</v>
+      </c>
+      <c r="D48" t="str">
+        <f>IF(MIN(Class_0!B14,Class_1!B14,Class_2!B14)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E48" t="str">
+        <f>IF(MIN(Class_0!C14,Class_1!C14,Class_2!C14)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F48" t="str">
+        <f>IF(MIN(Class_0!D14,Class_1!D14,Class_2!D14)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G48" t="str">
+        <f>IF(MIN(Class_0!E14,Class_1!E14,Class_2!E14)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H48" t="str">
+        <f>IF(MIN(Class_0!F14,Class_1!F14,Class_2!F14)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I48" t="str">
+        <f>IF(MIN(Class_0!G14,Class_1!G14,Class_2!G14)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J48" t="str">
+        <f>IF(MIN(Class_0!H14,Class_1!H14,Class_2!H14)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K48" t="str">
+        <f>IF(MIN(Class_0!I14,Class_1!I14,Class_2!I14)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L48" t="str">
+        <f>IF(MIN(Class_0!J14,Class_1!J14,Class_2!J14)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M48" t="str">
+        <f>IF(MIN(Class_0!K14,Class_1!K14,Class_2!K14)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N48" t="str">
+        <f>IF(MIN(Class_0!L14,Class_1!L14,Class_2!L14)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O48" t="str">
+        <f>IF(MIN(Class_0!M14,Class_1!M14,Class_2!M14)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P48" t="str">
+        <f>IF(MIN(Class_0!N14,Class_1!N14,Class_2!N14)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="49" spans="2:46" x14ac:dyDescent="0.35">
+      <c r="B49" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="D49" t="str">
+        <f>IF(MIN(Class_0!B15,Class_1!B15,Class_2!B15)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="E49" t="str">
+        <f>IF(MIN(Class_0!C15,Class_1!C15,Class_2!C15)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F49" t="str">
+        <f>IF(MIN(Class_0!D15,Class_1!D15,Class_2!D15)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G49" t="str">
+        <f>IF(MIN(Class_0!E15,Class_1!E15,Class_2!E15)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H49" t="str">
+        <f>IF(MIN(Class_0!F15,Class_1!F15,Class_2!F15)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="I49" t="str">
+        <f>IF(MIN(Class_0!G15,Class_1!G15,Class_2!G15)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="J49" t="str">
+        <f>IF(MIN(Class_0!H15,Class_1!H15,Class_2!H15)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K49" t="str">
+        <f>IF(MIN(Class_0!I15,Class_1!I15,Class_2!I15)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L49" t="str">
+        <f>IF(MIN(Class_0!J15,Class_1!J15,Class_2!J15)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M49" t="str">
+        <f>IF(MIN(Class_0!K15,Class_1!K15,Class_2!K15)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N49" t="str">
+        <f>IF(MIN(Class_0!L15,Class_1!L15,Class_2!L15)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="O49" t="str">
+        <f>IF(MIN(Class_0!M15,Class_1!M15,Class_2!M15)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="P49" t="str">
+        <f>IF(MIN(Class_0!N15,Class_1!N15,Class_2!N15)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q49" t="str">
+        <f>IF(MIN(Class_0!O15,Class_1!O15,Class_2!O15)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="50" spans="2:46" x14ac:dyDescent="0.35">
+      <c r="B50" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C50">
+        <f t="shared" si="7"/>
+        <v>14</v>
+      </c>
+      <c r="D50" t="str">
+        <f>IF(MIN(Class_0!B16,Class_1!B16,Class_2!B16)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E50" t="str">
+        <f>IF(MIN(Class_0!C16,Class_1!C16,Class_2!C16)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F50" t="str">
+        <f>IF(MIN(Class_0!D16,Class_1!D16,Class_2!D16)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G50" t="str">
+        <f>IF(MIN(Class_0!E16,Class_1!E16,Class_2!E16)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H50" t="str">
+        <f>IF(MIN(Class_0!F16,Class_1!F16,Class_2!F16)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="I50" t="str">
+        <f>IF(MIN(Class_0!G16,Class_1!G16,Class_2!G16)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="J50" t="str">
+        <f>IF(MIN(Class_0!H16,Class_1!H16,Class_2!H16)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K50" t="str">
+        <f>IF(MIN(Class_0!I16,Class_1!I16,Class_2!I16)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L50" t="str">
+        <f>IF(MIN(Class_0!J16,Class_1!J16,Class_2!J16)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M50" t="str">
+        <f>IF(MIN(Class_0!K16,Class_1!K16,Class_2!K16)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N50" t="str">
+        <f>IF(MIN(Class_0!L16,Class_1!L16,Class_2!L16)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="O50" t="str">
+        <f>IF(MIN(Class_0!M16,Class_1!M16,Class_2!M16)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P50" t="str">
+        <f>IF(MIN(Class_0!N16,Class_1!N16,Class_2!N16)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q50" t="str">
+        <f>IF(MIN(Class_0!O16,Class_1!O16,Class_2!O16)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R50" t="str">
+        <f>IF(MIN(Class_0!P16,Class_1!P16,Class_2!P16)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="51" spans="2:46" x14ac:dyDescent="0.35">
+      <c r="B51" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C51">
+        <f t="shared" si="7"/>
+        <v>15</v>
+      </c>
+      <c r="D51" t="str">
+        <f>IF(MIN(Class_0!B17,Class_1!B17,Class_2!B17)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E51" t="str">
+        <f>IF(MIN(Class_0!C17,Class_1!C17,Class_2!C17)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F51" t="str">
+        <f>IF(MIN(Class_0!D17,Class_1!D17,Class_2!D17)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G51" t="str">
+        <f>IF(MIN(Class_0!E17,Class_1!E17,Class_2!E17)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H51" t="str">
+        <f>IF(MIN(Class_0!F17,Class_1!F17,Class_2!F17)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I51" t="str">
+        <f>IF(MIN(Class_0!G17,Class_1!G17,Class_2!G17)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J51" t="str">
+        <f>IF(MIN(Class_0!H17,Class_1!H17,Class_2!H17)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="K51" t="str">
+        <f>IF(MIN(Class_0!I17,Class_1!I17,Class_2!I17)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L51" t="str">
+        <f>IF(MIN(Class_0!J17,Class_1!J17,Class_2!J17)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M51" t="str">
+        <f>IF(MIN(Class_0!K17,Class_1!K17,Class_2!K17)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N51" t="str">
+        <f>IF(MIN(Class_0!L17,Class_1!L17,Class_2!L17)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O51" t="str">
+        <f>IF(MIN(Class_0!M17,Class_1!M17,Class_2!M17)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P51" t="str">
+        <f>IF(MIN(Class_0!N17,Class_1!N17,Class_2!N17)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q51" t="str">
+        <f>IF(MIN(Class_0!O17,Class_1!O17,Class_2!O17)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R51" t="str">
+        <f>IF(MIN(Class_0!P17,Class_1!P17,Class_2!P17)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S51" t="str">
+        <f>IF(MIN(Class_0!Q17,Class_1!Q17,Class_2!Q17)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="52" spans="2:46" x14ac:dyDescent="0.35">
+      <c r="B52" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52">
+        <f t="shared" si="7"/>
+        <v>16</v>
+      </c>
+      <c r="D52" t="str">
+        <f>IF(MIN(Class_0!B18,Class_1!B18,Class_2!B18)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E52" t="str">
+        <f>IF(MIN(Class_0!C18,Class_1!C18,Class_2!C18)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F52" t="str">
+        <f>IF(MIN(Class_0!D18,Class_1!D18,Class_2!D18)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G52" t="str">
+        <f>IF(MIN(Class_0!E18,Class_1!E18,Class_2!E18)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H52" t="str">
+        <f>IF(MIN(Class_0!F18,Class_1!F18,Class_2!F18)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I52" t="str">
+        <f>IF(MIN(Class_0!G18,Class_1!G18,Class_2!G18)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J52" t="str">
+        <f>IF(MIN(Class_0!H18,Class_1!H18,Class_2!H18)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K52" t="str">
+        <f>IF(MIN(Class_0!I18,Class_1!I18,Class_2!I18)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L52" t="str">
+        <f>IF(MIN(Class_0!J18,Class_1!J18,Class_2!J18)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M52" t="str">
+        <f>IF(MIN(Class_0!K18,Class_1!K18,Class_2!K18)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N52" t="str">
+        <f>IF(MIN(Class_0!L18,Class_1!L18,Class_2!L18)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O52" t="str">
+        <f>IF(MIN(Class_0!M18,Class_1!M18,Class_2!M18)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P52" t="str">
+        <f>IF(MIN(Class_0!N18,Class_1!N18,Class_2!N18)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q52" t="str">
+        <f>IF(MIN(Class_0!O18,Class_1!O18,Class_2!O18)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R52" t="str">
+        <f>IF(MIN(Class_0!P18,Class_1!P18,Class_2!P18)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S52" t="str">
+        <f>IF(MIN(Class_0!Q18,Class_1!Q18,Class_2!Q18)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T52" t="str">
+        <f>IF(MIN(Class_0!R18,Class_1!R18,Class_2!R18)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="53" spans="2:46" x14ac:dyDescent="0.35">
+      <c r="B53" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C53">
+        <f t="shared" si="7"/>
+        <v>17</v>
+      </c>
+      <c r="D53" t="str">
+        <f>IF(MIN(Class_0!B19,Class_1!B19,Class_2!B19)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E53" t="str">
+        <f>IF(MIN(Class_0!C19,Class_1!C19,Class_2!C19)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F53" t="str">
+        <f>IF(MIN(Class_0!D19,Class_1!D19,Class_2!D19)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G53" t="str">
+        <f>IF(MIN(Class_0!E19,Class_1!E19,Class_2!E19)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H53" t="str">
+        <f>IF(MIN(Class_0!F19,Class_1!F19,Class_2!F19)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I53" t="str">
+        <f>IF(MIN(Class_0!G19,Class_1!G19,Class_2!G19)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J53" t="str">
+        <f>IF(MIN(Class_0!H19,Class_1!H19,Class_2!H19)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="K53" t="str">
+        <f>IF(MIN(Class_0!I19,Class_1!I19,Class_2!I19)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L53" t="str">
+        <f>IF(MIN(Class_0!J19,Class_1!J19,Class_2!J19)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M53" t="str">
+        <f>IF(MIN(Class_0!K19,Class_1!K19,Class_2!K19)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N53" t="str">
+        <f>IF(MIN(Class_0!L19,Class_1!L19,Class_2!L19)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O53" t="str">
+        <f>IF(MIN(Class_0!M19,Class_1!M19,Class_2!M19)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P53" t="str">
+        <f>IF(MIN(Class_0!N19,Class_1!N19,Class_2!N19)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q53" t="str">
+        <f>IF(MIN(Class_0!O19,Class_1!O19,Class_2!O19)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R53" t="str">
+        <f>IF(MIN(Class_0!P19,Class_1!P19,Class_2!P19)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S53" t="str">
+        <f>IF(MIN(Class_0!Q19,Class_1!Q19,Class_2!Q19)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T53" t="str">
+        <f>IF(MIN(Class_0!R19,Class_1!R19,Class_2!R19)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="U53" t="str">
+        <f>IF(MIN(Class_0!S19,Class_1!S19,Class_2!S19)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="54" spans="2:46" x14ac:dyDescent="0.35">
+      <c r="B54" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C54">
+        <f t="shared" si="7"/>
+        <v>18</v>
+      </c>
+      <c r="D54" t="str">
+        <f>IF(MIN(Class_0!B20,Class_1!B20,Class_2!B20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E54" t="str">
+        <f>IF(MIN(Class_0!C20,Class_1!C20,Class_2!C20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F54" t="str">
+        <f>IF(MIN(Class_0!D20,Class_1!D20,Class_2!D20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G54" t="str">
+        <f>IF(MIN(Class_0!E20,Class_1!E20,Class_2!E20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H54" t="str">
+        <f>IF(MIN(Class_0!F20,Class_1!F20,Class_2!F20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I54" t="str">
+        <f>IF(MIN(Class_0!G20,Class_1!G20,Class_2!G20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J54" t="str">
+        <f>IF(MIN(Class_0!H20,Class_1!H20,Class_2!H20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="K54" t="str">
+        <f>IF(MIN(Class_0!I20,Class_1!I20,Class_2!I20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="L54" t="str">
+        <f>IF(MIN(Class_0!J20,Class_1!J20,Class_2!J20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M54" t="str">
+        <f>IF(MIN(Class_0!K20,Class_1!K20,Class_2!K20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N54" t="str">
+        <f>IF(MIN(Class_0!L20,Class_1!L20,Class_2!L20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O54" t="str">
+        <f>IF(MIN(Class_0!M20,Class_1!M20,Class_2!M20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P54" t="str">
+        <f>IF(MIN(Class_0!N20,Class_1!N20,Class_2!N20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q54" t="str">
+        <f>IF(MIN(Class_0!O20,Class_1!O20,Class_2!O20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R54" t="str">
+        <f>IF(MIN(Class_0!P20,Class_1!P20,Class_2!P20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S54" t="str">
+        <f>IF(MIN(Class_0!Q20,Class_1!Q20,Class_2!Q20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T54" t="str">
+        <f>IF(MIN(Class_0!R20,Class_1!R20,Class_2!R20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="U54" t="str">
+        <f>IF(MIN(Class_0!S20,Class_1!S20,Class_2!S20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="V54" t="str">
+        <f>IF(MIN(Class_0!T20,Class_1!T20,Class_2!T20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="55" spans="2:46" x14ac:dyDescent="0.35">
+      <c r="B55" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C55">
+        <f t="shared" si="7"/>
+        <v>19</v>
+      </c>
+      <c r="D55" t="str">
+        <f>IF(MIN(Class_0!B21,Class_1!B21,Class_2!B21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E55" t="str">
+        <f>IF(MIN(Class_0!C21,Class_1!C21,Class_2!C21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F55" t="str">
+        <f>IF(MIN(Class_0!D21,Class_1!D21,Class_2!D21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G55" t="str">
+        <f>IF(MIN(Class_0!E21,Class_1!E21,Class_2!E21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H55" t="str">
+        <f>IF(MIN(Class_0!F21,Class_1!F21,Class_2!F21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I55" t="str">
+        <f>IF(MIN(Class_0!G21,Class_1!G21,Class_2!G21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J55" t="str">
+        <f>IF(MIN(Class_0!H21,Class_1!H21,Class_2!H21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="K55" t="str">
+        <f>IF(MIN(Class_0!I21,Class_1!I21,Class_2!I21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L55" t="str">
+        <f>IF(MIN(Class_0!J21,Class_1!J21,Class_2!J21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M55" t="str">
+        <f>IF(MIN(Class_0!K21,Class_1!K21,Class_2!K21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N55" t="str">
+        <f>IF(MIN(Class_0!L21,Class_1!L21,Class_2!L21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="O55" t="str">
+        <f>IF(MIN(Class_0!M21,Class_1!M21,Class_2!M21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P55" t="str">
+        <f>IF(MIN(Class_0!N21,Class_1!N21,Class_2!N21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q55" t="str">
+        <f>IF(MIN(Class_0!O21,Class_1!O21,Class_2!O21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R55" t="str">
+        <f>IF(MIN(Class_0!P21,Class_1!P21,Class_2!P21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S55" t="str">
+        <f>IF(MIN(Class_0!Q21,Class_1!Q21,Class_2!Q21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T55" t="str">
+        <f>IF(MIN(Class_0!R21,Class_1!R21,Class_2!R21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U55" t="str">
+        <f>IF(MIN(Class_0!S21,Class_1!S21,Class_2!S21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V55" t="str">
+        <f>IF(MIN(Class_0!T21,Class_1!T21,Class_2!T21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="W55" t="str">
+        <f>IF(MIN(Class_0!U21,Class_1!U21,Class_2!U21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AT55" t="str">
+        <f>IF(MIN(Class_0!AR21,Class_1!AR21,Class_2!AR21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="56" spans="2:46" x14ac:dyDescent="0.35">
+      <c r="B56" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C56">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="D56" t="str">
+        <f>IF(MIN(Class_0!B22,Class_1!B22,Class_2!B22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E56" t="str">
+        <f>IF(MIN(Class_0!C22,Class_1!C22,Class_2!C22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F56" t="str">
+        <f>IF(MIN(Class_0!D22,Class_1!D22,Class_2!D22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G56" t="str">
+        <f>IF(MIN(Class_0!E22,Class_1!E22,Class_2!E22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H56" t="str">
+        <f>IF(MIN(Class_0!F22,Class_1!F22,Class_2!F22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I56" t="str">
+        <f>IF(MIN(Class_0!G22,Class_1!G22,Class_2!G22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J56" t="str">
+        <f>IF(MIN(Class_0!H22,Class_1!H22,Class_2!H22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K56" t="str">
+        <f>IF(MIN(Class_0!I22,Class_1!I22,Class_2!I22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L56" t="str">
+        <f>IF(MIN(Class_0!J22,Class_1!J22,Class_2!J22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M56" t="str">
+        <f>IF(MIN(Class_0!K22,Class_1!K22,Class_2!K22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N56" t="str">
+        <f>IF(MIN(Class_0!L22,Class_1!L22,Class_2!L22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O56" t="str">
+        <f>IF(MIN(Class_0!M22,Class_1!M22,Class_2!M22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P56" t="str">
+        <f>IF(MIN(Class_0!N22,Class_1!N22,Class_2!N22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q56" t="str">
+        <f>IF(MIN(Class_0!O22,Class_1!O22,Class_2!O22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R56" t="str">
+        <f>IF(MIN(Class_0!P22,Class_1!P22,Class_2!P22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S56" t="str">
+        <f>IF(MIN(Class_0!Q22,Class_1!Q22,Class_2!Q22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T56" t="str">
+        <f>IF(MIN(Class_0!R22,Class_1!R22,Class_2!R22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="U56" t="str">
+        <f>IF(MIN(Class_0!S22,Class_1!S22,Class_2!S22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V56" t="str">
+        <f>IF(MIN(Class_0!T22,Class_1!T22,Class_2!T22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="W56" t="str">
+        <f>IF(MIN(Class_0!U22,Class_1!U22,Class_2!U22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="X56" t="str">
+        <f>IF(MIN(Class_0!V22,Class_1!V22,Class_2!V22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="57" spans="2:46" x14ac:dyDescent="0.35">
+      <c r="B57" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C57">
+        <f t="shared" si="7"/>
+        <v>21</v>
+      </c>
+      <c r="D57" t="str">
+        <f>IF(MIN(Class_0!B23,Class_1!B23,Class_2!B23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E57" t="str">
+        <f>IF(MIN(Class_0!C23,Class_1!C23,Class_2!C23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F57" t="str">
+        <f>IF(MIN(Class_0!D23,Class_1!D23,Class_2!D23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G57" t="str">
+        <f>IF(MIN(Class_0!E23,Class_1!E23,Class_2!E23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H57" t="str">
+        <f>IF(MIN(Class_0!F23,Class_1!F23,Class_2!F23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I57" t="str">
+        <f>IF(MIN(Class_0!G23,Class_1!G23,Class_2!G23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J57" t="str">
+        <f>IF(MIN(Class_0!H23,Class_1!H23,Class_2!H23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="K57" t="str">
+        <f>IF(MIN(Class_0!I23,Class_1!I23,Class_2!I23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L57" t="str">
+        <f>IF(MIN(Class_0!J23,Class_1!J23,Class_2!J23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M57" t="str">
+        <f>IF(MIN(Class_0!K23,Class_1!K23,Class_2!K23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N57" t="str">
+        <f>IF(MIN(Class_0!L23,Class_1!L23,Class_2!L23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O57" t="str">
+        <f>IF(MIN(Class_0!M23,Class_1!M23,Class_2!M23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P57" t="str">
+        <f>IF(MIN(Class_0!N23,Class_1!N23,Class_2!N23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q57" t="str">
+        <f>IF(MIN(Class_0!O23,Class_1!O23,Class_2!O23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R57" t="str">
+        <f>IF(MIN(Class_0!P23,Class_1!P23,Class_2!P23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S57" t="str">
+        <f>IF(MIN(Class_0!Q23,Class_1!Q23,Class_2!Q23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T57" t="str">
+        <f>IF(MIN(Class_0!R23,Class_1!R23,Class_2!R23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="U57" t="str">
+        <f>IF(MIN(Class_0!S23,Class_1!S23,Class_2!S23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="V57" t="str">
+        <f>IF(MIN(Class_0!T23,Class_1!T23,Class_2!T23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W57" t="str">
+        <f>IF(MIN(Class_0!U23,Class_1!U23,Class_2!U23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X57" t="str">
+        <f>IF(MIN(Class_0!V23,Class_1!V23,Class_2!V23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y57" t="str">
+        <f>IF(MIN(Class_0!W23,Class_1!W23,Class_2!W23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="58" spans="2:46" x14ac:dyDescent="0.35">
+      <c r="B58" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C58">
+        <f t="shared" si="7"/>
+        <v>22</v>
+      </c>
+      <c r="D58" t="str">
+        <f>IF(MIN(Class_0!B24,Class_1!B24,Class_2!B24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E58" t="str">
+        <f>IF(MIN(Class_0!C24,Class_1!C24,Class_2!C24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F58" t="str">
+        <f>IF(MIN(Class_0!D24,Class_1!D24,Class_2!D24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G58" t="str">
+        <f>IF(MIN(Class_0!E24,Class_1!E24,Class_2!E24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H58" t="str">
+        <f>IF(MIN(Class_0!F24,Class_1!F24,Class_2!F24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I58" t="str">
+        <f>IF(MIN(Class_0!G24,Class_1!G24,Class_2!G24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J58" t="str">
+        <f>IF(MIN(Class_0!H24,Class_1!H24,Class_2!H24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K58" t="str">
+        <f>IF(MIN(Class_0!I24,Class_1!I24,Class_2!I24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L58" t="str">
+        <f>IF(MIN(Class_0!J24,Class_1!J24,Class_2!J24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M58" t="str">
+        <f>IF(MIN(Class_0!K24,Class_1!K24,Class_2!K24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N58" t="str">
+        <f>IF(MIN(Class_0!L24,Class_1!L24,Class_2!L24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O58" t="str">
+        <f>IF(MIN(Class_0!M24,Class_1!M24,Class_2!M24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P58" t="str">
+        <f>IF(MIN(Class_0!N24,Class_1!N24,Class_2!N24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q58" t="str">
+        <f>IF(MIN(Class_0!O24,Class_1!O24,Class_2!O24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R58" t="str">
+        <f>IF(MIN(Class_0!P24,Class_1!P24,Class_2!P24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S58" t="str">
+        <f>IF(MIN(Class_0!Q24,Class_1!Q24,Class_2!Q24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T58" t="str">
+        <f>IF(MIN(Class_0!R24,Class_1!R24,Class_2!R24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U58" t="str">
+        <f>IF(MIN(Class_0!S24,Class_1!S24,Class_2!S24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V58" t="str">
+        <f>IF(MIN(Class_0!T24,Class_1!T24,Class_2!T24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W58" t="str">
+        <f>IF(MIN(Class_0!U24,Class_1!U24,Class_2!U24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X58" t="str">
+        <f>IF(MIN(Class_0!V24,Class_1!V24,Class_2!V24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y58" t="str">
+        <f>IF(MIN(Class_0!W24,Class_1!W24,Class_2!W24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Z58" t="str">
+        <f>IF(MIN(Class_0!X24,Class_1!X24,Class_2!X24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="59" spans="2:46" x14ac:dyDescent="0.35">
+      <c r="B59" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C59">
+        <f t="shared" si="7"/>
+        <v>23</v>
+      </c>
+      <c r="D59" t="str">
+        <f>IF(MIN(Class_0!B25,Class_1!B25,Class_2!B25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="E59" t="str">
+        <f>IF(MIN(Class_0!C25,Class_1!C25,Class_2!C25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F59" t="str">
+        <f>IF(MIN(Class_0!D25,Class_1!D25,Class_2!D25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G59" t="str">
+        <f>IF(MIN(Class_0!E25,Class_1!E25,Class_2!E25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H59" t="str">
+        <f>IF(MIN(Class_0!F25,Class_1!F25,Class_2!F25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I59" t="str">
+        <f>IF(MIN(Class_0!G25,Class_1!G25,Class_2!G25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J59" t="str">
+        <f>IF(MIN(Class_0!H25,Class_1!H25,Class_2!H25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K59" t="str">
+        <f>IF(MIN(Class_0!I25,Class_1!I25,Class_2!I25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L59" t="str">
+        <f>IF(MIN(Class_0!J25,Class_1!J25,Class_2!J25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M59" t="str">
+        <f>IF(MIN(Class_0!K25,Class_1!K25,Class_2!K25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N59" t="str">
+        <f>IF(MIN(Class_0!L25,Class_1!L25,Class_2!L25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O59" t="str">
+        <f>IF(MIN(Class_0!M25,Class_1!M25,Class_2!M25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P59" t="str">
+        <f>IF(MIN(Class_0!N25,Class_1!N25,Class_2!N25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q59" t="str">
+        <f>IF(MIN(Class_0!O25,Class_1!O25,Class_2!O25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R59" t="str">
+        <f>IF(MIN(Class_0!P25,Class_1!P25,Class_2!P25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S59" t="str">
+        <f>IF(MIN(Class_0!Q25,Class_1!Q25,Class_2!Q25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T59" t="str">
+        <f>IF(MIN(Class_0!R25,Class_1!R25,Class_2!R25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U59" t="str">
+        <f>IF(MIN(Class_0!S25,Class_1!S25,Class_2!S25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V59" t="str">
+        <f>IF(MIN(Class_0!T25,Class_1!T25,Class_2!T25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W59" t="str">
+        <f>IF(MIN(Class_0!U25,Class_1!U25,Class_2!U25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="X59" t="str">
+        <f>IF(MIN(Class_0!V25,Class_1!V25,Class_2!V25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Y59" t="str">
+        <f>IF(MIN(Class_0!W25,Class_1!W25,Class_2!W25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z59" t="str">
+        <f>IF(MIN(Class_0!X25,Class_1!X25,Class_2!X25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA59" t="str">
+        <f>IF(MIN(Class_0!Y25,Class_1!Y25,Class_2!Y25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="60" spans="2:46" x14ac:dyDescent="0.35">
+      <c r="B60" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="D60" t="str">
+        <f>IF(MIN(Class_0!B26,Class_1!B26,Class_2!B26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E60" t="str">
+        <f>IF(MIN(Class_0!C26,Class_1!C26,Class_2!C26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F60" t="str">
+        <f>IF(MIN(Class_0!D26,Class_1!D26,Class_2!D26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G60" t="str">
+        <f>IF(MIN(Class_0!E26,Class_1!E26,Class_2!E26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H60" t="str">
+        <f>IF(MIN(Class_0!F26,Class_1!F26,Class_2!F26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="I60" t="str">
+        <f>IF(MIN(Class_0!G26,Class_1!G26,Class_2!G26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="J60" t="str">
+        <f>IF(MIN(Class_0!H26,Class_1!H26,Class_2!H26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K60" t="str">
+        <f>IF(MIN(Class_0!I26,Class_1!I26,Class_2!I26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L60" t="str">
+        <f>IF(MIN(Class_0!J26,Class_1!J26,Class_2!J26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M60" t="str">
+        <f>IF(MIN(Class_0!K26,Class_1!K26,Class_2!K26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N60" t="str">
+        <f>IF(MIN(Class_0!L26,Class_1!L26,Class_2!L26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="O60" t="str">
+        <f>IF(MIN(Class_0!M26,Class_1!M26,Class_2!M26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="P60" t="str">
+        <f>IF(MIN(Class_0!N26,Class_1!N26,Class_2!N26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q60" t="str">
+        <f>IF(MIN(Class_0!O26,Class_1!O26,Class_2!O26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R60" t="str">
+        <f>IF(MIN(Class_0!P26,Class_1!P26,Class_2!P26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S60" t="str">
+        <f>IF(MIN(Class_0!Q26,Class_1!Q26,Class_2!Q26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T60" t="str">
+        <f>IF(MIN(Class_0!R26,Class_1!R26,Class_2!R26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U60" t="str">
+        <f>IF(MIN(Class_0!S26,Class_1!S26,Class_2!S26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V60" t="str">
+        <f>IF(MIN(Class_0!T26,Class_1!T26,Class_2!T26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W60" t="str">
+        <f>IF(MIN(Class_0!U26,Class_1!U26,Class_2!U26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X60" t="str">
+        <f>IF(MIN(Class_0!V26,Class_1!V26,Class_2!V26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y60" t="str">
+        <f>IF(MIN(Class_0!W26,Class_1!W26,Class_2!W26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z60" t="str">
+        <f>IF(MIN(Class_0!X26,Class_1!X26,Class_2!X26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA60" t="str">
+        <f>IF(MIN(Class_0!Y26,Class_1!Y26,Class_2!Y26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB60" t="str">
+        <f>IF(MIN(Class_0!Z26,Class_1!Z26,Class_2!Z26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="61" spans="2:46" x14ac:dyDescent="0.35">
+      <c r="B61" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C61">
+        <f t="shared" si="7"/>
+        <v>25</v>
+      </c>
+      <c r="D61" t="str">
+        <f>IF(MIN(Class_0!B27,Class_1!B27,Class_2!B27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E61" t="str">
+        <f>IF(MIN(Class_0!C27,Class_1!C27,Class_2!C27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F61" t="str">
+        <f>IF(MIN(Class_0!D27,Class_1!D27,Class_2!D27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G61" t="str">
+        <f>IF(MIN(Class_0!E27,Class_1!E27,Class_2!E27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H61" t="str">
+        <f>IF(MIN(Class_0!F27,Class_1!F27,Class_2!F27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I61" t="str">
+        <f>IF(MIN(Class_0!G27,Class_1!G27,Class_2!G27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J61" t="str">
+        <f>IF(MIN(Class_0!H27,Class_1!H27,Class_2!H27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K61" t="str">
+        <f>IF(MIN(Class_0!I27,Class_1!I27,Class_2!I27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L61" t="str">
+        <f>IF(MIN(Class_0!J27,Class_1!J27,Class_2!J27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M61" t="str">
+        <f>IF(MIN(Class_0!K27,Class_1!K27,Class_2!K27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N61" t="str">
+        <f>IF(MIN(Class_0!L27,Class_1!L27,Class_2!L27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="O61" t="str">
+        <f>IF(MIN(Class_0!M27,Class_1!M27,Class_2!M27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="P61" t="str">
+        <f>IF(MIN(Class_0!N27,Class_1!N27,Class_2!N27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q61" t="str">
+        <f>IF(MIN(Class_0!O27,Class_1!O27,Class_2!O27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R61" t="str">
+        <f>IF(MIN(Class_0!P27,Class_1!P27,Class_2!P27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S61" t="str">
+        <f>IF(MIN(Class_0!Q27,Class_1!Q27,Class_2!Q27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T61" t="str">
+        <f>IF(MIN(Class_0!R27,Class_1!R27,Class_2!R27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U61" t="str">
+        <f>IF(MIN(Class_0!S27,Class_1!S27,Class_2!S27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V61" t="str">
+        <f>IF(MIN(Class_0!T27,Class_1!T27,Class_2!T27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W61" t="str">
+        <f>IF(MIN(Class_0!U27,Class_1!U27,Class_2!U27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X61" t="str">
+        <f>IF(MIN(Class_0!V27,Class_1!V27,Class_2!V27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y61" t="str">
+        <f>IF(MIN(Class_0!W27,Class_1!W27,Class_2!W27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z61" t="str">
+        <f>IF(MIN(Class_0!X27,Class_1!X27,Class_2!X27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA61" t="str">
+        <f>IF(MIN(Class_0!Y27,Class_1!Y27,Class_2!Y27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB61" t="str">
+        <f>IF(MIN(Class_0!Z27,Class_1!Z27,Class_2!Z27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC61" t="str">
+        <f>IF(MIN(Class_0!AA27,Class_1!AA27,Class_2!AA27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="62" spans="2:46" x14ac:dyDescent="0.35">
+      <c r="B62" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C62">
+        <f t="shared" si="7"/>
+        <v>26</v>
+      </c>
+      <c r="D62" t="str">
+        <f>IF(MIN(Class_0!B28,Class_1!B28,Class_2!B28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E62" t="str">
+        <f>IF(MIN(Class_0!C28,Class_1!C28,Class_2!C28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F62" t="str">
+        <f>IF(MIN(Class_0!D28,Class_1!D28,Class_2!D28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G62" t="str">
+        <f>IF(MIN(Class_0!E28,Class_1!E28,Class_2!E28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H62" t="str">
+        <f>IF(MIN(Class_0!F28,Class_1!F28,Class_2!F28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I62" t="str">
+        <f>IF(MIN(Class_0!G28,Class_1!G28,Class_2!G28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J62" t="str">
+        <f>IF(MIN(Class_0!H28,Class_1!H28,Class_2!H28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K62" t="str">
+        <f>IF(MIN(Class_0!I28,Class_1!I28,Class_2!I28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L62" t="str">
+        <f>IF(MIN(Class_0!J28,Class_1!J28,Class_2!J28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M62" t="str">
+        <f>IF(MIN(Class_0!K28,Class_1!K28,Class_2!K28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N62" t="str">
+        <f>IF(MIN(Class_0!L28,Class_1!L28,Class_2!L28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="O62" t="str">
+        <f>IF(MIN(Class_0!M28,Class_1!M28,Class_2!M28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="P62" t="str">
+        <f>IF(MIN(Class_0!N28,Class_1!N28,Class_2!N28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q62" t="str">
+        <f>IF(MIN(Class_0!O28,Class_1!O28,Class_2!O28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R62" t="str">
+        <f>IF(MIN(Class_0!P28,Class_1!P28,Class_2!P28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S62" t="str">
+        <f>IF(MIN(Class_0!Q28,Class_1!Q28,Class_2!Q28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T62" t="str">
+        <f>IF(MIN(Class_0!R28,Class_1!R28,Class_2!R28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U62" t="str">
+        <f>IF(MIN(Class_0!S28,Class_1!S28,Class_2!S28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V62" t="str">
+        <f>IF(MIN(Class_0!T28,Class_1!T28,Class_2!T28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W62" t="str">
+        <f>IF(MIN(Class_0!U28,Class_1!U28,Class_2!U28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X62" t="str">
+        <f>IF(MIN(Class_0!V28,Class_1!V28,Class_2!V28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y62" t="str">
+        <f>IF(MIN(Class_0!W28,Class_1!W28,Class_2!W28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z62" t="str">
+        <f>IF(MIN(Class_0!X28,Class_1!X28,Class_2!X28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA62" t="str">
+        <f>IF(MIN(Class_0!Y28,Class_1!Y28,Class_2!Y28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB62" t="str">
+        <f>IF(MIN(Class_0!Z28,Class_1!Z28,Class_2!Z28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC62" t="str">
+        <f>IF(MIN(Class_0!AA28,Class_1!AA28,Class_2!AA28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD62" t="str">
+        <f>IF(MIN(Class_0!AB28,Class_1!AB28,Class_2!AB28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="63" spans="2:46" x14ac:dyDescent="0.35">
+      <c r="B63" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C63">
+        <f t="shared" si="7"/>
+        <v>27</v>
+      </c>
+      <c r="D63" t="str">
+        <f>IF(MIN(Class_0!B29,Class_1!B29,Class_2!B29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E63" t="str">
+        <f>IF(MIN(Class_0!C29,Class_1!C29,Class_2!C29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F63" t="str">
+        <f>IF(MIN(Class_0!D29,Class_1!D29,Class_2!D29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G63" t="str">
+        <f>IF(MIN(Class_0!E29,Class_1!E29,Class_2!E29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H63" t="str">
+        <f>IF(MIN(Class_0!F29,Class_1!F29,Class_2!F29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I63" t="str">
+        <f>IF(MIN(Class_0!G29,Class_1!G29,Class_2!G29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J63" t="str">
+        <f>IF(MIN(Class_0!H29,Class_1!H29,Class_2!H29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="K63" t="str">
+        <f>IF(MIN(Class_0!I29,Class_1!I29,Class_2!I29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="L63" t="str">
+        <f>IF(MIN(Class_0!J29,Class_1!J29,Class_2!J29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M63" t="str">
+        <f>IF(MIN(Class_0!K29,Class_1!K29,Class_2!K29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N63" t="str">
+        <f>IF(MIN(Class_0!L29,Class_1!L29,Class_2!L29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O63" t="str">
+        <f>IF(MIN(Class_0!M29,Class_1!M29,Class_2!M29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P63" t="str">
+        <f>IF(MIN(Class_0!N29,Class_1!N29,Class_2!N29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q63" t="str">
+        <f>IF(MIN(Class_0!O29,Class_1!O29,Class_2!O29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R63" t="str">
+        <f>IF(MIN(Class_0!P29,Class_1!P29,Class_2!P29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S63" t="str">
+        <f>IF(MIN(Class_0!Q29,Class_1!Q29,Class_2!Q29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T63" t="str">
+        <f>IF(MIN(Class_0!R29,Class_1!R29,Class_2!R29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U63" t="str">
+        <f>IF(MIN(Class_0!S29,Class_1!S29,Class_2!S29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V63" t="str">
+        <f>IF(MIN(Class_0!T29,Class_1!T29,Class_2!T29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W63" t="str">
+        <f>IF(MIN(Class_0!U29,Class_1!U29,Class_2!U29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X63" t="str">
+        <f>IF(MIN(Class_0!V29,Class_1!V29,Class_2!V29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y63" t="str">
+        <f>IF(MIN(Class_0!W29,Class_1!W29,Class_2!W29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z63" t="str">
+        <f>IF(MIN(Class_0!X29,Class_1!X29,Class_2!X29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA63" t="str">
+        <f>IF(MIN(Class_0!Y29,Class_1!Y29,Class_2!Y29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB63" t="str">
+        <f>IF(MIN(Class_0!Z29,Class_1!Z29,Class_2!Z29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC63" t="str">
+        <f>IF(MIN(Class_0!AA29,Class_1!AA29,Class_2!AA29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD63" t="str">
+        <f>IF(MIN(Class_0!AB29,Class_1!AB29,Class_2!AB29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE63" t="str">
+        <f>IF(MIN(Class_0!AC29,Class_1!AC29,Class_2!AC29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="64" spans="2:46" x14ac:dyDescent="0.35">
+      <c r="B64" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C64">
+        <f t="shared" si="7"/>
+        <v>28</v>
+      </c>
+      <c r="D64" t="str">
+        <f>IF(MIN(Class_0!B30,Class_1!B30,Class_2!B30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E64" t="str">
+        <f>IF(MIN(Class_0!C30,Class_1!C30,Class_2!C30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F64" t="str">
+        <f>IF(MIN(Class_0!D30,Class_1!D30,Class_2!D30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G64" t="str">
+        <f>IF(MIN(Class_0!E30,Class_1!E30,Class_2!E30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H64" t="str">
+        <f>IF(MIN(Class_0!F30,Class_1!F30,Class_2!F30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I64" t="str">
+        <f>IF(MIN(Class_0!G30,Class_1!G30,Class_2!G30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J64" t="str">
+        <f>IF(MIN(Class_0!H30,Class_1!H30,Class_2!H30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="K64" t="str">
+        <f>IF(MIN(Class_0!I30,Class_1!I30,Class_2!I30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="L64" t="str">
+        <f>IF(MIN(Class_0!J30,Class_1!J30,Class_2!J30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M64" t="str">
+        <f>IF(MIN(Class_0!K30,Class_1!K30,Class_2!K30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N64" t="str">
+        <f>IF(MIN(Class_0!L30,Class_1!L30,Class_2!L30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O64" t="str">
+        <f>IF(MIN(Class_0!M30,Class_1!M30,Class_2!M30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P64" t="str">
+        <f>IF(MIN(Class_0!N30,Class_1!N30,Class_2!N30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q64" t="str">
+        <f>IF(MIN(Class_0!O30,Class_1!O30,Class_2!O30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R64" t="str">
+        <f>IF(MIN(Class_0!P30,Class_1!P30,Class_2!P30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S64" t="str">
+        <f>IF(MIN(Class_0!Q30,Class_1!Q30,Class_2!Q30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T64" t="str">
+        <f>IF(MIN(Class_0!R30,Class_1!R30,Class_2!R30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U64" t="str">
+        <f>IF(MIN(Class_0!S30,Class_1!S30,Class_2!S30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V64" t="str">
+        <f>IF(MIN(Class_0!T30,Class_1!T30,Class_2!T30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="W64" t="str">
+        <f>IF(MIN(Class_0!U30,Class_1!U30,Class_2!U30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="X64" t="str">
+        <f>IF(MIN(Class_0!V30,Class_1!V30,Class_2!V30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y64" t="str">
+        <f>IF(MIN(Class_0!W30,Class_1!W30,Class_2!W30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z64" t="str">
+        <f>IF(MIN(Class_0!X30,Class_1!X30,Class_2!X30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA64" t="str">
+        <f>IF(MIN(Class_0!Y30,Class_1!Y30,Class_2!Y30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB64" t="str">
+        <f>IF(MIN(Class_0!Z30,Class_1!Z30,Class_2!Z30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC64" t="str">
+        <f>IF(MIN(Class_0!AA30,Class_1!AA30,Class_2!AA30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD64" t="str">
+        <f>IF(MIN(Class_0!AB30,Class_1!AB30,Class_2!AB30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE64" t="str">
+        <f>IF(MIN(Class_0!AC30,Class_1!AC30,Class_2!AC30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF64" t="str">
+        <f>IF(MIN(Class_0!AD30,Class_1!AD30,Class_2!AD30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="65" spans="2:48" x14ac:dyDescent="0.35">
+      <c r="B65" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C65">
+        <f t="shared" si="7"/>
+        <v>29</v>
+      </c>
+      <c r="D65" t="str">
+        <f>IF(MIN(Class_0!B31,Class_1!B31,Class_2!B31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E65" t="str">
+        <f>IF(MIN(Class_0!C31,Class_1!C31,Class_2!C31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F65" t="str">
+        <f>IF(MIN(Class_0!D31,Class_1!D31,Class_2!D31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G65" t="str">
+        <f>IF(MIN(Class_0!E31,Class_1!E31,Class_2!E31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H65" t="str">
+        <f>IF(MIN(Class_0!F31,Class_1!F31,Class_2!F31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I65" t="str">
+        <f>IF(MIN(Class_0!G31,Class_1!G31,Class_2!G31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J65" t="str">
+        <f>IF(MIN(Class_0!H31,Class_1!H31,Class_2!H31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="K65" t="str">
+        <f>IF(MIN(Class_0!I31,Class_1!I31,Class_2!I31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L65" t="str">
+        <f>IF(MIN(Class_0!J31,Class_1!J31,Class_2!J31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M65" t="str">
+        <f>IF(MIN(Class_0!K31,Class_1!K31,Class_2!K31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N65" t="str">
+        <f>IF(MIN(Class_0!L31,Class_1!L31,Class_2!L31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O65" t="str">
+        <f>IF(MIN(Class_0!M31,Class_1!M31,Class_2!M31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P65" t="str">
+        <f>IF(MIN(Class_0!N31,Class_1!N31,Class_2!N31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q65" t="str">
+        <f>IF(MIN(Class_0!O31,Class_1!O31,Class_2!O31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R65" t="str">
+        <f>IF(MIN(Class_0!P31,Class_1!P31,Class_2!P31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S65" t="str">
+        <f>IF(MIN(Class_0!Q31,Class_1!Q31,Class_2!Q31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T65" t="str">
+        <f>IF(MIN(Class_0!R31,Class_1!R31,Class_2!R31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U65" t="str">
+        <f>IF(MIN(Class_0!S31,Class_1!S31,Class_2!S31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V65" t="str">
+        <f>IF(MIN(Class_0!T31,Class_1!T31,Class_2!T31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W65" t="str">
+        <f>IF(MIN(Class_0!U31,Class_1!U31,Class_2!U31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X65" t="str">
+        <f>IF(MIN(Class_0!V31,Class_1!V31,Class_2!V31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y65" t="str">
+        <f>IF(MIN(Class_0!W31,Class_1!W31,Class_2!W31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z65" t="str">
+        <f>IF(MIN(Class_0!X31,Class_1!X31,Class_2!X31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA65" t="str">
+        <f>IF(MIN(Class_0!Y31,Class_1!Y31,Class_2!Y31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB65" t="str">
+        <f>IF(MIN(Class_0!Z31,Class_1!Z31,Class_2!Z31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC65" t="str">
+        <f>IF(MIN(Class_0!AA31,Class_1!AA31,Class_2!AA31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD65" t="str">
+        <f>IF(MIN(Class_0!AB31,Class_1!AB31,Class_2!AB31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE65" t="str">
+        <f>IF(MIN(Class_0!AC31,Class_1!AC31,Class_2!AC31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF65" t="str">
+        <f>IF(MIN(Class_0!AD31,Class_1!AD31,Class_2!AD31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG65" t="str">
+        <f>IF(MIN(Class_0!AE31,Class_1!AE31,Class_2!AE31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="66" spans="2:48" x14ac:dyDescent="0.35">
+      <c r="B66" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C66">
+        <f t="shared" si="7"/>
+        <v>30</v>
+      </c>
+      <c r="D66" t="str">
+        <f>IF(MIN(Class_0!B32,Class_1!B32,Class_2!B32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E66" t="str">
+        <f>IF(MIN(Class_0!C32,Class_1!C32,Class_2!C32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F66" t="str">
+        <f>IF(MIN(Class_0!D32,Class_1!D32,Class_2!D32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G66" t="str">
+        <f>IF(MIN(Class_0!E32,Class_1!E32,Class_2!E32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H66" t="str">
+        <f>IF(MIN(Class_0!F32,Class_1!F32,Class_2!F32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I66" t="str">
+        <f>IF(MIN(Class_0!G32,Class_1!G32,Class_2!G32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J66" t="str">
+        <f>IF(MIN(Class_0!H32,Class_1!H32,Class_2!H32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K66" t="str">
+        <f>IF(MIN(Class_0!I32,Class_1!I32,Class_2!I32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="L66" t="str">
+        <f>IF(MIN(Class_0!J32,Class_1!J32,Class_2!J32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M66" t="str">
+        <f>IF(MIN(Class_0!K32,Class_1!K32,Class_2!K32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N66" t="str">
+        <f>IF(MIN(Class_0!L32,Class_1!L32,Class_2!L32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O66" t="str">
+        <f>IF(MIN(Class_0!M32,Class_1!M32,Class_2!M32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P66" t="str">
+        <f>IF(MIN(Class_0!N32,Class_1!N32,Class_2!N32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q66" t="str">
+        <f>IF(MIN(Class_0!O32,Class_1!O32,Class_2!O32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R66" t="str">
+        <f>IF(MIN(Class_0!P32,Class_1!P32,Class_2!P32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S66" t="str">
+        <f>IF(MIN(Class_0!Q32,Class_1!Q32,Class_2!Q32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T66" t="str">
+        <f>IF(MIN(Class_0!R32,Class_1!R32,Class_2!R32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U66" t="str">
+        <f>IF(MIN(Class_0!S32,Class_1!S32,Class_2!S32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V66" t="str">
+        <f>IF(MIN(Class_0!T32,Class_1!T32,Class_2!T32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W66" t="str">
+        <f>IF(MIN(Class_0!U32,Class_1!U32,Class_2!U32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X66" t="str">
+        <f>IF(MIN(Class_0!V32,Class_1!V32,Class_2!V32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y66" t="str">
+        <f>IF(MIN(Class_0!W32,Class_1!W32,Class_2!W32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z66" t="str">
+        <f>IF(MIN(Class_0!X32,Class_1!X32,Class_2!X32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA66" t="str">
+        <f>IF(MIN(Class_0!Y32,Class_1!Y32,Class_2!Y32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB66" t="str">
+        <f>IF(MIN(Class_0!Z32,Class_1!Z32,Class_2!Z32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC66" t="str">
+        <f>IF(MIN(Class_0!AA32,Class_1!AA32,Class_2!AA32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD66" t="str">
+        <f>IF(MIN(Class_0!AB32,Class_1!AB32,Class_2!AB32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE66" t="str">
+        <f>IF(MIN(Class_0!AC32,Class_1!AC32,Class_2!AC32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF66" t="str">
+        <f>IF(MIN(Class_0!AD32,Class_1!AD32,Class_2!AD32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG66" t="str">
+        <f>IF(MIN(Class_0!AE32,Class_1!AE32,Class_2!AE32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH66" t="str">
+        <f>IF(MIN(Class_0!AF32,Class_1!AF32,Class_2!AF32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="67" spans="2:48" x14ac:dyDescent="0.35">
+      <c r="B67" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67">
+        <f t="shared" si="7"/>
+        <v>31</v>
+      </c>
+      <c r="D67" t="str">
+        <f>IF(MIN(Class_0!B33,Class_1!B33,Class_2!B33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E67" t="str">
+        <f>IF(MIN(Class_0!C33,Class_1!C33,Class_2!C33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F67" t="str">
+        <f>IF(MIN(Class_0!D33,Class_1!D33,Class_2!D33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G67" t="str">
+        <f>IF(MIN(Class_0!E33,Class_1!E33,Class_2!E33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H67" t="str">
+        <f>IF(MIN(Class_0!F33,Class_1!F33,Class_2!F33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I67" t="str">
+        <f>IF(MIN(Class_0!G33,Class_1!G33,Class_2!G33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J67" t="str">
+        <f>IF(MIN(Class_0!H33,Class_1!H33,Class_2!H33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K67" t="str">
+        <f>IF(MIN(Class_0!I33,Class_1!I33,Class_2!I33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L67" t="str">
+        <f>IF(MIN(Class_0!J33,Class_1!J33,Class_2!J33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M67" t="str">
+        <f>IF(MIN(Class_0!K33,Class_1!K33,Class_2!K33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N67" t="str">
+        <f>IF(MIN(Class_0!L33,Class_1!L33,Class_2!L33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O67" t="str">
+        <f>IF(MIN(Class_0!M33,Class_1!M33,Class_2!M33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P67" t="str">
+        <f>IF(MIN(Class_0!N33,Class_1!N33,Class_2!N33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q67" t="str">
+        <f>IF(MIN(Class_0!O33,Class_1!O33,Class_2!O33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R67" t="str">
+        <f>IF(MIN(Class_0!P33,Class_1!P33,Class_2!P33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S67" t="str">
+        <f>IF(MIN(Class_0!Q33,Class_1!Q33,Class_2!Q33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T67" t="str">
+        <f>IF(MIN(Class_0!R33,Class_1!R33,Class_2!R33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U67" t="str">
+        <f>IF(MIN(Class_0!S33,Class_1!S33,Class_2!S33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V67" t="str">
+        <f>IF(MIN(Class_0!T33,Class_1!T33,Class_2!T33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W67" t="str">
+        <f>IF(MIN(Class_0!U33,Class_1!U33,Class_2!U33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="X67" t="str">
+        <f>IF(MIN(Class_0!V33,Class_1!V33,Class_2!V33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y67" t="str">
+        <f>IF(MIN(Class_0!W33,Class_1!W33,Class_2!W33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z67" t="str">
+        <f>IF(MIN(Class_0!X33,Class_1!X33,Class_2!X33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA67" t="str">
+        <f>IF(MIN(Class_0!Y33,Class_1!Y33,Class_2!Y33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB67" t="str">
+        <f>IF(MIN(Class_0!Z33,Class_1!Z33,Class_2!Z33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC67" t="str">
+        <f>IF(MIN(Class_0!AA33,Class_1!AA33,Class_2!AA33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD67" t="str">
+        <f>IF(MIN(Class_0!AB33,Class_1!AB33,Class_2!AB33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE67" t="str">
+        <f>IF(MIN(Class_0!AC33,Class_1!AC33,Class_2!AC33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF67" t="str">
+        <f>IF(MIN(Class_0!AD33,Class_1!AD33,Class_2!AD33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG67" t="str">
+        <f>IF(MIN(Class_0!AE33,Class_1!AE33,Class_2!AE33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH67" t="str">
+        <f>IF(MIN(Class_0!AF33,Class_1!AF33,Class_2!AF33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI67" t="str">
+        <f>IF(MIN(Class_0!AG33,Class_1!AG33,Class_2!AG33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="68" spans="2:48" x14ac:dyDescent="0.35">
+      <c r="B68" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C68">
+        <f t="shared" si="7"/>
+        <v>32</v>
+      </c>
+      <c r="D68" t="str">
+        <f>IF(MIN(Class_0!B34,Class_1!B34,Class_2!B34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E68" t="str">
+        <f>IF(MIN(Class_0!C34,Class_1!C34,Class_2!C34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F68" t="str">
+        <f>IF(MIN(Class_0!D34,Class_1!D34,Class_2!D34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G68" t="str">
+        <f>IF(MIN(Class_0!E34,Class_1!E34,Class_2!E34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H68" t="str">
+        <f>IF(MIN(Class_0!F34,Class_1!F34,Class_2!F34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I68" t="str">
+        <f>IF(MIN(Class_0!G34,Class_1!G34,Class_2!G34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J68" t="str">
+        <f>IF(MIN(Class_0!H34,Class_1!H34,Class_2!H34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K68" t="str">
+        <f>IF(MIN(Class_0!I34,Class_1!I34,Class_2!I34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L68" t="str">
+        <f>IF(MIN(Class_0!J34,Class_1!J34,Class_2!J34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M68" t="str">
+        <f>IF(MIN(Class_0!K34,Class_1!K34,Class_2!K34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N68" t="str">
+        <f>IF(MIN(Class_0!L34,Class_1!L34,Class_2!L34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O68" t="str">
+        <f>IF(MIN(Class_0!M34,Class_1!M34,Class_2!M34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P68" t="str">
+        <f>IF(MIN(Class_0!N34,Class_1!N34,Class_2!N34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q68" t="str">
+        <f>IF(MIN(Class_0!O34,Class_1!O34,Class_2!O34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R68" t="str">
+        <f>IF(MIN(Class_0!P34,Class_1!P34,Class_2!P34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S68" t="str">
+        <f>IF(MIN(Class_0!Q34,Class_1!Q34,Class_2!Q34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T68" t="str">
+        <f>IF(MIN(Class_0!R34,Class_1!R34,Class_2!R34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U68" t="str">
+        <f>IF(MIN(Class_0!S34,Class_1!S34,Class_2!S34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="V68" t="str">
+        <f>IF(MIN(Class_0!T34,Class_1!T34,Class_2!T34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W68" t="str">
+        <f>IF(MIN(Class_0!U34,Class_1!U34,Class_2!U34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X68" t="str">
+        <f>IF(MIN(Class_0!V34,Class_1!V34,Class_2!V34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y68" t="str">
+        <f>IF(MIN(Class_0!W34,Class_1!W34,Class_2!W34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z68" t="str">
+        <f>IF(MIN(Class_0!X34,Class_1!X34,Class_2!X34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA68" t="str">
+        <f>IF(MIN(Class_0!Y34,Class_1!Y34,Class_2!Y34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB68" t="str">
+        <f>IF(MIN(Class_0!Z34,Class_1!Z34,Class_2!Z34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC68" t="str">
+        <f>IF(MIN(Class_0!AA34,Class_1!AA34,Class_2!AA34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD68" t="str">
+        <f>IF(MIN(Class_0!AB34,Class_1!AB34,Class_2!AB34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE68" t="str">
+        <f>IF(MIN(Class_0!AC34,Class_1!AC34,Class_2!AC34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF68" t="str">
+        <f>IF(MIN(Class_0!AD34,Class_1!AD34,Class_2!AD34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG68" t="str">
+        <f>IF(MIN(Class_0!AE34,Class_1!AE34,Class_2!AE34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH68" t="str">
+        <f>IF(MIN(Class_0!AF34,Class_1!AF34,Class_2!AF34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI68" t="str">
+        <f>IF(MIN(Class_0!AG34,Class_1!AG34,Class_2!AG34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ68" t="str">
+        <f>IF(MIN(Class_0!AH34,Class_1!AH34,Class_2!AH34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="69" spans="2:48" x14ac:dyDescent="0.35">
+      <c r="B69" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C69">
+        <f t="shared" si="7"/>
+        <v>33</v>
+      </c>
+      <c r="D69" t="str">
+        <f>IF(MIN(Class_0!B35,Class_1!B35,Class_2!B35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E69" t="str">
+        <f>IF(MIN(Class_0!C35,Class_1!C35,Class_2!C35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F69" t="str">
+        <f>IF(MIN(Class_0!D35,Class_1!D35,Class_2!D35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G69" t="str">
+        <f>IF(MIN(Class_0!E35,Class_1!E35,Class_2!E35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H69" t="str">
+        <f>IF(MIN(Class_0!F35,Class_1!F35,Class_2!F35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I69" t="str">
+        <f>IF(MIN(Class_0!G35,Class_1!G35,Class_2!G35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J69" t="str">
+        <f>IF(MIN(Class_0!H35,Class_1!H35,Class_2!H35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K69" t="str">
+        <f>IF(MIN(Class_0!I35,Class_1!I35,Class_2!I35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L69" t="str">
+        <f>IF(MIN(Class_0!J35,Class_1!J35,Class_2!J35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M69" t="str">
+        <f>IF(MIN(Class_0!K35,Class_1!K35,Class_2!K35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N69" t="str">
+        <f>IF(MIN(Class_0!L35,Class_1!L35,Class_2!L35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O69" t="str">
+        <f>IF(MIN(Class_0!M35,Class_1!M35,Class_2!M35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P69" t="str">
+        <f>IF(MIN(Class_0!N35,Class_1!N35,Class_2!N35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Q69" t="str">
+        <f>IF(MIN(Class_0!O35,Class_1!O35,Class_2!O35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R69" t="str">
+        <f>IF(MIN(Class_0!P35,Class_1!P35,Class_2!P35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S69" t="str">
+        <f>IF(MIN(Class_0!Q35,Class_1!Q35,Class_2!Q35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T69" t="str">
+        <f>IF(MIN(Class_0!R35,Class_1!R35,Class_2!R35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U69" t="str">
+        <f>IF(MIN(Class_0!S35,Class_1!S35,Class_2!S35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V69" t="str">
+        <f>IF(MIN(Class_0!T35,Class_1!T35,Class_2!T35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="W69" t="str">
+        <f>IF(MIN(Class_0!U35,Class_1!U35,Class_2!U35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="X69" t="str">
+        <f>IF(MIN(Class_0!V35,Class_1!V35,Class_2!V35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Y69" t="str">
+        <f>IF(MIN(Class_0!W35,Class_1!W35,Class_2!W35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z69" t="str">
+        <f>IF(MIN(Class_0!X35,Class_1!X35,Class_2!X35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA69" t="str">
+        <f>IF(MIN(Class_0!Y35,Class_1!Y35,Class_2!Y35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB69" t="str">
+        <f>IF(MIN(Class_0!Z35,Class_1!Z35,Class_2!Z35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC69" t="str">
+        <f>IF(MIN(Class_0!AA35,Class_1!AA35,Class_2!AA35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD69" t="str">
+        <f>IF(MIN(Class_0!AB35,Class_1!AB35,Class_2!AB35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE69" t="str">
+        <f>IF(MIN(Class_0!AC35,Class_1!AC35,Class_2!AC35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF69" t="str">
+        <f>IF(MIN(Class_0!AD35,Class_1!AD35,Class_2!AD35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG69" t="str">
+        <f>IF(MIN(Class_0!AE35,Class_1!AE35,Class_2!AE35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH69" t="str">
+        <f>IF(MIN(Class_0!AF35,Class_1!AF35,Class_2!AF35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI69" t="str">
+        <f>IF(MIN(Class_0!AG35,Class_1!AG35,Class_2!AG35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ69" t="str">
+        <f>IF(MIN(Class_0!AH35,Class_1!AH35,Class_2!AH35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK69" t="str">
+        <f>IF(MIN(Class_0!AI35,Class_1!AI35,Class_2!AI35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="70" spans="2:48" x14ac:dyDescent="0.35">
+      <c r="B70" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C70">
+        <f t="shared" si="7"/>
+        <v>34</v>
+      </c>
+      <c r="D70" t="str">
+        <f>IF(MIN(Class_0!B36,Class_1!B36,Class_2!B36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E70" t="str">
+        <f>IF(MIN(Class_0!C36,Class_1!C36,Class_2!C36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F70" t="str">
+        <f>IF(MIN(Class_0!D36,Class_1!D36,Class_2!D36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G70" t="str">
+        <f>IF(MIN(Class_0!E36,Class_1!E36,Class_2!E36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H70" t="str">
+        <f>IF(MIN(Class_0!F36,Class_1!F36,Class_2!F36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I70" t="str">
+        <f>IF(MIN(Class_0!G36,Class_1!G36,Class_2!G36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J70" t="str">
+        <f>IF(MIN(Class_0!H36,Class_1!H36,Class_2!H36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="K70" t="str">
+        <f>IF(MIN(Class_0!I36,Class_1!I36,Class_2!I36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L70" t="str">
+        <f>IF(MIN(Class_0!J36,Class_1!J36,Class_2!J36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M70" t="str">
+        <f>IF(MIN(Class_0!K36,Class_1!K36,Class_2!K36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N70" t="str">
+        <f>IF(MIN(Class_0!L36,Class_1!L36,Class_2!L36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O70" t="str">
+        <f>IF(MIN(Class_0!M36,Class_1!M36,Class_2!M36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P70" t="str">
+        <f>IF(MIN(Class_0!N36,Class_1!N36,Class_2!N36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q70" t="str">
+        <f>IF(MIN(Class_0!O36,Class_1!O36,Class_2!O36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R70" t="str">
+        <f>IF(MIN(Class_0!P36,Class_1!P36,Class_2!P36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S70" t="str">
+        <f>IF(MIN(Class_0!Q36,Class_1!Q36,Class_2!Q36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T70" t="str">
+        <f>IF(MIN(Class_0!R36,Class_1!R36,Class_2!R36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U70" t="str">
+        <f>IF(MIN(Class_0!S36,Class_1!S36,Class_2!S36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V70" t="str">
+        <f>IF(MIN(Class_0!T36,Class_1!T36,Class_2!T36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="W70" t="str">
+        <f>IF(MIN(Class_0!U36,Class_1!U36,Class_2!U36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="X70" t="str">
+        <f>IF(MIN(Class_0!V36,Class_1!V36,Class_2!V36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Y70" t="str">
+        <f>IF(MIN(Class_0!W36,Class_1!W36,Class_2!W36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z70" t="str">
+        <f>IF(MIN(Class_0!X36,Class_1!X36,Class_2!X36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA70" t="str">
+        <f>IF(MIN(Class_0!Y36,Class_1!Y36,Class_2!Y36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB70" t="str">
+        <f>IF(MIN(Class_0!Z36,Class_1!Z36,Class_2!Z36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC70" t="str">
+        <f>IF(MIN(Class_0!AA36,Class_1!AA36,Class_2!AA36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD70" t="str">
+        <f>IF(MIN(Class_0!AB36,Class_1!AB36,Class_2!AB36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE70" t="str">
+        <f>IF(MIN(Class_0!AC36,Class_1!AC36,Class_2!AC36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF70" t="str">
+        <f>IF(MIN(Class_0!AD36,Class_1!AD36,Class_2!AD36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG70" t="str">
+        <f>IF(MIN(Class_0!AE36,Class_1!AE36,Class_2!AE36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH70" t="str">
+        <f>IF(MIN(Class_0!AF36,Class_1!AF36,Class_2!AF36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI70" t="str">
+        <f>IF(MIN(Class_0!AG36,Class_1!AG36,Class_2!AG36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ70" t="str">
+        <f>IF(MIN(Class_0!AH36,Class_1!AH36,Class_2!AH36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AK70" t="str">
+        <f>IF(MIN(Class_0!AI36,Class_1!AI36,Class_2!AI36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL70" t="str">
+        <f>IF(MIN(Class_0!AJ36,Class_1!AJ36,Class_2!AJ36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="71" spans="2:48" x14ac:dyDescent="0.35">
+      <c r="B71" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C71">
+        <f t="shared" si="7"/>
+        <v>35</v>
+      </c>
+      <c r="D71" t="str">
+        <f>IF(MIN(Class_0!B37,Class_1!B37,Class_2!B37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E71" t="str">
+        <f>IF(MIN(Class_0!C37,Class_1!C37,Class_2!C37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F71" t="str">
+        <f>IF(MIN(Class_0!D37,Class_1!D37,Class_2!D37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G71" t="str">
+        <f>IF(MIN(Class_0!E37,Class_1!E37,Class_2!E37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H71" t="str">
+        <f>IF(MIN(Class_0!F37,Class_1!F37,Class_2!F37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I71" t="str">
+        <f>IF(MIN(Class_0!G37,Class_1!G37,Class_2!G37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J71" t="str">
+        <f>IF(MIN(Class_0!H37,Class_1!H37,Class_2!H37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="K71" t="str">
+        <f>IF(MIN(Class_0!I37,Class_1!I37,Class_2!I37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="L71" t="str">
+        <f>IF(MIN(Class_0!J37,Class_1!J37,Class_2!J37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M71" t="str">
+        <f>IF(MIN(Class_0!K37,Class_1!K37,Class_2!K37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N71" t="str">
+        <f>IF(MIN(Class_0!L37,Class_1!L37,Class_2!L37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O71" t="str">
+        <f>IF(MIN(Class_0!M37,Class_1!M37,Class_2!M37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P71" t="str">
+        <f>IF(MIN(Class_0!N37,Class_1!N37,Class_2!N37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Q71" t="str">
+        <f>IF(MIN(Class_0!O37,Class_1!O37,Class_2!O37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R71" t="str">
+        <f>IF(MIN(Class_0!P37,Class_1!P37,Class_2!P37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S71" t="str">
+        <f>IF(MIN(Class_0!Q37,Class_1!Q37,Class_2!Q37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T71" t="str">
+        <f>IF(MIN(Class_0!R37,Class_1!R37,Class_2!R37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U71" t="str">
+        <f>IF(MIN(Class_0!S37,Class_1!S37,Class_2!S37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V71" t="str">
+        <f>IF(MIN(Class_0!T37,Class_1!T37,Class_2!T37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W71" t="str">
+        <f>IF(MIN(Class_0!U37,Class_1!U37,Class_2!U37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X71" t="str">
+        <f>IF(MIN(Class_0!V37,Class_1!V37,Class_2!V37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y71" t="str">
+        <f>IF(MIN(Class_0!W37,Class_1!W37,Class_2!W37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Z71" t="str">
+        <f>IF(MIN(Class_0!X37,Class_1!X37,Class_2!X37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA71" t="str">
+        <f>IF(MIN(Class_0!Y37,Class_1!Y37,Class_2!Y37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB71" t="str">
+        <f>IF(MIN(Class_0!Z37,Class_1!Z37,Class_2!Z37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC71" t="str">
+        <f>IF(MIN(Class_0!AA37,Class_1!AA37,Class_2!AA37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD71" t="str">
+        <f>IF(MIN(Class_0!AB37,Class_1!AB37,Class_2!AB37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE71" t="str">
+        <f>IF(MIN(Class_0!AC37,Class_1!AC37,Class_2!AC37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF71" t="str">
+        <f>IF(MIN(Class_0!AD37,Class_1!AD37,Class_2!AD37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG71" t="str">
+        <f>IF(MIN(Class_0!AE37,Class_1!AE37,Class_2!AE37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH71" t="str">
+        <f>IF(MIN(Class_0!AF37,Class_1!AF37,Class_2!AF37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI71" t="str">
+        <f>IF(MIN(Class_0!AG37,Class_1!AG37,Class_2!AG37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ71" t="str">
+        <f>IF(MIN(Class_0!AH37,Class_1!AH37,Class_2!AH37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AK71" t="str">
+        <f>IF(MIN(Class_0!AI37,Class_1!AI37,Class_2!AI37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL71" t="str">
+        <f>IF(MIN(Class_0!AJ37,Class_1!AJ37,Class_2!AJ37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM71" t="str">
+        <f>IF(MIN(Class_0!AK37,Class_1!AK37,Class_2!AK37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="72" spans="2:48" x14ac:dyDescent="0.35">
+      <c r="B72" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C72">
+        <f t="shared" si="7"/>
+        <v>36</v>
+      </c>
+      <c r="D72" t="str">
+        <f>IF(MIN(Class_0!B38,Class_1!B38,Class_2!B38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E72" t="str">
+        <f>IF(MIN(Class_0!C38,Class_1!C38,Class_2!C38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F72" t="str">
+        <f>IF(MIN(Class_0!D38,Class_1!D38,Class_2!D38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G72" t="str">
+        <f>IF(MIN(Class_0!E38,Class_1!E38,Class_2!E38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H72" t="str">
+        <f>IF(MIN(Class_0!F38,Class_1!F38,Class_2!F38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="I72" t="str">
+        <f>IF(MIN(Class_0!G38,Class_1!G38,Class_2!G38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J72" t="str">
+        <f>IF(MIN(Class_0!H38,Class_1!H38,Class_2!H38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K72" t="str">
+        <f>IF(MIN(Class_0!I38,Class_1!I38,Class_2!I38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L72" t="str">
+        <f>IF(MIN(Class_0!J38,Class_1!J38,Class_2!J38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M72" t="str">
+        <f>IF(MIN(Class_0!K38,Class_1!K38,Class_2!K38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N72" t="str">
+        <f>IF(MIN(Class_0!L38,Class_1!L38,Class_2!L38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="O72" t="str">
+        <f>IF(MIN(Class_0!M38,Class_1!M38,Class_2!M38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="P72" t="str">
+        <f>IF(MIN(Class_0!N38,Class_1!N38,Class_2!N38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q72" t="str">
+        <f>IF(MIN(Class_0!O38,Class_1!O38,Class_2!O38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R72" t="str">
+        <f>IF(MIN(Class_0!P38,Class_1!P38,Class_2!P38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S72" t="str">
+        <f>IF(MIN(Class_0!Q38,Class_1!Q38,Class_2!Q38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T72" t="str">
+        <f>IF(MIN(Class_0!R38,Class_1!R38,Class_2!R38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U72" t="str">
+        <f>IF(MIN(Class_0!S38,Class_1!S38,Class_2!S38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V72" t="str">
+        <f>IF(MIN(Class_0!T38,Class_1!T38,Class_2!T38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W72" t="str">
+        <f>IF(MIN(Class_0!U38,Class_1!U38,Class_2!U38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X72" t="str">
+        <f>IF(MIN(Class_0!V38,Class_1!V38,Class_2!V38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y72" t="str">
+        <f>IF(MIN(Class_0!W38,Class_1!W38,Class_2!W38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z72" t="str">
+        <f>IF(MIN(Class_0!X38,Class_1!X38,Class_2!X38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA72" t="str">
+        <f>IF(MIN(Class_0!Y38,Class_1!Y38,Class_2!Y38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB72" t="str">
+        <f>IF(MIN(Class_0!Z38,Class_1!Z38,Class_2!Z38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC72" t="str">
+        <f>IF(MIN(Class_0!AA38,Class_1!AA38,Class_2!AA38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD72" t="str">
+        <f>IF(MIN(Class_0!AB38,Class_1!AB38,Class_2!AB38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE72" t="str">
+        <f>IF(MIN(Class_0!AC38,Class_1!AC38,Class_2!AC38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF72" t="str">
+        <f>IF(MIN(Class_0!AD38,Class_1!AD38,Class_2!AD38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG72" t="str">
+        <f>IF(MIN(Class_0!AE38,Class_1!AE38,Class_2!AE38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH72" t="str">
+        <f>IF(MIN(Class_0!AF38,Class_1!AF38,Class_2!AF38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI72" t="str">
+        <f>IF(MIN(Class_0!AG38,Class_1!AG38,Class_2!AG38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ72" t="str">
+        <f>IF(MIN(Class_0!AH38,Class_1!AH38,Class_2!AH38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AK72" t="str">
+        <f>IF(MIN(Class_0!AI38,Class_1!AI38,Class_2!AI38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL72" t="str">
+        <f>IF(MIN(Class_0!AJ38,Class_1!AJ38,Class_2!AJ38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM72" t="str">
+        <f>IF(MIN(Class_0!AK38,Class_1!AK38,Class_2!AK38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN72" t="str">
+        <f>IF(MIN(Class_0!AL38,Class_1!AL38,Class_2!AL38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="73" spans="2:48" x14ac:dyDescent="0.35">
+      <c r="B73" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C73">
+        <f t="shared" si="7"/>
+        <v>37</v>
+      </c>
+      <c r="D73" t="str">
+        <f>IF(MIN(Class_0!B39,Class_1!B39,Class_2!B39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E73" t="str">
+        <f>IF(MIN(Class_0!C39,Class_1!C39,Class_2!C39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F73" t="str">
+        <f>IF(MIN(Class_0!D39,Class_1!D39,Class_2!D39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G73" t="str">
+        <f>IF(MIN(Class_0!E39,Class_1!E39,Class_2!E39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H73" t="str">
+        <f>IF(MIN(Class_0!F39,Class_1!F39,Class_2!F39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="I73" t="str">
+        <f>IF(MIN(Class_0!G39,Class_1!G39,Class_2!G39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J73" t="str">
+        <f>IF(MIN(Class_0!H39,Class_1!H39,Class_2!H39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K73" t="str">
+        <f>IF(MIN(Class_0!I39,Class_1!I39,Class_2!I39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L73" t="str">
+        <f>IF(MIN(Class_0!J39,Class_1!J39,Class_2!J39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M73" t="str">
+        <f>IF(MIN(Class_0!K39,Class_1!K39,Class_2!K39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N73" t="str">
+        <f>IF(MIN(Class_0!L39,Class_1!L39,Class_2!L39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="O73" t="str">
+        <f>IF(MIN(Class_0!M39,Class_1!M39,Class_2!M39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="P73" t="str">
+        <f>IF(MIN(Class_0!N39,Class_1!N39,Class_2!N39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q73" t="str">
+        <f>IF(MIN(Class_0!O39,Class_1!O39,Class_2!O39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R73" t="str">
+        <f>IF(MIN(Class_0!P39,Class_1!P39,Class_2!P39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S73" t="str">
+        <f>IF(MIN(Class_0!Q39,Class_1!Q39,Class_2!Q39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T73" t="str">
+        <f>IF(MIN(Class_0!R39,Class_1!R39,Class_2!R39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U73" t="str">
+        <f>IF(MIN(Class_0!S39,Class_1!S39,Class_2!S39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V73" t="str">
+        <f>IF(MIN(Class_0!T39,Class_1!T39,Class_2!T39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W73" t="str">
+        <f>IF(MIN(Class_0!U39,Class_1!U39,Class_2!U39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X73" t="str">
+        <f>IF(MIN(Class_0!V39,Class_1!V39,Class_2!V39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y73" t="str">
+        <f>IF(MIN(Class_0!W39,Class_1!W39,Class_2!W39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z73" t="str">
+        <f>IF(MIN(Class_0!X39,Class_1!X39,Class_2!X39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA73" t="str">
+        <f>IF(MIN(Class_0!Y39,Class_1!Y39,Class_2!Y39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB73" t="str">
+        <f>IF(MIN(Class_0!Z39,Class_1!Z39,Class_2!Z39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC73" t="str">
+        <f>IF(MIN(Class_0!AA39,Class_1!AA39,Class_2!AA39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD73" t="str">
+        <f>IF(MIN(Class_0!AB39,Class_1!AB39,Class_2!AB39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE73" t="str">
+        <f>IF(MIN(Class_0!AC39,Class_1!AC39,Class_2!AC39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF73" t="str">
+        <f>IF(MIN(Class_0!AD39,Class_1!AD39,Class_2!AD39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG73" t="str">
+        <f>IF(MIN(Class_0!AE39,Class_1!AE39,Class_2!AE39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH73" t="str">
+        <f>IF(MIN(Class_0!AF39,Class_1!AF39,Class_2!AF39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI73" t="str">
+        <f>IF(MIN(Class_0!AG39,Class_1!AG39,Class_2!AG39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ73" t="str">
+        <f>IF(MIN(Class_0!AH39,Class_1!AH39,Class_2!AH39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK73" t="str">
+        <f>IF(MIN(Class_0!AI39,Class_1!AI39,Class_2!AI39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL73" t="str">
+        <f>IF(MIN(Class_0!AJ39,Class_1!AJ39,Class_2!AJ39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM73" t="str">
+        <f>IF(MIN(Class_0!AK39,Class_1!AK39,Class_2!AK39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN73" t="str">
+        <f>IF(MIN(Class_0!AL39,Class_1!AL39,Class_2!AL39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO73" t="str">
+        <f>IF(MIN(Class_0!AM39,Class_1!AM39,Class_2!AM39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="74" spans="2:48" x14ac:dyDescent="0.35">
+      <c r="B74" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C74">
+        <f t="shared" si="7"/>
+        <v>38</v>
+      </c>
+      <c r="D74" t="str">
+        <f>IF(MIN(Class_0!B40,Class_1!B40,Class_2!B40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="E74" t="str">
+        <f>IF(MIN(Class_0!C40,Class_1!C40,Class_2!C40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F74" t="str">
+        <f>IF(MIN(Class_0!D40,Class_1!D40,Class_2!D40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G74" t="str">
+        <f>IF(MIN(Class_0!E40,Class_1!E40,Class_2!E40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H74" t="str">
+        <f>IF(MIN(Class_0!F40,Class_1!F40,Class_2!F40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I74" t="str">
+        <f>IF(MIN(Class_0!G40,Class_1!G40,Class_2!G40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="J74" t="str">
+        <f>IF(MIN(Class_0!H40,Class_1!H40,Class_2!H40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K74" t="str">
+        <f>IF(MIN(Class_0!I40,Class_1!I40,Class_2!I40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L74" t="str">
+        <f>IF(MIN(Class_0!J40,Class_1!J40,Class_2!J40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M74" t="str">
+        <f>IF(MIN(Class_0!K40,Class_1!K40,Class_2!K40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N74" t="str">
+        <f>IF(MIN(Class_0!L40,Class_1!L40,Class_2!L40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O74" t="str">
+        <f>IF(MIN(Class_0!M40,Class_1!M40,Class_2!M40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P74" t="str">
+        <f>IF(MIN(Class_0!N40,Class_1!N40,Class_2!N40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q74" t="str">
+        <f>IF(MIN(Class_0!O40,Class_1!O40,Class_2!O40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R74" t="str">
+        <f>IF(MIN(Class_0!P40,Class_1!P40,Class_2!P40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S74" t="str">
+        <f>IF(MIN(Class_0!Q40,Class_1!Q40,Class_2!Q40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T74" t="str">
+        <f>IF(MIN(Class_0!R40,Class_1!R40,Class_2!R40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="U74" t="str">
+        <f>IF(MIN(Class_0!S40,Class_1!S40,Class_2!S40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V74" t="str">
+        <f>IF(MIN(Class_0!T40,Class_1!T40,Class_2!T40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W74" t="str">
+        <f>IF(MIN(Class_0!U40,Class_1!U40,Class_2!U40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X74" t="str">
+        <f>IF(MIN(Class_0!V40,Class_1!V40,Class_2!V40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y74" t="str">
+        <f>IF(MIN(Class_0!W40,Class_1!W40,Class_2!W40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z74" t="str">
+        <f>IF(MIN(Class_0!X40,Class_1!X40,Class_2!X40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA74" t="str">
+        <f>IF(MIN(Class_0!Y40,Class_1!Y40,Class_2!Y40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB74" t="str">
+        <f>IF(MIN(Class_0!Z40,Class_1!Z40,Class_2!Z40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC74" t="str">
+        <f>IF(MIN(Class_0!AA40,Class_1!AA40,Class_2!AA40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD74" t="str">
+        <f>IF(MIN(Class_0!AB40,Class_1!AB40,Class_2!AB40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE74" t="str">
+        <f>IF(MIN(Class_0!AC40,Class_1!AC40,Class_2!AC40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF74" t="str">
+        <f>IF(MIN(Class_0!AD40,Class_1!AD40,Class_2!AD40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG74" t="str">
+        <f>IF(MIN(Class_0!AE40,Class_1!AE40,Class_2!AE40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH74" t="str">
+        <f>IF(MIN(Class_0!AF40,Class_1!AF40,Class_2!AF40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI74" t="str">
+        <f>IF(MIN(Class_0!AG40,Class_1!AG40,Class_2!AG40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ74" t="str">
+        <f>IF(MIN(Class_0!AH40,Class_1!AH40,Class_2!AH40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AK74" t="str">
+        <f>IF(MIN(Class_0!AI40,Class_1!AI40,Class_2!AI40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL74" t="str">
+        <f>IF(MIN(Class_0!AJ40,Class_1!AJ40,Class_2!AJ40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM74" t="str">
+        <f>IF(MIN(Class_0!AK40,Class_1!AK40,Class_2!AK40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN74" t="str">
+        <f>IF(MIN(Class_0!AL40,Class_1!AL40,Class_2!AL40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO74" t="str">
+        <f>IF(MIN(Class_0!AM40,Class_1!AM40,Class_2!AM40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AP74" t="str">
+        <f>IF(MIN(Class_0!AN40,Class_1!AN40,Class_2!AN40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="75" spans="2:48" x14ac:dyDescent="0.35">
+      <c r="B75" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C75">
+        <f t="shared" si="7"/>
+        <v>39</v>
+      </c>
+      <c r="D75" t="str">
+        <f>IF(MIN(Class_0!B41,Class_1!B41,Class_2!B41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="E75" t="str">
+        <f>IF(MIN(Class_0!C41,Class_1!C41,Class_2!C41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F75" t="str">
+        <f>IF(MIN(Class_0!D41,Class_1!D41,Class_2!D41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G75" t="str">
+        <f>IF(MIN(Class_0!E41,Class_1!E41,Class_2!E41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H75" t="str">
+        <f>IF(MIN(Class_0!F41,Class_1!F41,Class_2!F41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I75" t="str">
+        <f>IF(MIN(Class_0!G41,Class_1!G41,Class_2!G41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J75" t="str">
+        <f>IF(MIN(Class_0!H41,Class_1!H41,Class_2!H41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K75" t="str">
+        <f>IF(MIN(Class_0!I41,Class_1!I41,Class_2!I41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L75" t="str">
+        <f>IF(MIN(Class_0!J41,Class_1!J41,Class_2!J41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M75" t="str">
+        <f>IF(MIN(Class_0!K41,Class_1!K41,Class_2!K41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N75" t="str">
+        <f>IF(MIN(Class_0!L41,Class_1!L41,Class_2!L41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O75" t="str">
+        <f>IF(MIN(Class_0!M41,Class_1!M41,Class_2!M41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P75" t="str">
+        <f>IF(MIN(Class_0!N41,Class_1!N41,Class_2!N41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q75" t="str">
+        <f>IF(MIN(Class_0!O41,Class_1!O41,Class_2!O41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R75" t="str">
+        <f>IF(MIN(Class_0!P41,Class_1!P41,Class_2!P41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S75" t="str">
+        <f>IF(MIN(Class_0!Q41,Class_1!Q41,Class_2!Q41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T75" t="str">
+        <f>IF(MIN(Class_0!R41,Class_1!R41,Class_2!R41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="U75" t="str">
+        <f>IF(MIN(Class_0!S41,Class_1!S41,Class_2!S41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="V75" t="str">
+        <f>IF(MIN(Class_0!T41,Class_1!T41,Class_2!T41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W75" t="str">
+        <f>IF(MIN(Class_0!U41,Class_1!U41,Class_2!U41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X75" t="str">
+        <f>IF(MIN(Class_0!V41,Class_1!V41,Class_2!V41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y75" t="str">
+        <f>IF(MIN(Class_0!W41,Class_1!W41,Class_2!W41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Z75" t="str">
+        <f>IF(MIN(Class_0!X41,Class_1!X41,Class_2!X41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA75" t="str">
+        <f>IF(MIN(Class_0!Y41,Class_1!Y41,Class_2!Y41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB75" t="str">
+        <f>IF(MIN(Class_0!Z41,Class_1!Z41,Class_2!Z41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC75" t="str">
+        <f>IF(MIN(Class_0!AA41,Class_1!AA41,Class_2!AA41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD75" t="str">
+        <f>IF(MIN(Class_0!AB41,Class_1!AB41,Class_2!AB41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE75" t="str">
+        <f>IF(MIN(Class_0!AC41,Class_1!AC41,Class_2!AC41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF75" t="str">
+        <f>IF(MIN(Class_0!AD41,Class_1!AD41,Class_2!AD41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG75" t="str">
+        <f>IF(MIN(Class_0!AE41,Class_1!AE41,Class_2!AE41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH75" t="str">
+        <f>IF(MIN(Class_0!AF41,Class_1!AF41,Class_2!AF41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI75" t="str">
+        <f>IF(MIN(Class_0!AG41,Class_1!AG41,Class_2!AG41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ75" t="str">
+        <f>IF(MIN(Class_0!AH41,Class_1!AH41,Class_2!AH41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AK75" t="str">
+        <f>IF(MIN(Class_0!AI41,Class_1!AI41,Class_2!AI41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL75" t="str">
+        <f>IF(MIN(Class_0!AJ41,Class_1!AJ41,Class_2!AJ41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM75" t="str">
+        <f>IF(MIN(Class_0!AK41,Class_1!AK41,Class_2!AK41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AN75" t="str">
+        <f>IF(MIN(Class_0!AL41,Class_1!AL41,Class_2!AL41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO75" t="str">
+        <f>IF(MIN(Class_0!AM41,Class_1!AM41,Class_2!AM41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AP75" t="str">
+        <f>IF(MIN(Class_0!AN41,Class_1!AN41,Class_2!AN41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AQ75" t="str">
+        <f>IF(MIN(Class_0!AO41,Class_1!AO41,Class_2!AO41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="76" spans="2:48" x14ac:dyDescent="0.35">
+      <c r="B76" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C76">
+        <f t="shared" si="7"/>
+        <v>40</v>
+      </c>
+      <c r="D76" t="str">
+        <f>IF(MIN(Class_0!B42,Class_1!B42,Class_2!B42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E76" t="str">
+        <f>IF(MIN(Class_0!C42,Class_1!C42,Class_2!C42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F76" t="str">
+        <f>IF(MIN(Class_0!D42,Class_1!D42,Class_2!D42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G76" t="str">
+        <f>IF(MIN(Class_0!E42,Class_1!E42,Class_2!E42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H76" t="str">
+        <f>IF(MIN(Class_0!F42,Class_1!F42,Class_2!F42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="I76" t="str">
+        <f>IF(MIN(Class_0!G42,Class_1!G42,Class_2!G42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J76" t="str">
+        <f>IF(MIN(Class_0!H42,Class_1!H42,Class_2!H42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K76" t="str">
+        <f>IF(MIN(Class_0!I42,Class_1!I42,Class_2!I42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L76" t="str">
+        <f>IF(MIN(Class_0!J42,Class_1!J42,Class_2!J42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M76" t="str">
+        <f>IF(MIN(Class_0!K42,Class_1!K42,Class_2!K42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N76" t="str">
+        <f>IF(MIN(Class_0!L42,Class_1!L42,Class_2!L42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="O76" t="str">
+        <f>IF(MIN(Class_0!M42,Class_1!M42,Class_2!M42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="P76" t="str">
+        <f>IF(MIN(Class_0!N42,Class_1!N42,Class_2!N42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q76" t="str">
+        <f>IF(MIN(Class_0!O42,Class_1!O42,Class_2!O42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R76" t="str">
+        <f>IF(MIN(Class_0!P42,Class_1!P42,Class_2!P42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S76" t="str">
+        <f>IF(MIN(Class_0!Q42,Class_1!Q42,Class_2!Q42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T76" t="str">
+        <f>IF(MIN(Class_0!R42,Class_1!R42,Class_2!R42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U76" t="str">
+        <f>IF(MIN(Class_0!S42,Class_1!S42,Class_2!S42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V76" t="str">
+        <f>IF(MIN(Class_0!T42,Class_1!T42,Class_2!T42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W76" t="str">
+        <f>IF(MIN(Class_0!U42,Class_1!U42,Class_2!U42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X76" t="str">
+        <f>IF(MIN(Class_0!V42,Class_1!V42,Class_2!V42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y76" t="str">
+        <f>IF(MIN(Class_0!W42,Class_1!W42,Class_2!W42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z76" t="str">
+        <f>IF(MIN(Class_0!X42,Class_1!X42,Class_2!X42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA76" t="str">
+        <f>IF(MIN(Class_0!Y42,Class_1!Y42,Class_2!Y42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB76" t="str">
+        <f>IF(MIN(Class_0!Z42,Class_1!Z42,Class_2!Z42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC76" t="str">
+        <f>IF(MIN(Class_0!AA42,Class_1!AA42,Class_2!AA42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD76" t="str">
+        <f>IF(MIN(Class_0!AB42,Class_1!AB42,Class_2!AB42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE76" t="str">
+        <f>IF(MIN(Class_0!AC42,Class_1!AC42,Class_2!AC42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF76" t="str">
+        <f>IF(MIN(Class_0!AD42,Class_1!AD42,Class_2!AD42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG76" t="str">
+        <f>IF(MIN(Class_0!AE42,Class_1!AE42,Class_2!AE42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH76" t="str">
+        <f>IF(MIN(Class_0!AF42,Class_1!AF42,Class_2!AF42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI76" t="str">
+        <f>IF(MIN(Class_0!AG42,Class_1!AG42,Class_2!AG42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ76" t="str">
+        <f>IF(MIN(Class_0!AH42,Class_1!AH42,Class_2!AH42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK76" t="str">
+        <f>IF(MIN(Class_0!AI42,Class_1!AI42,Class_2!AI42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL76" t="str">
+        <f>IF(MIN(Class_0!AJ42,Class_1!AJ42,Class_2!AJ42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM76" t="str">
+        <f>IF(MIN(Class_0!AK42,Class_1!AK42,Class_2!AK42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN76" t="str">
+        <f>IF(MIN(Class_0!AL42,Class_1!AL42,Class_2!AL42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO76" t="str">
+        <f>IF(MIN(Class_0!AM42,Class_1!AM42,Class_2!AM42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP76" t="str">
+        <f>IF(MIN(Class_0!AN42,Class_1!AN42,Class_2!AN42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ76" t="str">
+        <f>IF(MIN(Class_0!AO42,Class_1!AO42,Class_2!AO42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR76" t="str">
+        <f>IF(MIN(Class_0!AP42,Class_1!AP42,Class_2!AP42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="77" spans="2:48" x14ac:dyDescent="0.35">
+      <c r="B77" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C77">
+        <f t="shared" si="7"/>
+        <v>41</v>
+      </c>
+      <c r="D77" t="str">
+        <f>IF(MIN(Class_0!B43,Class_1!B43,Class_2!B43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E77" t="str">
+        <f>IF(MIN(Class_0!C43,Class_1!C43,Class_2!C43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F77" t="str">
+        <f>IF(MIN(Class_0!D43,Class_1!D43,Class_2!D43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G77" t="str">
+        <f>IF(MIN(Class_0!E43,Class_1!E43,Class_2!E43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H77" t="str">
+        <f>IF(MIN(Class_0!F43,Class_1!F43,Class_2!F43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I77" t="str">
+        <f>IF(MIN(Class_0!G43,Class_1!G43,Class_2!G43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J77" t="str">
+        <f>IF(MIN(Class_0!H43,Class_1!H43,Class_2!H43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K77" t="str">
+        <f>IF(MIN(Class_0!I43,Class_1!I43,Class_2!I43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L77" t="str">
+        <f>IF(MIN(Class_0!J43,Class_1!J43,Class_2!J43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M77" t="str">
+        <f>IF(MIN(Class_0!K43,Class_1!K43,Class_2!K43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N77" t="str">
+        <f>IF(MIN(Class_0!L43,Class_1!L43,Class_2!L43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O77" t="str">
+        <f>IF(MIN(Class_0!M43,Class_1!M43,Class_2!M43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="P77" t="str">
+        <f>IF(MIN(Class_0!N43,Class_1!N43,Class_2!N43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q77" t="str">
+        <f>IF(MIN(Class_0!O43,Class_1!O43,Class_2!O43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R77" t="str">
+        <f>IF(MIN(Class_0!P43,Class_1!P43,Class_2!P43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S77" t="str">
+        <f>IF(MIN(Class_0!Q43,Class_1!Q43,Class_2!Q43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T77" t="str">
+        <f>IF(MIN(Class_0!R43,Class_1!R43,Class_2!R43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U77" t="str">
+        <f>IF(MIN(Class_0!S43,Class_1!S43,Class_2!S43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V77" t="str">
+        <f>IF(MIN(Class_0!T43,Class_1!T43,Class_2!T43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W77" t="str">
+        <f>IF(MIN(Class_0!U43,Class_1!U43,Class_2!U43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X77" t="str">
+        <f>IF(MIN(Class_0!V43,Class_1!V43,Class_2!V43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y77" t="str">
+        <f>IF(MIN(Class_0!W43,Class_1!W43,Class_2!W43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z77" t="str">
+        <f>IF(MIN(Class_0!X43,Class_1!X43,Class_2!X43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA77" t="str">
+        <f>IF(MIN(Class_0!Y43,Class_1!Y43,Class_2!Y43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB77" t="str">
+        <f>IF(MIN(Class_0!Z43,Class_1!Z43,Class_2!Z43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC77" t="str">
+        <f>IF(MIN(Class_0!AA43,Class_1!AA43,Class_2!AA43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD77" t="str">
+        <f>IF(MIN(Class_0!AB43,Class_1!AB43,Class_2!AB43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE77" t="str">
+        <f>IF(MIN(Class_0!AC43,Class_1!AC43,Class_2!AC43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF77" t="str">
+        <f>IF(MIN(Class_0!AD43,Class_1!AD43,Class_2!AD43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG77" t="str">
+        <f>IF(MIN(Class_0!AE43,Class_1!AE43,Class_2!AE43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH77" t="str">
+        <f>IF(MIN(Class_0!AF43,Class_1!AF43,Class_2!AF43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI77" t="str">
+        <f>IF(MIN(Class_0!AG43,Class_1!AG43,Class_2!AG43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ77" t="str">
+        <f>IF(MIN(Class_0!AH43,Class_1!AH43,Class_2!AH43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AK77" t="str">
+        <f>IF(MIN(Class_0!AI43,Class_1!AI43,Class_2!AI43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL77" t="str">
+        <f>IF(MIN(Class_0!AJ43,Class_1!AJ43,Class_2!AJ43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM77" t="str">
+        <f>IF(MIN(Class_0!AK43,Class_1!AK43,Class_2!AK43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN77" t="str">
+        <f>IF(MIN(Class_0!AL43,Class_1!AL43,Class_2!AL43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO77" t="str">
+        <f>IF(MIN(Class_0!AM43,Class_1!AM43,Class_2!AM43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP77" t="str">
+        <f>IF(MIN(Class_0!AN43,Class_1!AN43,Class_2!AN43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ77" t="str">
+        <f>IF(MIN(Class_0!AO43,Class_1!AO43,Class_2!AO43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR77" t="str">
+        <f>IF(MIN(Class_0!AP43,Class_1!AP43,Class_2!AP43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AS77" t="str">
+        <f>IF(MIN(Class_0!AQ43,Class_1!AQ43,Class_2!AQ43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="78" spans="2:48" x14ac:dyDescent="0.35">
+      <c r="B78" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C78">
+        <f t="shared" si="7"/>
+        <v>42</v>
+      </c>
+      <c r="D78" t="str">
+        <f>IF(MIN(Class_0!B44,Class_1!B44,Class_2!B44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E78" t="str">
+        <f>IF(MIN(Class_0!C44,Class_1!C44,Class_2!C44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F78" t="str">
+        <f>IF(MIN(Class_0!D44,Class_1!D44,Class_2!D44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G78" t="str">
+        <f>IF(MIN(Class_0!E44,Class_1!E44,Class_2!E44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H78" t="str">
+        <f>IF(MIN(Class_0!F44,Class_1!F44,Class_2!F44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I78" t="str">
+        <f>IF(MIN(Class_0!G44,Class_1!G44,Class_2!G44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J78" t="str">
+        <f>IF(MIN(Class_0!H44,Class_1!H44,Class_2!H44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K78" t="str">
+        <f>IF(MIN(Class_0!I44,Class_1!I44,Class_2!I44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L78" t="str">
+        <f>IF(MIN(Class_0!J44,Class_1!J44,Class_2!J44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M78" t="str">
+        <f>IF(MIN(Class_0!K44,Class_1!K44,Class_2!K44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N78" t="str">
+        <f>IF(MIN(Class_0!L44,Class_1!L44,Class_2!L44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O78" t="str">
+        <f>IF(MIN(Class_0!M44,Class_1!M44,Class_2!M44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="P78" t="str">
+        <f>IF(MIN(Class_0!N44,Class_1!N44,Class_2!N44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q78" t="str">
+        <f>IF(MIN(Class_0!O44,Class_1!O44,Class_2!O44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R78" t="str">
+        <f>IF(MIN(Class_0!P44,Class_1!P44,Class_2!P44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S78" t="str">
+        <f>IF(MIN(Class_0!Q44,Class_1!Q44,Class_2!Q44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T78" t="str">
+        <f>IF(MIN(Class_0!R44,Class_1!R44,Class_2!R44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U78" t="str">
+        <f>IF(MIN(Class_0!S44,Class_1!S44,Class_2!S44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V78" t="str">
+        <f>IF(MIN(Class_0!T44,Class_1!T44,Class_2!T44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W78" t="str">
+        <f>IF(MIN(Class_0!U44,Class_1!U44,Class_2!U44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X78" t="str">
+        <f>IF(MIN(Class_0!V44,Class_1!V44,Class_2!V44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y78" t="str">
+        <f>IF(MIN(Class_0!W44,Class_1!W44,Class_2!W44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z78" t="str">
+        <f>IF(MIN(Class_0!X44,Class_1!X44,Class_2!X44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA78" t="str">
+        <f>IF(MIN(Class_0!Y44,Class_1!Y44,Class_2!Y44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB78" t="str">
+        <f>IF(MIN(Class_0!Z44,Class_1!Z44,Class_2!Z44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC78" t="str">
+        <f>IF(MIN(Class_0!AA44,Class_1!AA44,Class_2!AA44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD78" t="str">
+        <f>IF(MIN(Class_0!AB44,Class_1!AB44,Class_2!AB44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE78" t="str">
+        <f>IF(MIN(Class_0!AC44,Class_1!AC44,Class_2!AC44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF78" t="str">
+        <f>IF(MIN(Class_0!AD44,Class_1!AD44,Class_2!AD44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG78" t="str">
+        <f>IF(MIN(Class_0!AE44,Class_1!AE44,Class_2!AE44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH78" t="str">
+        <f>IF(MIN(Class_0!AF44,Class_1!AF44,Class_2!AF44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI78" t="str">
+        <f>IF(MIN(Class_0!AG44,Class_1!AG44,Class_2!AG44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ78" t="str">
+        <f>IF(MIN(Class_0!AH44,Class_1!AH44,Class_2!AH44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK78" t="str">
+        <f>IF(MIN(Class_0!AI44,Class_1!AI44,Class_2!AI44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL78" t="str">
+        <f>IF(MIN(Class_0!AJ44,Class_1!AJ44,Class_2!AJ44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM78" t="str">
+        <f>IF(MIN(Class_0!AK44,Class_1!AK44,Class_2!AK44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN78" t="str">
+        <f>IF(MIN(Class_0!AL44,Class_1!AL44,Class_2!AL44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO78" t="str">
+        <f>IF(MIN(Class_0!AM44,Class_1!AM44,Class_2!AM44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP78" t="str">
+        <f>IF(MIN(Class_0!AN44,Class_1!AN44,Class_2!AN44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ78" t="str">
+        <f>IF(MIN(Class_0!AO44,Class_1!AO44,Class_2!AO44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR78" t="str">
+        <f>IF(MIN(Class_0!AP44,Class_1!AP44,Class_2!AP44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AS78" t="str">
+        <f>IF(MIN(Class_0!AQ44,Class_1!AQ44,Class_2!AQ44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AT78" t="str">
+        <f>IF(MIN(Class_0!AR44,Class_1!AR44,Class_2!AR44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="79" spans="2:48" x14ac:dyDescent="0.35">
+      <c r="B79" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C79">
+        <f t="shared" si="7"/>
+        <v>43</v>
+      </c>
+      <c r="D79" t="str">
+        <f>IF(MIN(Class_0!B45,Class_1!B45,Class_2!B45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E79" t="str">
+        <f>IF(MIN(Class_0!C45,Class_1!C45,Class_2!C45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F79" t="str">
+        <f>IF(MIN(Class_0!D45,Class_1!D45,Class_2!D45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G79" t="str">
+        <f>IF(MIN(Class_0!E45,Class_1!E45,Class_2!E45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H79" t="str">
+        <f>IF(MIN(Class_0!F45,Class_1!F45,Class_2!F45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I79" t="str">
+        <f>IF(MIN(Class_0!G45,Class_1!G45,Class_2!G45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J79" t="str">
+        <f>IF(MIN(Class_0!H45,Class_1!H45,Class_2!H45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K79" t="str">
+        <f>IF(MIN(Class_0!I45,Class_1!I45,Class_2!I45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L79" t="str">
+        <f>IF(MIN(Class_0!J45,Class_1!J45,Class_2!J45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M79" t="str">
+        <f>IF(MIN(Class_0!K45,Class_1!K45,Class_2!K45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N79" t="str">
+        <f>IF(MIN(Class_0!L45,Class_1!L45,Class_2!L45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O79" t="str">
+        <f>IF(MIN(Class_0!M45,Class_1!M45,Class_2!M45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="P79" t="str">
+        <f>IF(MIN(Class_0!N45,Class_1!N45,Class_2!N45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q79" t="str">
+        <f>IF(MIN(Class_0!O45,Class_1!O45,Class_2!O45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R79" t="str">
+        <f>IF(MIN(Class_0!P45,Class_1!P45,Class_2!P45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S79" t="str">
+        <f>IF(MIN(Class_0!Q45,Class_1!Q45,Class_2!Q45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T79" t="str">
+        <f>IF(MIN(Class_0!R45,Class_1!R45,Class_2!R45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U79" t="str">
+        <f>IF(MIN(Class_0!S45,Class_1!S45,Class_2!S45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V79" t="str">
+        <f>IF(MIN(Class_0!T45,Class_1!T45,Class_2!T45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W79" t="str">
+        <f>IF(MIN(Class_0!U45,Class_1!U45,Class_2!U45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X79" t="str">
+        <f>IF(MIN(Class_0!V45,Class_1!V45,Class_2!V45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y79" t="str">
+        <f>IF(MIN(Class_0!W45,Class_1!W45,Class_2!W45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z79" t="str">
+        <f>IF(MIN(Class_0!X45,Class_1!X45,Class_2!X45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA79" t="str">
+        <f>IF(MIN(Class_0!Y45,Class_1!Y45,Class_2!Y45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB79" t="str">
+        <f>IF(MIN(Class_0!Z45,Class_1!Z45,Class_2!Z45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC79" t="str">
+        <f>IF(MIN(Class_0!AA45,Class_1!AA45,Class_2!AA45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD79" t="str">
+        <f>IF(MIN(Class_0!AB45,Class_1!AB45,Class_2!AB45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE79" t="str">
+        <f>IF(MIN(Class_0!AC45,Class_1!AC45,Class_2!AC45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF79" t="str">
+        <f>IF(MIN(Class_0!AD45,Class_1!AD45,Class_2!AD45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG79" t="str">
+        <f>IF(MIN(Class_0!AE45,Class_1!AE45,Class_2!AE45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH79" t="str">
+        <f>IF(MIN(Class_0!AF45,Class_1!AF45,Class_2!AF45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI79" t="str">
+        <f>IF(MIN(Class_0!AG45,Class_1!AG45,Class_2!AG45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ79" t="str">
+        <f>IF(MIN(Class_0!AH45,Class_1!AH45,Class_2!AH45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AK79" t="str">
+        <f>IF(MIN(Class_0!AI45,Class_1!AI45,Class_2!AI45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL79" t="str">
+        <f>IF(MIN(Class_0!AJ45,Class_1!AJ45,Class_2!AJ45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM79" t="str">
+        <f>IF(MIN(Class_0!AK45,Class_1!AK45,Class_2!AK45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN79" t="str">
+        <f>IF(MIN(Class_0!AL45,Class_1!AL45,Class_2!AL45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO79" t="str">
+        <f>IF(MIN(Class_0!AM45,Class_1!AM45,Class_2!AM45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP79" t="str">
+        <f>IF(MIN(Class_0!AN45,Class_1!AN45,Class_2!AN45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ79" t="str">
+        <f>IF(MIN(Class_0!AO45,Class_1!AO45,Class_2!AO45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR79" t="str">
+        <f>IF(MIN(Class_0!AP45,Class_1!AP45,Class_2!AP45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AS79" t="str">
+        <f>IF(MIN(Class_0!AQ45,Class_1!AQ45,Class_2!AQ45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AT79" t="str">
+        <f>IF(MIN(Class_0!AR45,Class_1!AR45,Class_2!AR45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AU79" t="str">
+        <f>IF(MIN(Class_0!AS45,Class_1!AS45,Class_2!AS45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="80" spans="2:48" x14ac:dyDescent="0.35">
+      <c r="B80" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C80">
+        <f t="shared" si="7"/>
+        <v>44</v>
+      </c>
+      <c r="D80" t="str">
+        <f>IF(MIN(Class_0!B46,Class_1!B46,Class_2!B46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E80" t="str">
+        <f>IF(MIN(Class_0!C46,Class_1!C46,Class_2!C46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F80" t="str">
+        <f>IF(MIN(Class_0!D46,Class_1!D46,Class_2!D46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G80" t="str">
+        <f>IF(MIN(Class_0!E46,Class_1!E46,Class_2!E46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H80" t="str">
+        <f>IF(MIN(Class_0!F46,Class_1!F46,Class_2!F46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I80" t="str">
+        <f>IF(MIN(Class_0!G46,Class_1!G46,Class_2!G46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J80" t="str">
+        <f>IF(MIN(Class_0!H46,Class_1!H46,Class_2!H46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K80" t="str">
+        <f>IF(MIN(Class_0!I46,Class_1!I46,Class_2!I46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L80" t="str">
+        <f>IF(MIN(Class_0!J46,Class_1!J46,Class_2!J46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M80" t="str">
+        <f>IF(MIN(Class_0!K46,Class_1!K46,Class_2!K46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N80" t="str">
+        <f>IF(MIN(Class_0!L46,Class_1!L46,Class_2!L46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O80" t="str">
+        <f>IF(MIN(Class_0!M46,Class_1!M46,Class_2!M46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P80" t="str">
+        <f>IF(MIN(Class_0!N46,Class_1!N46,Class_2!N46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q80" t="str">
+        <f>IF(MIN(Class_0!O46,Class_1!O46,Class_2!O46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R80" t="str">
+        <f>IF(MIN(Class_0!P46,Class_1!P46,Class_2!P46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S80" t="str">
+        <f>IF(MIN(Class_0!Q46,Class_1!Q46,Class_2!Q46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T80" t="str">
+        <f>IF(MIN(Class_0!R46,Class_1!R46,Class_2!R46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U80" t="str">
+        <f>IF(MIN(Class_0!S46,Class_1!S46,Class_2!S46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V80" t="str">
+        <f>IF(MIN(Class_0!T46,Class_1!T46,Class_2!T46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="W80" t="str">
+        <f>IF(MIN(Class_0!U46,Class_1!U46,Class_2!U46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X80" t="str">
+        <f>IF(MIN(Class_0!V46,Class_1!V46,Class_2!V46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Y80" t="str">
+        <f>IF(MIN(Class_0!W46,Class_1!W46,Class_2!W46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Z80" t="str">
+        <f>IF(MIN(Class_0!X46,Class_1!X46,Class_2!X46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA80" t="str">
+        <f>IF(MIN(Class_0!Y46,Class_1!Y46,Class_2!Y46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB80" t="str">
+        <f>IF(MIN(Class_0!Z46,Class_1!Z46,Class_2!Z46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC80" t="str">
+        <f>IF(MIN(Class_0!AA46,Class_1!AA46,Class_2!AA46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD80" t="str">
+        <f>IF(MIN(Class_0!AB46,Class_1!AB46,Class_2!AB46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE80" t="str">
+        <f>IF(MIN(Class_0!AC46,Class_1!AC46,Class_2!AC46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF80" t="str">
+        <f>IF(MIN(Class_0!AD46,Class_1!AD46,Class_2!AD46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG80" t="str">
+        <f>IF(MIN(Class_0!AE46,Class_1!AE46,Class_2!AE46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH80" t="str">
+        <f>IF(MIN(Class_0!AF46,Class_1!AF46,Class_2!AF46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI80" t="str">
+        <f>IF(MIN(Class_0!AG46,Class_1!AG46,Class_2!AG46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ80" t="str">
+        <f>IF(MIN(Class_0!AH46,Class_1!AH46,Class_2!AH46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK80" t="str">
+        <f>IF(MIN(Class_0!AI46,Class_1!AI46,Class_2!AI46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL80" t="str">
+        <f>IF(MIN(Class_0!AJ46,Class_1!AJ46,Class_2!AJ46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM80" t="str">
+        <f>IF(MIN(Class_0!AK46,Class_1!AK46,Class_2!AK46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN80" t="str">
+        <f>IF(MIN(Class_0!AL46,Class_1!AL46,Class_2!AL46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO80" t="str">
+        <f>IF(MIN(Class_0!AM46,Class_1!AM46,Class_2!AM46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AP80" t="str">
+        <f>IF(MIN(Class_0!AN46,Class_1!AN46,Class_2!AN46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ80" t="str">
+        <f>IF(MIN(Class_0!AO46,Class_1!AO46,Class_2!AO46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR80" t="str">
+        <f>IF(MIN(Class_0!AP46,Class_1!AP46,Class_2!AP46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS80" t="str">
+        <f>IF(MIN(Class_0!AQ46,Class_1!AQ46,Class_2!AQ46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT80" t="str">
+        <f>IF(MIN(Class_0!AR46,Class_1!AR46,Class_2!AR46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AU80" t="str">
+        <f>IF(MIN(Class_0!AS46,Class_1!AS46,Class_2!AS46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AV80" t="str">
+        <f>IF(MIN(Class_0!AT46,Class_1!AT46,Class_2!AT46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="81" spans="2:64" x14ac:dyDescent="0.35">
+      <c r="B81" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C81">
+        <f t="shared" si="7"/>
+        <v>45</v>
+      </c>
+      <c r="D81" t="str">
+        <f>IF(MIN(Class_0!B47,Class_1!B47,Class_2!B47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="E81" t="str">
+        <f>IF(MIN(Class_0!C47,Class_1!C47,Class_2!C47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F81" t="str">
+        <f>IF(MIN(Class_0!D47,Class_1!D47,Class_2!D47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G81" t="str">
+        <f>IF(MIN(Class_0!E47,Class_1!E47,Class_2!E47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H81" t="str">
+        <f>IF(MIN(Class_0!F47,Class_1!F47,Class_2!F47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I81" t="str">
+        <f>IF(MIN(Class_0!G47,Class_1!G47,Class_2!G47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J81" t="str">
+        <f>IF(MIN(Class_0!H47,Class_1!H47,Class_2!H47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K81" t="str">
+        <f>IF(MIN(Class_0!I47,Class_1!I47,Class_2!I47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L81" t="str">
+        <f>IF(MIN(Class_0!J47,Class_1!J47,Class_2!J47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M81" t="str">
+        <f>IF(MIN(Class_0!K47,Class_1!K47,Class_2!K47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N81" t="str">
+        <f>IF(MIN(Class_0!L47,Class_1!L47,Class_2!L47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O81" t="str">
+        <f>IF(MIN(Class_0!M47,Class_1!M47,Class_2!M47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="P81" t="str">
+        <f>IF(MIN(Class_0!N47,Class_1!N47,Class_2!N47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q81" t="str">
+        <f>IF(MIN(Class_0!O47,Class_1!O47,Class_2!O47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R81" t="str">
+        <f>IF(MIN(Class_0!P47,Class_1!P47,Class_2!P47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S81" t="str">
+        <f>IF(MIN(Class_0!Q47,Class_1!Q47,Class_2!Q47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T81" t="str">
+        <f>IF(MIN(Class_0!R47,Class_1!R47,Class_2!R47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U81" t="str">
+        <f>IF(MIN(Class_0!S47,Class_1!S47,Class_2!S47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V81" t="str">
+        <f>IF(MIN(Class_0!T47,Class_1!T47,Class_2!T47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W81" t="str">
+        <f>IF(MIN(Class_0!U47,Class_1!U47,Class_2!U47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X81" t="str">
+        <f>IF(MIN(Class_0!V47,Class_1!V47,Class_2!V47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y81" t="str">
+        <f>IF(MIN(Class_0!W47,Class_1!W47,Class_2!W47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z81" t="str">
+        <f>IF(MIN(Class_0!X47,Class_1!X47,Class_2!X47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA81" t="str">
+        <f>IF(MIN(Class_0!Y47,Class_1!Y47,Class_2!Y47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB81" t="str">
+        <f>IF(MIN(Class_0!Z47,Class_1!Z47,Class_2!Z47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC81" t="str">
+        <f>IF(MIN(Class_0!AA47,Class_1!AA47,Class_2!AA47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD81" t="str">
+        <f>IF(MIN(Class_0!AB47,Class_1!AB47,Class_2!AB47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE81" t="str">
+        <f>IF(MIN(Class_0!AC47,Class_1!AC47,Class_2!AC47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF81" t="str">
+        <f>IF(MIN(Class_0!AD47,Class_1!AD47,Class_2!AD47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG81" t="str">
+        <f>IF(MIN(Class_0!AE47,Class_1!AE47,Class_2!AE47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH81" t="str">
+        <f>IF(MIN(Class_0!AF47,Class_1!AF47,Class_2!AF47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI81" t="str">
+        <f>IF(MIN(Class_0!AG47,Class_1!AG47,Class_2!AG47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ81" t="str">
+        <f>IF(MIN(Class_0!AH47,Class_1!AH47,Class_2!AH47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK81" t="str">
+        <f>IF(MIN(Class_0!AI47,Class_1!AI47,Class_2!AI47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL81" t="str">
+        <f>IF(MIN(Class_0!AJ47,Class_1!AJ47,Class_2!AJ47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM81" t="str">
+        <f>IF(MIN(Class_0!AK47,Class_1!AK47,Class_2!AK47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN81" t="str">
+        <f>IF(MIN(Class_0!AL47,Class_1!AL47,Class_2!AL47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO81" t="str">
+        <f>IF(MIN(Class_0!AM47,Class_1!AM47,Class_2!AM47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP81" t="str">
+        <f>IF(MIN(Class_0!AN47,Class_1!AN47,Class_2!AN47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ81" t="str">
+        <f>IF(MIN(Class_0!AO47,Class_1!AO47,Class_2!AO47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR81" t="str">
+        <f>IF(MIN(Class_0!AP47,Class_1!AP47,Class_2!AP47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AS81" t="str">
+        <f>IF(MIN(Class_0!AQ47,Class_1!AQ47,Class_2!AQ47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AT81" t="str">
+        <f>IF(MIN(Class_0!AR47,Class_1!AR47,Class_2!AR47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AU81" t="str">
+        <f>IF(MIN(Class_0!AS47,Class_1!AS47,Class_2!AS47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV81" t="str">
+        <f>IF(MIN(Class_0!AT47,Class_1!AT47,Class_2!AT47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW81" t="str">
+        <f>IF(MIN(Class_0!AU47,Class_1!AU47,Class_2!AU47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="82" spans="2:64" x14ac:dyDescent="0.35">
+      <c r="B82" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C82">
+        <f t="shared" si="7"/>
+        <v>46</v>
+      </c>
+      <c r="D82" t="str">
+        <f>IF(MIN(Class_0!B48,Class_1!B48,Class_2!B48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E82" t="str">
+        <f>IF(MIN(Class_0!C48,Class_1!C48,Class_2!C48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F82" t="str">
+        <f>IF(MIN(Class_0!D48,Class_1!D48,Class_2!D48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G82" t="str">
+        <f>IF(MIN(Class_0!E48,Class_1!E48,Class_2!E48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H82" t="str">
+        <f>IF(MIN(Class_0!F48,Class_1!F48,Class_2!F48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="I82" t="str">
+        <f>IF(MIN(Class_0!G48,Class_1!G48,Class_2!G48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J82" t="str">
+        <f>IF(MIN(Class_0!H48,Class_1!H48,Class_2!H48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K82" t="str">
+        <f>IF(MIN(Class_0!I48,Class_1!I48,Class_2!I48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L82" t="str">
+        <f>IF(MIN(Class_0!J48,Class_1!J48,Class_2!J48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M82" t="str">
+        <f>IF(MIN(Class_0!K48,Class_1!K48,Class_2!K48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N82" t="str">
+        <f>IF(MIN(Class_0!L48,Class_1!L48,Class_2!L48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="O82" t="str">
+        <f>IF(MIN(Class_0!M48,Class_1!M48,Class_2!M48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="P82" t="str">
+        <f>IF(MIN(Class_0!N48,Class_1!N48,Class_2!N48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q82" t="str">
+        <f>IF(MIN(Class_0!O48,Class_1!O48,Class_2!O48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R82" t="str">
+        <f>IF(MIN(Class_0!P48,Class_1!P48,Class_2!P48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S82" t="str">
+        <f>IF(MIN(Class_0!Q48,Class_1!Q48,Class_2!Q48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T82" t="str">
+        <f>IF(MIN(Class_0!R48,Class_1!R48,Class_2!R48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U82" t="str">
+        <f>IF(MIN(Class_0!S48,Class_1!S48,Class_2!S48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V82" t="str">
+        <f>IF(MIN(Class_0!T48,Class_1!T48,Class_2!T48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W82" t="str">
+        <f>IF(MIN(Class_0!U48,Class_1!U48,Class_2!U48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X82" t="str">
+        <f>IF(MIN(Class_0!V48,Class_1!V48,Class_2!V48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y82" t="str">
+        <f>IF(MIN(Class_0!W48,Class_1!W48,Class_2!W48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z82" t="str">
+        <f>IF(MIN(Class_0!X48,Class_1!X48,Class_2!X48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA82" t="str">
+        <f>IF(MIN(Class_0!Y48,Class_1!Y48,Class_2!Y48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB82" t="str">
+        <f>IF(MIN(Class_0!Z48,Class_1!Z48,Class_2!Z48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC82" t="str">
+        <f>IF(MIN(Class_0!AA48,Class_1!AA48,Class_2!AA48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD82" t="str">
+        <f>IF(MIN(Class_0!AB48,Class_1!AB48,Class_2!AB48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE82" t="str">
+        <f>IF(MIN(Class_0!AC48,Class_1!AC48,Class_2!AC48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF82" t="str">
+        <f>IF(MIN(Class_0!AD48,Class_1!AD48,Class_2!AD48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG82" t="str">
+        <f>IF(MIN(Class_0!AE48,Class_1!AE48,Class_2!AE48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH82" t="str">
+        <f>IF(MIN(Class_0!AF48,Class_1!AF48,Class_2!AF48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI82" t="str">
+        <f>IF(MIN(Class_0!AG48,Class_1!AG48,Class_2!AG48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ82" t="str">
+        <f>IF(MIN(Class_0!AH48,Class_1!AH48,Class_2!AH48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK82" t="str">
+        <f>IF(MIN(Class_0!AI48,Class_1!AI48,Class_2!AI48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL82" t="str">
+        <f>IF(MIN(Class_0!AJ48,Class_1!AJ48,Class_2!AJ48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM82" t="str">
+        <f>IF(MIN(Class_0!AK48,Class_1!AK48,Class_2!AK48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN82" t="str">
+        <f>IF(MIN(Class_0!AL48,Class_1!AL48,Class_2!AL48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO82" t="str">
+        <f>IF(MIN(Class_0!AM48,Class_1!AM48,Class_2!AM48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP82" t="str">
+        <f>IF(MIN(Class_0!AN48,Class_1!AN48,Class_2!AN48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ82" t="str">
+        <f>IF(MIN(Class_0!AO48,Class_1!AO48,Class_2!AO48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR82" t="str">
+        <f>IF(MIN(Class_0!AP48,Class_1!AP48,Class_2!AP48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AS82" t="str">
+        <f>IF(MIN(Class_0!AQ48,Class_1!AQ48,Class_2!AQ48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AT82" t="str">
+        <f>IF(MIN(Class_0!AR48,Class_1!AR48,Class_2!AR48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AU82" t="str">
+        <f>IF(MIN(Class_0!AS48,Class_1!AS48,Class_2!AS48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AV82" t="str">
+        <f>IF(MIN(Class_0!AT48,Class_1!AT48,Class_2!AT48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW82" t="str">
+        <f>IF(MIN(Class_0!AU48,Class_1!AU48,Class_2!AU48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AX82" t="str">
+        <f>IF(MIN(Class_0!AV48,Class_1!AV48,Class_2!AV48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="83" spans="2:64" x14ac:dyDescent="0.35">
+      <c r="B83" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C83">
+        <f t="shared" si="7"/>
+        <v>47</v>
+      </c>
+      <c r="D83" t="str">
+        <f>IF(MIN(Class_0!B49,Class_1!B49,Class_2!B49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E83" t="str">
+        <f>IF(MIN(Class_0!C49,Class_1!C49,Class_2!C49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F83" t="str">
+        <f>IF(MIN(Class_0!D49,Class_1!D49,Class_2!D49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G83" t="str">
+        <f>IF(MIN(Class_0!E49,Class_1!E49,Class_2!E49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H83" t="str">
+        <f>IF(MIN(Class_0!F49,Class_1!F49,Class_2!F49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="I83" t="str">
+        <f>IF(MIN(Class_0!G49,Class_1!G49,Class_2!G49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J83" t="str">
+        <f>IF(MIN(Class_0!H49,Class_1!H49,Class_2!H49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K83" t="str">
+        <f>IF(MIN(Class_0!I49,Class_1!I49,Class_2!I49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L83" t="str">
+        <f>IF(MIN(Class_0!J49,Class_1!J49,Class_2!J49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M83" t="str">
+        <f>IF(MIN(Class_0!K49,Class_1!K49,Class_2!K49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N83" t="str">
+        <f>IF(MIN(Class_0!L49,Class_1!L49,Class_2!L49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="O83" t="str">
+        <f>IF(MIN(Class_0!M49,Class_1!M49,Class_2!M49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="P83" t="str">
+        <f>IF(MIN(Class_0!N49,Class_1!N49,Class_2!N49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q83" t="str">
+        <f>IF(MIN(Class_0!O49,Class_1!O49,Class_2!O49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R83" t="str">
+        <f>IF(MIN(Class_0!P49,Class_1!P49,Class_2!P49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S83" t="str">
+        <f>IF(MIN(Class_0!Q49,Class_1!Q49,Class_2!Q49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T83" t="str">
+        <f>IF(MIN(Class_0!R49,Class_1!R49,Class_2!R49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U83" t="str">
+        <f>IF(MIN(Class_0!S49,Class_1!S49,Class_2!S49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V83" t="str">
+        <f>IF(MIN(Class_0!T49,Class_1!T49,Class_2!T49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W83" t="str">
+        <f>IF(MIN(Class_0!U49,Class_1!U49,Class_2!U49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X83" t="str">
+        <f>IF(MIN(Class_0!V49,Class_1!V49,Class_2!V49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y83" t="str">
+        <f>IF(MIN(Class_0!W49,Class_1!W49,Class_2!W49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z83" t="str">
+        <f>IF(MIN(Class_0!X49,Class_1!X49,Class_2!X49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA83" t="str">
+        <f>IF(MIN(Class_0!Y49,Class_1!Y49,Class_2!Y49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB83" t="str">
+        <f>IF(MIN(Class_0!Z49,Class_1!Z49,Class_2!Z49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC83" t="str">
+        <f>IF(MIN(Class_0!AA49,Class_1!AA49,Class_2!AA49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD83" t="str">
+        <f>IF(MIN(Class_0!AB49,Class_1!AB49,Class_2!AB49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE83" t="str">
+        <f>IF(MIN(Class_0!AC49,Class_1!AC49,Class_2!AC49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF83" t="str">
+        <f>IF(MIN(Class_0!AD49,Class_1!AD49,Class_2!AD49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG83" t="str">
+        <f>IF(MIN(Class_0!AE49,Class_1!AE49,Class_2!AE49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH83" t="str">
+        <f>IF(MIN(Class_0!AF49,Class_1!AF49,Class_2!AF49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI83" t="str">
+        <f>IF(MIN(Class_0!AG49,Class_1!AG49,Class_2!AG49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ83" t="str">
+        <f>IF(MIN(Class_0!AH49,Class_1!AH49,Class_2!AH49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK83" t="str">
+        <f>IF(MIN(Class_0!AI49,Class_1!AI49,Class_2!AI49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL83" t="str">
+        <f>IF(MIN(Class_0!AJ49,Class_1!AJ49,Class_2!AJ49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM83" t="str">
+        <f>IF(MIN(Class_0!AK49,Class_1!AK49,Class_2!AK49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN83" t="str">
+        <f>IF(MIN(Class_0!AL49,Class_1!AL49,Class_2!AL49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO83" t="str">
+        <f>IF(MIN(Class_0!AM49,Class_1!AM49,Class_2!AM49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP83" t="str">
+        <f>IF(MIN(Class_0!AN49,Class_1!AN49,Class_2!AN49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ83" t="str">
+        <f>IF(MIN(Class_0!AO49,Class_1!AO49,Class_2!AO49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR83" t="str">
+        <f>IF(MIN(Class_0!AP49,Class_1!AP49,Class_2!AP49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AS83" t="str">
+        <f>IF(MIN(Class_0!AQ49,Class_1!AQ49,Class_2!AQ49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AT83" t="str">
+        <f>IF(MIN(Class_0!AR49,Class_1!AR49,Class_2!AR49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AU83" t="str">
+        <f>IF(MIN(Class_0!AS49,Class_1!AS49,Class_2!AS49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV83" t="str">
+        <f>IF(MIN(Class_0!AT49,Class_1!AT49,Class_2!AT49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW83" t="str">
+        <f>IF(MIN(Class_0!AU49,Class_1!AU49,Class_2!AU49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AX83" t="str">
+        <f>IF(MIN(Class_0!AV49,Class_1!AV49,Class_2!AV49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AY83" t="str">
+        <f>IF(MIN(Class_0!AW49,Class_1!AW49,Class_2!AW49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="84" spans="2:64" x14ac:dyDescent="0.35">
+      <c r="B84" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C84">
+        <f t="shared" si="7"/>
+        <v>48</v>
+      </c>
+      <c r="D84" t="str">
+        <f>IF(MIN(Class_0!B50,Class_1!B50,Class_2!B50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E84" t="str">
+        <f>IF(MIN(Class_0!C50,Class_1!C50,Class_2!C50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F84" t="str">
+        <f>IF(MIN(Class_0!D50,Class_1!D50,Class_2!D50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G84" t="str">
+        <f>IF(MIN(Class_0!E50,Class_1!E50,Class_2!E50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H84" t="str">
+        <f>IF(MIN(Class_0!F50,Class_1!F50,Class_2!F50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="I84" t="str">
+        <f>IF(MIN(Class_0!G50,Class_1!G50,Class_2!G50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="J84" t="str">
+        <f>IF(MIN(Class_0!H50,Class_1!H50,Class_2!H50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K84" t="str">
+        <f>IF(MIN(Class_0!I50,Class_1!I50,Class_2!I50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L84" t="str">
+        <f>IF(MIN(Class_0!J50,Class_1!J50,Class_2!J50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M84" t="str">
+        <f>IF(MIN(Class_0!K50,Class_1!K50,Class_2!K50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N84" t="str">
+        <f>IF(MIN(Class_0!L50,Class_1!L50,Class_2!L50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="O84" t="str">
+        <f>IF(MIN(Class_0!M50,Class_1!M50,Class_2!M50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P84" t="str">
+        <f>IF(MIN(Class_0!N50,Class_1!N50,Class_2!N50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q84" t="str">
+        <f>IF(MIN(Class_0!O50,Class_1!O50,Class_2!O50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R84" t="str">
+        <f>IF(MIN(Class_0!P50,Class_1!P50,Class_2!P50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S84" t="str">
+        <f>IF(MIN(Class_0!Q50,Class_1!Q50,Class_2!Q50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T84" t="str">
+        <f>IF(MIN(Class_0!R50,Class_1!R50,Class_2!R50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U84" t="str">
+        <f>IF(MIN(Class_0!S50,Class_1!S50,Class_2!S50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V84" t="str">
+        <f>IF(MIN(Class_0!T50,Class_1!T50,Class_2!T50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W84" t="str">
+        <f>IF(MIN(Class_0!U50,Class_1!U50,Class_2!U50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="X84" t="str">
+        <f>IF(MIN(Class_0!V50,Class_1!V50,Class_2!V50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y84" t="str">
+        <f>IF(MIN(Class_0!W50,Class_1!W50,Class_2!W50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z84" t="str">
+        <f>IF(MIN(Class_0!X50,Class_1!X50,Class_2!X50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA84" t="str">
+        <f>IF(MIN(Class_0!Y50,Class_1!Y50,Class_2!Y50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB84" t="str">
+        <f>IF(MIN(Class_0!Z50,Class_1!Z50,Class_2!Z50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC84" t="str">
+        <f>IF(MIN(Class_0!AA50,Class_1!AA50,Class_2!AA50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD84" t="str">
+        <f>IF(MIN(Class_0!AB50,Class_1!AB50,Class_2!AB50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE84" t="str">
+        <f>IF(MIN(Class_0!AC50,Class_1!AC50,Class_2!AC50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF84" t="str">
+        <f>IF(MIN(Class_0!AD50,Class_1!AD50,Class_2!AD50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG84" t="str">
+        <f>IF(MIN(Class_0!AE50,Class_1!AE50,Class_2!AE50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH84" t="str">
+        <f>IF(MIN(Class_0!AF50,Class_1!AF50,Class_2!AF50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI84" t="str">
+        <f>IF(MIN(Class_0!AG50,Class_1!AG50,Class_2!AG50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ84" t="str">
+        <f>IF(MIN(Class_0!AH50,Class_1!AH50,Class_2!AH50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK84" t="str">
+        <f>IF(MIN(Class_0!AI50,Class_1!AI50,Class_2!AI50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL84" t="str">
+        <f>IF(MIN(Class_0!AJ50,Class_1!AJ50,Class_2!AJ50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM84" t="str">
+        <f>IF(MIN(Class_0!AK50,Class_1!AK50,Class_2!AK50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN84" t="str">
+        <f>IF(MIN(Class_0!AL50,Class_1!AL50,Class_2!AL50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO84" t="str">
+        <f>IF(MIN(Class_0!AM50,Class_1!AM50,Class_2!AM50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP84" t="str">
+        <f>IF(MIN(Class_0!AN50,Class_1!AN50,Class_2!AN50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ84" t="str">
+        <f>IF(MIN(Class_0!AO50,Class_1!AO50,Class_2!AO50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR84" t="str">
+        <f>IF(MIN(Class_0!AP50,Class_1!AP50,Class_2!AP50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS84" t="str">
+        <f>IF(MIN(Class_0!AQ50,Class_1!AQ50,Class_2!AQ50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT84" t="str">
+        <f>IF(MIN(Class_0!AR50,Class_1!AR50,Class_2!AR50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AU84" t="str">
+        <f>IF(MIN(Class_0!AS50,Class_1!AS50,Class_2!AS50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AV84" t="str">
+        <f>IF(MIN(Class_0!AT50,Class_1!AT50,Class_2!AT50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AW84" t="str">
+        <f>IF(MIN(Class_0!AU50,Class_1!AU50,Class_2!AU50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AX84" t="str">
+        <f>IF(MIN(Class_0!AV50,Class_1!AV50,Class_2!AV50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AY84" t="str">
+        <f>IF(MIN(Class_0!AW50,Class_1!AW50,Class_2!AW50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AZ84" t="str">
+        <f>IF(MIN(Class_0!AX50,Class_1!AX50,Class_2!AX50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="85" spans="2:64" x14ac:dyDescent="0.35">
+      <c r="B85" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C85">
+        <f t="shared" si="7"/>
+        <v>49</v>
+      </c>
+      <c r="D85" t="str">
+        <f>IF(MIN(Class_0!B51,Class_1!B51,Class_2!B51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E85" t="str">
+        <f>IF(MIN(Class_0!C51,Class_1!C51,Class_2!C51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F85" t="str">
+        <f>IF(MIN(Class_0!D51,Class_1!D51,Class_2!D51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G85" t="str">
+        <f>IF(MIN(Class_0!E51,Class_1!E51,Class_2!E51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H85" t="str">
+        <f>IF(MIN(Class_0!F51,Class_1!F51,Class_2!F51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I85" t="str">
+        <f>IF(MIN(Class_0!G51,Class_1!G51,Class_2!G51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J85" t="str">
+        <f>IF(MIN(Class_0!H51,Class_1!H51,Class_2!H51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K85" t="str">
+        <f>IF(MIN(Class_0!I51,Class_1!I51,Class_2!I51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L85" t="str">
+        <f>IF(MIN(Class_0!J51,Class_1!J51,Class_2!J51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M85" t="str">
+        <f>IF(MIN(Class_0!K51,Class_1!K51,Class_2!K51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N85" t="str">
+        <f>IF(MIN(Class_0!L51,Class_1!L51,Class_2!L51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O85" t="str">
+        <f>IF(MIN(Class_0!M51,Class_1!M51,Class_2!M51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P85" t="str">
+        <f>IF(MIN(Class_0!N51,Class_1!N51,Class_2!N51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q85" t="str">
+        <f>IF(MIN(Class_0!O51,Class_1!O51,Class_2!O51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R85" t="str">
+        <f>IF(MIN(Class_0!P51,Class_1!P51,Class_2!P51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S85" t="str">
+        <f>IF(MIN(Class_0!Q51,Class_1!Q51,Class_2!Q51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T85" t="str">
+        <f>IF(MIN(Class_0!R51,Class_1!R51,Class_2!R51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U85" t="str">
+        <f>IF(MIN(Class_0!S51,Class_1!S51,Class_2!S51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V85" t="str">
+        <f>IF(MIN(Class_0!T51,Class_1!T51,Class_2!T51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W85" t="str">
+        <f>IF(MIN(Class_0!U51,Class_1!U51,Class_2!U51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X85" t="str">
+        <f>IF(MIN(Class_0!V51,Class_1!V51,Class_2!V51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y85" t="str">
+        <f>IF(MIN(Class_0!W51,Class_1!W51,Class_2!W51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z85" t="str">
+        <f>IF(MIN(Class_0!X51,Class_1!X51,Class_2!X51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA85" t="str">
+        <f>IF(MIN(Class_0!Y51,Class_1!Y51,Class_2!Y51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB85" t="str">
+        <f>IF(MIN(Class_0!Z51,Class_1!Z51,Class_2!Z51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC85" t="str">
+        <f>IF(MIN(Class_0!AA51,Class_1!AA51,Class_2!AA51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD85" t="str">
+        <f>IF(MIN(Class_0!AB51,Class_1!AB51,Class_2!AB51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE85" t="str">
+        <f>IF(MIN(Class_0!AC51,Class_1!AC51,Class_2!AC51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF85" t="str">
+        <f>IF(MIN(Class_0!AD51,Class_1!AD51,Class_2!AD51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG85" t="str">
+        <f>IF(MIN(Class_0!AE51,Class_1!AE51,Class_2!AE51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH85" t="str">
+        <f>IF(MIN(Class_0!AF51,Class_1!AF51,Class_2!AF51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI85" t="str">
+        <f>IF(MIN(Class_0!AG51,Class_1!AG51,Class_2!AG51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ85" t="str">
+        <f>IF(MIN(Class_0!AH51,Class_1!AH51,Class_2!AH51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK85" t="str">
+        <f>IF(MIN(Class_0!AI51,Class_1!AI51,Class_2!AI51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL85" t="str">
+        <f>IF(MIN(Class_0!AJ51,Class_1!AJ51,Class_2!AJ51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM85" t="str">
+        <f>IF(MIN(Class_0!AK51,Class_1!AK51,Class_2!AK51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN85" t="str">
+        <f>IF(MIN(Class_0!AL51,Class_1!AL51,Class_2!AL51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO85" t="str">
+        <f>IF(MIN(Class_0!AM51,Class_1!AM51,Class_2!AM51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP85" t="str">
+        <f>IF(MIN(Class_0!AN51,Class_1!AN51,Class_2!AN51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ85" t="str">
+        <f>IF(MIN(Class_0!AO51,Class_1!AO51,Class_2!AO51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR85" t="str">
+        <f>IF(MIN(Class_0!AP51,Class_1!AP51,Class_2!AP51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AS85" t="str">
+        <f>IF(MIN(Class_0!AQ51,Class_1!AQ51,Class_2!AQ51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT85" t="str">
+        <f>IF(MIN(Class_0!AR51,Class_1!AR51,Class_2!AR51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AU85" t="str">
+        <f>IF(MIN(Class_0!AS51,Class_1!AS51,Class_2!AS51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV85" t="str">
+        <f>IF(MIN(Class_0!AT51,Class_1!AT51,Class_2!AT51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW85" t="str">
+        <f>IF(MIN(Class_0!AU51,Class_1!AU51,Class_2!AU51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AX85" t="str">
+        <f>IF(MIN(Class_0!AV51,Class_1!AV51,Class_2!AV51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AY85" t="str">
+        <f>IF(MIN(Class_0!AW51,Class_1!AW51,Class_2!AW51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AZ85" t="str">
+        <f>IF(MIN(Class_0!AX51,Class_1!AX51,Class_2!AX51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BA85" t="str">
+        <f>IF(MIN(Class_0!AY51,Class_1!AY51,Class_2!AY51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="86" spans="2:64" x14ac:dyDescent="0.35">
+      <c r="B86" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C86">
+        <f t="shared" si="7"/>
+        <v>50</v>
+      </c>
+      <c r="D86" t="str">
+        <f>IF(MIN(Class_0!B52,Class_1!B52,Class_2!B52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E86" t="str">
+        <f>IF(MIN(Class_0!C52,Class_1!C52,Class_2!C52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F86" t="str">
+        <f>IF(MIN(Class_0!D52,Class_1!D52,Class_2!D52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G86" t="str">
+        <f>IF(MIN(Class_0!E52,Class_1!E52,Class_2!E52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H86" t="str">
+        <f>IF(MIN(Class_0!F52,Class_1!F52,Class_2!F52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I86" t="str">
+        <f>IF(MIN(Class_0!G52,Class_1!G52,Class_2!G52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J86" t="str">
+        <f>IF(MIN(Class_0!H52,Class_1!H52,Class_2!H52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K86" t="str">
+        <f>IF(MIN(Class_0!I52,Class_1!I52,Class_2!I52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L86" t="str">
+        <f>IF(MIN(Class_0!J52,Class_1!J52,Class_2!J52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M86" t="str">
+        <f>IF(MIN(Class_0!K52,Class_1!K52,Class_2!K52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N86" t="str">
+        <f>IF(MIN(Class_0!L52,Class_1!L52,Class_2!L52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O86" t="str">
+        <f>IF(MIN(Class_0!M52,Class_1!M52,Class_2!M52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P86" t="str">
+        <f>IF(MIN(Class_0!N52,Class_1!N52,Class_2!N52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q86" t="str">
+        <f>IF(MIN(Class_0!O52,Class_1!O52,Class_2!O52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R86" t="str">
+        <f>IF(MIN(Class_0!P52,Class_1!P52,Class_2!P52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S86" t="str">
+        <f>IF(MIN(Class_0!Q52,Class_1!Q52,Class_2!Q52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T86" t="str">
+        <f>IF(MIN(Class_0!R52,Class_1!R52,Class_2!R52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U86" t="str">
+        <f>IF(MIN(Class_0!S52,Class_1!S52,Class_2!S52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V86" t="str">
+        <f>IF(MIN(Class_0!T52,Class_1!T52,Class_2!T52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W86" t="str">
+        <f>IF(MIN(Class_0!U52,Class_1!U52,Class_2!U52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X86" t="str">
+        <f>IF(MIN(Class_0!V52,Class_1!V52,Class_2!V52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y86" t="str">
+        <f>IF(MIN(Class_0!W52,Class_1!W52,Class_2!W52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z86" t="str">
+        <f>IF(MIN(Class_0!X52,Class_1!X52,Class_2!X52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA86" t="str">
+        <f>IF(MIN(Class_0!Y52,Class_1!Y52,Class_2!Y52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB86" t="str">
+        <f>IF(MIN(Class_0!Z52,Class_1!Z52,Class_2!Z52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC86" t="str">
+        <f>IF(MIN(Class_0!AA52,Class_1!AA52,Class_2!AA52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD86" t="str">
+        <f>IF(MIN(Class_0!AB52,Class_1!AB52,Class_2!AB52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE86" t="str">
+        <f>IF(MIN(Class_0!AC52,Class_1!AC52,Class_2!AC52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF86" t="str">
+        <f>IF(MIN(Class_0!AD52,Class_1!AD52,Class_2!AD52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG86" t="str">
+        <f>IF(MIN(Class_0!AE52,Class_1!AE52,Class_2!AE52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH86" t="str">
+        <f>IF(MIN(Class_0!AF52,Class_1!AF52,Class_2!AF52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI86" t="str">
+        <f>IF(MIN(Class_0!AG52,Class_1!AG52,Class_2!AG52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ86" t="str">
+        <f>IF(MIN(Class_0!AH52,Class_1!AH52,Class_2!AH52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK86" t="str">
+        <f>IF(MIN(Class_0!AI52,Class_1!AI52,Class_2!AI52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL86" t="str">
+        <f>IF(MIN(Class_0!AJ52,Class_1!AJ52,Class_2!AJ52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM86" t="str">
+        <f>IF(MIN(Class_0!AK52,Class_1!AK52,Class_2!AK52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN86" t="str">
+        <f>IF(MIN(Class_0!AL52,Class_1!AL52,Class_2!AL52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO86" t="str">
+        <f>IF(MIN(Class_0!AM52,Class_1!AM52,Class_2!AM52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP86" t="str">
+        <f>IF(MIN(Class_0!AN52,Class_1!AN52,Class_2!AN52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ86" t="str">
+        <f>IF(MIN(Class_0!AO52,Class_1!AO52,Class_2!AO52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR86" t="str">
+        <f>IF(MIN(Class_0!AP52,Class_1!AP52,Class_2!AP52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AS86" t="str">
+        <f>IF(MIN(Class_0!AQ52,Class_1!AQ52,Class_2!AQ52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AT86" t="str">
+        <f>IF(MIN(Class_0!AR52,Class_1!AR52,Class_2!AR52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AU86" t="str">
+        <f>IF(MIN(Class_0!AS52,Class_1!AS52,Class_2!AS52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV86" t="str">
+        <f>IF(MIN(Class_0!AT52,Class_1!AT52,Class_2!AT52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW86" t="str">
+        <f>IF(MIN(Class_0!AU52,Class_1!AU52,Class_2!AU52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AX86" t="str">
+        <f>IF(MIN(Class_0!AV52,Class_1!AV52,Class_2!AV52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AY86" t="str">
+        <f>IF(MIN(Class_0!AW52,Class_1!AW52,Class_2!AW52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AZ86" t="str">
+        <f>IF(MIN(Class_0!AX52,Class_1!AX52,Class_2!AX52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BA86" t="str">
+        <f>IF(MIN(Class_0!AY52,Class_1!AY52,Class_2!AY52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BB86" t="str">
+        <f>IF(MIN(Class_0!AZ52,Class_1!AZ52,Class_2!AZ52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="87" spans="2:64" x14ac:dyDescent="0.35">
+      <c r="B87" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C87">
+        <f t="shared" si="7"/>
+        <v>51</v>
+      </c>
+      <c r="D87" t="str">
+        <f>IF(MIN(Class_0!B53,Class_1!B53,Class_2!B53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E87" t="str">
+        <f>IF(MIN(Class_0!C53,Class_1!C53,Class_2!C53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F87" t="str">
+        <f>IF(MIN(Class_0!D53,Class_1!D53,Class_2!D53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G87" t="str">
+        <f>IF(MIN(Class_0!E53,Class_1!E53,Class_2!E53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H87" t="str">
+        <f>IF(MIN(Class_0!F53,Class_1!F53,Class_2!F53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I87" t="str">
+        <f>IF(MIN(Class_0!G53,Class_1!G53,Class_2!G53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J87" t="str">
+        <f>IF(MIN(Class_0!H53,Class_1!H53,Class_2!H53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K87" t="str">
+        <f>IF(MIN(Class_0!I53,Class_1!I53,Class_2!I53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L87" t="str">
+        <f>IF(MIN(Class_0!J53,Class_1!J53,Class_2!J53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M87" t="str">
+        <f>IF(MIN(Class_0!K53,Class_1!K53,Class_2!K53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N87" t="str">
+        <f>IF(MIN(Class_0!L53,Class_1!L53,Class_2!L53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O87" t="str">
+        <f>IF(MIN(Class_0!M53,Class_1!M53,Class_2!M53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P87" t="str">
+        <f>IF(MIN(Class_0!N53,Class_1!N53,Class_2!N53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q87" t="str">
+        <f>IF(MIN(Class_0!O53,Class_1!O53,Class_2!O53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R87" t="str">
+        <f>IF(MIN(Class_0!P53,Class_1!P53,Class_2!P53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S87" t="str">
+        <f>IF(MIN(Class_0!Q53,Class_1!Q53,Class_2!Q53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T87" t="str">
+        <f>IF(MIN(Class_0!R53,Class_1!R53,Class_2!R53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U87" t="str">
+        <f>IF(MIN(Class_0!S53,Class_1!S53,Class_2!S53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V87" t="str">
+        <f>IF(MIN(Class_0!T53,Class_1!T53,Class_2!T53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W87" t="str">
+        <f>IF(MIN(Class_0!U53,Class_1!U53,Class_2!U53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X87" t="str">
+        <f>IF(MIN(Class_0!V53,Class_1!V53,Class_2!V53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y87" t="str">
+        <f>IF(MIN(Class_0!W53,Class_1!W53,Class_2!W53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z87" t="str">
+        <f>IF(MIN(Class_0!X53,Class_1!X53,Class_2!X53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA87" t="str">
+        <f>IF(MIN(Class_0!Y53,Class_1!Y53,Class_2!Y53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB87" t="str">
+        <f>IF(MIN(Class_0!Z53,Class_1!Z53,Class_2!Z53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC87" t="str">
+        <f>IF(MIN(Class_0!AA53,Class_1!AA53,Class_2!AA53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD87" t="str">
+        <f>IF(MIN(Class_0!AB53,Class_1!AB53,Class_2!AB53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE87" t="str">
+        <f>IF(MIN(Class_0!AC53,Class_1!AC53,Class_2!AC53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF87" t="str">
+        <f>IF(MIN(Class_0!AD53,Class_1!AD53,Class_2!AD53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG87" t="str">
+        <f>IF(MIN(Class_0!AE53,Class_1!AE53,Class_2!AE53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH87" t="str">
+        <f>IF(MIN(Class_0!AF53,Class_1!AF53,Class_2!AF53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI87" t="str">
+        <f>IF(MIN(Class_0!AG53,Class_1!AG53,Class_2!AG53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ87" t="str">
+        <f>IF(MIN(Class_0!AH53,Class_1!AH53,Class_2!AH53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AK87" t="str">
+        <f>IF(MIN(Class_0!AI53,Class_1!AI53,Class_2!AI53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL87" t="str">
+        <f>IF(MIN(Class_0!AJ53,Class_1!AJ53,Class_2!AJ53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM87" t="str">
+        <f>IF(MIN(Class_0!AK53,Class_1!AK53,Class_2!AK53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN87" t="str">
+        <f>IF(MIN(Class_0!AL53,Class_1!AL53,Class_2!AL53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO87" t="str">
+        <f>IF(MIN(Class_0!AM53,Class_1!AM53,Class_2!AM53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP87" t="str">
+        <f>IF(MIN(Class_0!AN53,Class_1!AN53,Class_2!AN53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ87" t="str">
+        <f>IF(MIN(Class_0!AO53,Class_1!AO53,Class_2!AO53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR87" t="str">
+        <f>IF(MIN(Class_0!AP53,Class_1!AP53,Class_2!AP53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AS87" t="str">
+        <f>IF(MIN(Class_0!AQ53,Class_1!AQ53,Class_2!AQ53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AT87" t="str">
+        <f>IF(MIN(Class_0!AR53,Class_1!AR53,Class_2!AR53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AU87" t="str">
+        <f>IF(MIN(Class_0!AS53,Class_1!AS53,Class_2!AS53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV87" t="str">
+        <f>IF(MIN(Class_0!AT53,Class_1!AT53,Class_2!AT53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW87" t="str">
+        <f>IF(MIN(Class_0!AU53,Class_1!AU53,Class_2!AU53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AX87" t="str">
+        <f>IF(MIN(Class_0!AV53,Class_1!AV53,Class_2!AV53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AY87" t="str">
+        <f>IF(MIN(Class_0!AW53,Class_1!AW53,Class_2!AW53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AZ87" t="str">
+        <f>IF(MIN(Class_0!AX53,Class_1!AX53,Class_2!AX53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BA87" t="str">
+        <f>IF(MIN(Class_0!AY53,Class_1!AY53,Class_2!AY53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BB87" t="str">
+        <f>IF(MIN(Class_0!AZ53,Class_1!AZ53,Class_2!AZ53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BC87" t="str">
+        <f>IF(MIN(Class_0!BA53,Class_1!BA53,Class_2!BA53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="88" spans="2:64" x14ac:dyDescent="0.35">
+      <c r="B88" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C88">
+        <f t="shared" si="7"/>
+        <v>52</v>
+      </c>
+      <c r="D88" t="str">
+        <f>IF(MIN(Class_0!B54,Class_1!B54,Class_2!B54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E88" t="str">
+        <f>IF(MIN(Class_0!C54,Class_1!C54,Class_2!C54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F88" t="str">
+        <f>IF(MIN(Class_0!D54,Class_1!D54,Class_2!D54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G88" t="str">
+        <f>IF(MIN(Class_0!E54,Class_1!E54,Class_2!E54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H88" t="str">
+        <f>IF(MIN(Class_0!F54,Class_1!F54,Class_2!F54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I88" t="str">
+        <f>IF(MIN(Class_0!G54,Class_1!G54,Class_2!G54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="J88" t="str">
+        <f>IF(MIN(Class_0!H54,Class_1!H54,Class_2!H54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K88" t="str">
+        <f>IF(MIN(Class_0!I54,Class_1!I54,Class_2!I54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L88" t="str">
+        <f>IF(MIN(Class_0!J54,Class_1!J54,Class_2!J54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M88" t="str">
+        <f>IF(MIN(Class_0!K54,Class_1!K54,Class_2!K54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N88" t="str">
+        <f>IF(MIN(Class_0!L54,Class_1!L54,Class_2!L54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O88" t="str">
+        <f>IF(MIN(Class_0!M54,Class_1!M54,Class_2!M54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="P88" t="str">
+        <f>IF(MIN(Class_0!N54,Class_1!N54,Class_2!N54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q88" t="str">
+        <f>IF(MIN(Class_0!O54,Class_1!O54,Class_2!O54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R88" t="str">
+        <f>IF(MIN(Class_0!P54,Class_1!P54,Class_2!P54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S88" t="str">
+        <f>IF(MIN(Class_0!Q54,Class_1!Q54,Class_2!Q54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T88" t="str">
+        <f>IF(MIN(Class_0!R54,Class_1!R54,Class_2!R54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U88" t="str">
+        <f>IF(MIN(Class_0!S54,Class_1!S54,Class_2!S54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V88" t="str">
+        <f>IF(MIN(Class_0!T54,Class_1!T54,Class_2!T54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W88" t="str">
+        <f>IF(MIN(Class_0!U54,Class_1!U54,Class_2!U54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X88" t="str">
+        <f>IF(MIN(Class_0!V54,Class_1!V54,Class_2!V54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y88" t="str">
+        <f>IF(MIN(Class_0!W54,Class_1!W54,Class_2!W54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z88" t="str">
+        <f>IF(MIN(Class_0!X54,Class_1!X54,Class_2!X54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA88" t="str">
+        <f>IF(MIN(Class_0!Y54,Class_1!Y54,Class_2!Y54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB88" t="str">
+        <f>IF(MIN(Class_0!Z54,Class_1!Z54,Class_2!Z54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC88" t="str">
+        <f>IF(MIN(Class_0!AA54,Class_1!AA54,Class_2!AA54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD88" t="str">
+        <f>IF(MIN(Class_0!AB54,Class_1!AB54,Class_2!AB54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE88" t="str">
+        <f>IF(MIN(Class_0!AC54,Class_1!AC54,Class_2!AC54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF88" t="str">
+        <f>IF(MIN(Class_0!AD54,Class_1!AD54,Class_2!AD54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG88" t="str">
+        <f>IF(MIN(Class_0!AE54,Class_1!AE54,Class_2!AE54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH88" t="str">
+        <f>IF(MIN(Class_0!AF54,Class_1!AF54,Class_2!AF54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI88" t="str">
+        <f>IF(MIN(Class_0!AG54,Class_1!AG54,Class_2!AG54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ88" t="str">
+        <f>IF(MIN(Class_0!AH54,Class_1!AH54,Class_2!AH54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AK88" t="str">
+        <f>IF(MIN(Class_0!AI54,Class_1!AI54,Class_2!AI54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL88" t="str">
+        <f>IF(MIN(Class_0!AJ54,Class_1!AJ54,Class_2!AJ54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM88" t="str">
+        <f>IF(MIN(Class_0!AK54,Class_1!AK54,Class_2!AK54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN88" t="str">
+        <f>IF(MIN(Class_0!AL54,Class_1!AL54,Class_2!AL54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO88" t="str">
+        <f>IF(MIN(Class_0!AM54,Class_1!AM54,Class_2!AM54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP88" t="str">
+        <f>IF(MIN(Class_0!AN54,Class_1!AN54,Class_2!AN54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ88" t="str">
+        <f>IF(MIN(Class_0!AO54,Class_1!AO54,Class_2!AO54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR88" t="str">
+        <f>IF(MIN(Class_0!AP54,Class_1!AP54,Class_2!AP54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AS88" t="str">
+        <f>IF(MIN(Class_0!AQ54,Class_1!AQ54,Class_2!AQ54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AT88" t="str">
+        <f>IF(MIN(Class_0!AR54,Class_1!AR54,Class_2!AR54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AU88" t="str">
+        <f>IF(MIN(Class_0!AS54,Class_1!AS54,Class_2!AS54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV88" t="str">
+        <f>IF(MIN(Class_0!AT54,Class_1!AT54,Class_2!AT54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW88" t="str">
+        <f>IF(MIN(Class_0!AU54,Class_1!AU54,Class_2!AU54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AX88" t="str">
+        <f>IF(MIN(Class_0!AV54,Class_1!AV54,Class_2!AV54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AY88" t="str">
+        <f>IF(MIN(Class_0!AW54,Class_1!AW54,Class_2!AW54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AZ88" t="str">
+        <f>IF(MIN(Class_0!AX54,Class_1!AX54,Class_2!AX54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BA88" t="str">
+        <f>IF(MIN(Class_0!AY54,Class_1!AY54,Class_2!AY54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BB88" t="str">
+        <f>IF(MIN(Class_0!AZ54,Class_1!AZ54,Class_2!AZ54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BC88" t="str">
+        <f>IF(MIN(Class_0!BA54,Class_1!BA54,Class_2!BA54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BD88" t="str">
+        <f>IF(MIN(Class_0!BB54,Class_1!BB54,Class_2!BB54)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="89" spans="2:64" x14ac:dyDescent="0.35">
+      <c r="B89" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C89">
+        <f t="shared" si="7"/>
+        <v>53</v>
+      </c>
+      <c r="D89" t="str">
+        <f>IF(MIN(Class_0!B55,Class_1!B55,Class_2!B55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E89" t="str">
+        <f>IF(MIN(Class_0!C55,Class_1!C55,Class_2!C55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F89" t="str">
+        <f>IF(MIN(Class_0!D55,Class_1!D55,Class_2!D55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G89" t="str">
+        <f>IF(MIN(Class_0!E55,Class_1!E55,Class_2!E55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H89" t="str">
+        <f>IF(MIN(Class_0!F55,Class_1!F55,Class_2!F55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I89" t="str">
+        <f>IF(MIN(Class_0!G55,Class_1!G55,Class_2!G55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J89" t="str">
+        <f>IF(MIN(Class_0!H55,Class_1!H55,Class_2!H55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K89" t="str">
+        <f>IF(MIN(Class_0!I55,Class_1!I55,Class_2!I55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="L89" t="str">
+        <f>IF(MIN(Class_0!J55,Class_1!J55,Class_2!J55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M89" t="str">
+        <f>IF(MIN(Class_0!K55,Class_1!K55,Class_2!K55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N89" t="str">
+        <f>IF(MIN(Class_0!L55,Class_1!L55,Class_2!L55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O89" t="str">
+        <f>IF(MIN(Class_0!M55,Class_1!M55,Class_2!M55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P89" t="str">
+        <f>IF(MIN(Class_0!N55,Class_1!N55,Class_2!N55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q89" t="str">
+        <f>IF(MIN(Class_0!O55,Class_1!O55,Class_2!O55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R89" t="str">
+        <f>IF(MIN(Class_0!P55,Class_1!P55,Class_2!P55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S89" t="str">
+        <f>IF(MIN(Class_0!Q55,Class_1!Q55,Class_2!Q55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T89" t="str">
+        <f>IF(MIN(Class_0!R55,Class_1!R55,Class_2!R55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U89" t="str">
+        <f>IF(MIN(Class_0!S55,Class_1!S55,Class_2!S55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V89" t="str">
+        <f>IF(MIN(Class_0!T55,Class_1!T55,Class_2!T55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W89" t="str">
+        <f>IF(MIN(Class_0!U55,Class_1!U55,Class_2!U55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X89" t="str">
+        <f>IF(MIN(Class_0!V55,Class_1!V55,Class_2!V55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y89" t="str">
+        <f>IF(MIN(Class_0!W55,Class_1!W55,Class_2!W55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z89" t="str">
+        <f>IF(MIN(Class_0!X55,Class_1!X55,Class_2!X55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA89" t="str">
+        <f>IF(MIN(Class_0!Y55,Class_1!Y55,Class_2!Y55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB89" t="str">
+        <f>IF(MIN(Class_0!Z55,Class_1!Z55,Class_2!Z55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC89" t="str">
+        <f>IF(MIN(Class_0!AA55,Class_1!AA55,Class_2!AA55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD89" t="str">
+        <f>IF(MIN(Class_0!AB55,Class_1!AB55,Class_2!AB55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE89" t="str">
+        <f>IF(MIN(Class_0!AC55,Class_1!AC55,Class_2!AC55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF89" t="str">
+        <f>IF(MIN(Class_0!AD55,Class_1!AD55,Class_2!AD55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG89" t="str">
+        <f>IF(MIN(Class_0!AE55,Class_1!AE55,Class_2!AE55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH89" t="str">
+        <f>IF(MIN(Class_0!AF55,Class_1!AF55,Class_2!AF55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI89" t="str">
+        <f>IF(MIN(Class_0!AG55,Class_1!AG55,Class_2!AG55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ89" t="str">
+        <f>IF(MIN(Class_0!AH55,Class_1!AH55,Class_2!AH55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AK89" t="str">
+        <f>IF(MIN(Class_0!AI55,Class_1!AI55,Class_2!AI55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL89" t="str">
+        <f>IF(MIN(Class_0!AJ55,Class_1!AJ55,Class_2!AJ55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM89" t="str">
+        <f>IF(MIN(Class_0!AK55,Class_1!AK55,Class_2!AK55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN89" t="str">
+        <f>IF(MIN(Class_0!AL55,Class_1!AL55,Class_2!AL55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO89" t="str">
+        <f>IF(MIN(Class_0!AM55,Class_1!AM55,Class_2!AM55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP89" t="str">
+        <f>IF(MIN(Class_0!AN55,Class_1!AN55,Class_2!AN55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ89" t="str">
+        <f>IF(MIN(Class_0!AO55,Class_1!AO55,Class_2!AO55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR89" t="str">
+        <f>IF(MIN(Class_0!AP55,Class_1!AP55,Class_2!AP55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS89" t="str">
+        <f>IF(MIN(Class_0!AQ55,Class_1!AQ55,Class_2!AQ55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT89" t="str">
+        <f>IF(MIN(Class_0!AR55,Class_1!AR55,Class_2!AR55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AU89" t="str">
+        <f>IF(MIN(Class_0!AS55,Class_1!AS55,Class_2!AS55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV89" t="str">
+        <f>IF(MIN(Class_0!AT55,Class_1!AT55,Class_2!AT55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW89" t="str">
+        <f>IF(MIN(Class_0!AU55,Class_1!AU55,Class_2!AU55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AX89" t="str">
+        <f>IF(MIN(Class_0!AV55,Class_1!AV55,Class_2!AV55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AY89" t="str">
+        <f>IF(MIN(Class_0!AW55,Class_1!AW55,Class_2!AW55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AZ89" t="str">
+        <f>IF(MIN(Class_0!AX55,Class_1!AX55,Class_2!AX55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BA89" t="str">
+        <f>IF(MIN(Class_0!AY55,Class_1!AY55,Class_2!AY55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BB89" t="str">
+        <f>IF(MIN(Class_0!AZ55,Class_1!AZ55,Class_2!AZ55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BC89" t="str">
+        <f>IF(MIN(Class_0!BA55,Class_1!BA55,Class_2!BA55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BD89" t="str">
+        <f>IF(MIN(Class_0!BB55,Class_1!BB55,Class_2!BB55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BE89" t="str">
+        <f>IF(MIN(Class_0!BC55,Class_1!BC55,Class_2!BC55)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="90" spans="2:64" x14ac:dyDescent="0.35">
+      <c r="B90" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C90">
+        <f t="shared" si="7"/>
+        <v>54</v>
+      </c>
+      <c r="D90" t="str">
+        <f>IF(MIN(Class_0!B56,Class_1!B56,Class_2!B56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E90" t="str">
+        <f>IF(MIN(Class_0!C56,Class_1!C56,Class_2!C56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F90" t="str">
+        <f>IF(MIN(Class_0!D56,Class_1!D56,Class_2!D56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G90" t="str">
+        <f>IF(MIN(Class_0!E56,Class_1!E56,Class_2!E56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H90" t="str">
+        <f>IF(MIN(Class_0!F56,Class_1!F56,Class_2!F56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I90" t="str">
+        <f>IF(MIN(Class_0!G56,Class_1!G56,Class_2!G56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J90" t="str">
+        <f>IF(MIN(Class_0!H56,Class_1!H56,Class_2!H56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K90" t="str">
+        <f>IF(MIN(Class_0!I56,Class_1!I56,Class_2!I56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L90" t="str">
+        <f>IF(MIN(Class_0!J56,Class_1!J56,Class_2!J56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M90" t="str">
+        <f>IF(MIN(Class_0!K56,Class_1!K56,Class_2!K56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N90" t="str">
+        <f>IF(MIN(Class_0!L56,Class_1!L56,Class_2!L56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="O90" t="str">
+        <f>IF(MIN(Class_0!M56,Class_1!M56,Class_2!M56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P90" t="str">
+        <f>IF(MIN(Class_0!N56,Class_1!N56,Class_2!N56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Q90" t="str">
+        <f>IF(MIN(Class_0!O56,Class_1!O56,Class_2!O56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R90" t="str">
+        <f>IF(MIN(Class_0!P56,Class_1!P56,Class_2!P56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S90" t="str">
+        <f>IF(MIN(Class_0!Q56,Class_1!Q56,Class_2!Q56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T90" t="str">
+        <f>IF(MIN(Class_0!R56,Class_1!R56,Class_2!R56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U90" t="str">
+        <f>IF(MIN(Class_0!S56,Class_1!S56,Class_2!S56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V90" t="str">
+        <f>IF(MIN(Class_0!T56,Class_1!T56,Class_2!T56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W90" t="str">
+        <f>IF(MIN(Class_0!U56,Class_1!U56,Class_2!U56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X90" t="str">
+        <f>IF(MIN(Class_0!V56,Class_1!V56,Class_2!V56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y90" t="str">
+        <f>IF(MIN(Class_0!W56,Class_1!W56,Class_2!W56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z90" t="str">
+        <f>IF(MIN(Class_0!X56,Class_1!X56,Class_2!X56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA90" t="str">
+        <f>IF(MIN(Class_0!Y56,Class_1!Y56,Class_2!Y56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB90" t="str">
+        <f>IF(MIN(Class_0!Z56,Class_1!Z56,Class_2!Z56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC90" t="str">
+        <f>IF(MIN(Class_0!AA56,Class_1!AA56,Class_2!AA56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD90" t="str">
+        <f>IF(MIN(Class_0!AB56,Class_1!AB56,Class_2!AB56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE90" t="str">
+        <f>IF(MIN(Class_0!AC56,Class_1!AC56,Class_2!AC56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF90" t="str">
+        <f>IF(MIN(Class_0!AD56,Class_1!AD56,Class_2!AD56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG90" t="str">
+        <f>IF(MIN(Class_0!AE56,Class_1!AE56,Class_2!AE56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH90" t="str">
+        <f>IF(MIN(Class_0!AF56,Class_1!AF56,Class_2!AF56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI90" t="str">
+        <f>IF(MIN(Class_0!AG56,Class_1!AG56,Class_2!AG56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ90" t="str">
+        <f>IF(MIN(Class_0!AH56,Class_1!AH56,Class_2!AH56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AK90" t="str">
+        <f>IF(MIN(Class_0!AI56,Class_1!AI56,Class_2!AI56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL90" t="str">
+        <f>IF(MIN(Class_0!AJ56,Class_1!AJ56,Class_2!AJ56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM90" t="str">
+        <f>IF(MIN(Class_0!AK56,Class_1!AK56,Class_2!AK56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN90" t="str">
+        <f>IF(MIN(Class_0!AL56,Class_1!AL56,Class_2!AL56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO90" t="str">
+        <f>IF(MIN(Class_0!AM56,Class_1!AM56,Class_2!AM56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP90" t="str">
+        <f>IF(MIN(Class_0!AN56,Class_1!AN56,Class_2!AN56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ90" t="str">
+        <f>IF(MIN(Class_0!AO56,Class_1!AO56,Class_2!AO56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR90" t="str">
+        <f>IF(MIN(Class_0!AP56,Class_1!AP56,Class_2!AP56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS90" t="str">
+        <f>IF(MIN(Class_0!AQ56,Class_1!AQ56,Class_2!AQ56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT90" t="str">
+        <f>IF(MIN(Class_0!AR56,Class_1!AR56,Class_2!AR56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AU90" t="str">
+        <f>IF(MIN(Class_0!AS56,Class_1!AS56,Class_2!AS56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV90" t="str">
+        <f>IF(MIN(Class_0!AT56,Class_1!AT56,Class_2!AT56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW90" t="str">
+        <f>IF(MIN(Class_0!AU56,Class_1!AU56,Class_2!AU56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AX90" t="str">
+        <f>IF(MIN(Class_0!AV56,Class_1!AV56,Class_2!AV56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AY90" t="str">
+        <f>IF(MIN(Class_0!AW56,Class_1!AW56,Class_2!AW56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AZ90" t="str">
+        <f>IF(MIN(Class_0!AX56,Class_1!AX56,Class_2!AX56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BA90" t="str">
+        <f>IF(MIN(Class_0!AY56,Class_1!AY56,Class_2!AY56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BB90" t="str">
+        <f>IF(MIN(Class_0!AZ56,Class_1!AZ56,Class_2!AZ56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BC90" t="str">
+        <f>IF(MIN(Class_0!BA56,Class_1!BA56,Class_2!BA56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BD90" t="str">
+        <f>IF(MIN(Class_0!BB56,Class_1!BB56,Class_2!BB56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BE90" t="str">
+        <f>IF(MIN(Class_0!BC56,Class_1!BC56,Class_2!BC56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BF90" t="str">
+        <f>IF(MIN(Class_0!BD56,Class_1!BD56,Class_2!BD56)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="91" spans="2:64" x14ac:dyDescent="0.35">
+      <c r="B91" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C91">
+        <f t="shared" si="7"/>
+        <v>55</v>
+      </c>
+      <c r="D91" t="str">
+        <f>IF(MIN(Class_0!B57,Class_1!B57,Class_2!B57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E91" t="str">
+        <f>IF(MIN(Class_0!C57,Class_1!C57,Class_2!C57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F91" t="str">
+        <f>IF(MIN(Class_0!D57,Class_1!D57,Class_2!D57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G91" t="str">
+        <f>IF(MIN(Class_0!E57,Class_1!E57,Class_2!E57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H91" t="str">
+        <f>IF(MIN(Class_0!F57,Class_1!F57,Class_2!F57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I91" t="str">
+        <f>IF(MIN(Class_0!G57,Class_1!G57,Class_2!G57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J91" t="str">
+        <f>IF(MIN(Class_0!H57,Class_1!H57,Class_2!H57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K91" t="str">
+        <f>IF(MIN(Class_0!I57,Class_1!I57,Class_2!I57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="L91" t="str">
+        <f>IF(MIN(Class_0!J57,Class_1!J57,Class_2!J57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M91" t="str">
+        <f>IF(MIN(Class_0!K57,Class_1!K57,Class_2!K57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N91" t="str">
+        <f>IF(MIN(Class_0!L57,Class_1!L57,Class_2!L57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O91" t="str">
+        <f>IF(MIN(Class_0!M57,Class_1!M57,Class_2!M57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P91" t="str">
+        <f>IF(MIN(Class_0!N57,Class_1!N57,Class_2!N57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q91" t="str">
+        <f>IF(MIN(Class_0!O57,Class_1!O57,Class_2!O57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R91" t="str">
+        <f>IF(MIN(Class_0!P57,Class_1!P57,Class_2!P57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S91" t="str">
+        <f>IF(MIN(Class_0!Q57,Class_1!Q57,Class_2!Q57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T91" t="str">
+        <f>IF(MIN(Class_0!R57,Class_1!R57,Class_2!R57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U91" t="str">
+        <f>IF(MIN(Class_0!S57,Class_1!S57,Class_2!S57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="V91" t="str">
+        <f>IF(MIN(Class_0!T57,Class_1!T57,Class_2!T57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W91" t="str">
+        <f>IF(MIN(Class_0!U57,Class_1!U57,Class_2!U57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X91" t="str">
+        <f>IF(MIN(Class_0!V57,Class_1!V57,Class_2!V57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y91" t="str">
+        <f>IF(MIN(Class_0!W57,Class_1!W57,Class_2!W57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Z91" t="str">
+        <f>IF(MIN(Class_0!X57,Class_1!X57,Class_2!X57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA91" t="str">
+        <f>IF(MIN(Class_0!Y57,Class_1!Y57,Class_2!Y57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB91" t="str">
+        <f>IF(MIN(Class_0!Z57,Class_1!Z57,Class_2!Z57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC91" t="str">
+        <f>IF(MIN(Class_0!AA57,Class_1!AA57,Class_2!AA57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD91" t="str">
+        <f>IF(MIN(Class_0!AB57,Class_1!AB57,Class_2!AB57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE91" t="str">
+        <f>IF(MIN(Class_0!AC57,Class_1!AC57,Class_2!AC57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF91" t="str">
+        <f>IF(MIN(Class_0!AD57,Class_1!AD57,Class_2!AD57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG91" t="str">
+        <f>IF(MIN(Class_0!AE57,Class_1!AE57,Class_2!AE57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH91" t="str">
+        <f>IF(MIN(Class_0!AF57,Class_1!AF57,Class_2!AF57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI91" t="str">
+        <f>IF(MIN(Class_0!AG57,Class_1!AG57,Class_2!AG57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ91" t="str">
+        <f>IF(MIN(Class_0!AH57,Class_1!AH57,Class_2!AH57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AK91" t="str">
+        <f>IF(MIN(Class_0!AI57,Class_1!AI57,Class_2!AI57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL91" t="str">
+        <f>IF(MIN(Class_0!AJ57,Class_1!AJ57,Class_2!AJ57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM91" t="str">
+        <f>IF(MIN(Class_0!AK57,Class_1!AK57,Class_2!AK57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AN91" t="str">
+        <f>IF(MIN(Class_0!AL57,Class_1!AL57,Class_2!AL57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO91" t="str">
+        <f>IF(MIN(Class_0!AM57,Class_1!AM57,Class_2!AM57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP91" t="str">
+        <f>IF(MIN(Class_0!AN57,Class_1!AN57,Class_2!AN57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ91" t="str">
+        <f>IF(MIN(Class_0!AO57,Class_1!AO57,Class_2!AO57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR91" t="str">
+        <f>IF(MIN(Class_0!AP57,Class_1!AP57,Class_2!AP57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS91" t="str">
+        <f>IF(MIN(Class_0!AQ57,Class_1!AQ57,Class_2!AQ57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AT91" t="str">
+        <f>IF(MIN(Class_0!AR57,Class_1!AR57,Class_2!AR57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AU91" t="str">
+        <f>IF(MIN(Class_0!AS57,Class_1!AS57,Class_2!AS57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV91" t="str">
+        <f>IF(MIN(Class_0!AT57,Class_1!AT57,Class_2!AT57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW91" t="str">
+        <f>IF(MIN(Class_0!AU57,Class_1!AU57,Class_2!AU57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AX91" t="str">
+        <f>IF(MIN(Class_0!AV57,Class_1!AV57,Class_2!AV57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AY91" t="str">
+        <f>IF(MIN(Class_0!AW57,Class_1!AW57,Class_2!AW57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AZ91" t="str">
+        <f>IF(MIN(Class_0!AX57,Class_1!AX57,Class_2!AX57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BA91" t="str">
+        <f>IF(MIN(Class_0!AY57,Class_1!AY57,Class_2!AY57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BB91" t="str">
+        <f>IF(MIN(Class_0!AZ57,Class_1!AZ57,Class_2!AZ57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BC91" t="str">
+        <f>IF(MIN(Class_0!BA57,Class_1!BA57,Class_2!BA57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BD91" t="str">
+        <f>IF(MIN(Class_0!BB57,Class_1!BB57,Class_2!BB57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BE91" t="str">
+        <f>IF(MIN(Class_0!BC57,Class_1!BC57,Class_2!BC57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BF91" t="str">
+        <f>IF(MIN(Class_0!BD57,Class_1!BD57,Class_2!BD57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BG91" t="str">
+        <f>IF(MIN(Class_0!BE57,Class_1!BE57,Class_2!BE57)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="92" spans="2:64" x14ac:dyDescent="0.35">
+      <c r="B92" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C92">
+        <f t="shared" si="7"/>
+        <v>56</v>
+      </c>
+      <c r="D92" t="str">
+        <f>IF(MIN(Class_0!B58,Class_1!B58,Class_2!B58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E92" t="str">
+        <f>IF(MIN(Class_0!C58,Class_1!C58,Class_2!C58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F92" t="str">
+        <f>IF(MIN(Class_0!D58,Class_1!D58,Class_2!D58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G92" t="str">
+        <f>IF(MIN(Class_0!E58,Class_1!E58,Class_2!E58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H92" t="str">
+        <f>IF(MIN(Class_0!F58,Class_1!F58,Class_2!F58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I92" t="str">
+        <f>IF(MIN(Class_0!G58,Class_1!G58,Class_2!G58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="J92" t="str">
+        <f>IF(MIN(Class_0!H58,Class_1!H58,Class_2!H58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K92" t="str">
+        <f>IF(MIN(Class_0!I58,Class_1!I58,Class_2!I58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="L92" t="str">
+        <f>IF(MIN(Class_0!J58,Class_1!J58,Class_2!J58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M92" t="str">
+        <f>IF(MIN(Class_0!K58,Class_1!K58,Class_2!K58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N92" t="str">
+        <f>IF(MIN(Class_0!L58,Class_1!L58,Class_2!L58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="O92" t="str">
+        <f>IF(MIN(Class_0!M58,Class_1!M58,Class_2!M58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P92" t="str">
+        <f>IF(MIN(Class_0!N58,Class_1!N58,Class_2!N58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q92" t="str">
+        <f>IF(MIN(Class_0!O58,Class_1!O58,Class_2!O58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R92" t="str">
+        <f>IF(MIN(Class_0!P58,Class_1!P58,Class_2!P58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S92" t="str">
+        <f>IF(MIN(Class_0!Q58,Class_1!Q58,Class_2!Q58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T92" t="str">
+        <f>IF(MIN(Class_0!R58,Class_1!R58,Class_2!R58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U92" t="str">
+        <f>IF(MIN(Class_0!S58,Class_1!S58,Class_2!S58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V92" t="str">
+        <f>IF(MIN(Class_0!T58,Class_1!T58,Class_2!T58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W92" t="str">
+        <f>IF(MIN(Class_0!U58,Class_1!U58,Class_2!U58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X92" t="str">
+        <f>IF(MIN(Class_0!V58,Class_1!V58,Class_2!V58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y92" t="str">
+        <f>IF(MIN(Class_0!W58,Class_1!W58,Class_2!W58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z92" t="str">
+        <f>IF(MIN(Class_0!X58,Class_1!X58,Class_2!X58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA92" t="str">
+        <f>IF(MIN(Class_0!Y58,Class_1!Y58,Class_2!Y58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB92" t="str">
+        <f>IF(MIN(Class_0!Z58,Class_1!Z58,Class_2!Z58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC92" t="str">
+        <f>IF(MIN(Class_0!AA58,Class_1!AA58,Class_2!AA58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD92" t="str">
+        <f>IF(MIN(Class_0!AB58,Class_1!AB58,Class_2!AB58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE92" t="str">
+        <f>IF(MIN(Class_0!AC58,Class_1!AC58,Class_2!AC58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF92" t="str">
+        <f>IF(MIN(Class_0!AD58,Class_1!AD58,Class_2!AD58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG92" t="str">
+        <f>IF(MIN(Class_0!AE58,Class_1!AE58,Class_2!AE58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH92" t="str">
+        <f>IF(MIN(Class_0!AF58,Class_1!AF58,Class_2!AF58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI92" t="str">
+        <f>IF(MIN(Class_0!AG58,Class_1!AG58,Class_2!AG58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ92" t="str">
+        <f>IF(MIN(Class_0!AH58,Class_1!AH58,Class_2!AH58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK92" t="str">
+        <f>IF(MIN(Class_0!AI58,Class_1!AI58,Class_2!AI58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL92" t="str">
+        <f>IF(MIN(Class_0!AJ58,Class_1!AJ58,Class_2!AJ58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM92" t="str">
+        <f>IF(MIN(Class_0!AK58,Class_1!AK58,Class_2!AK58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN92" t="str">
+        <f>IF(MIN(Class_0!AL58,Class_1!AL58,Class_2!AL58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO92" t="str">
+        <f>IF(MIN(Class_0!AM58,Class_1!AM58,Class_2!AM58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP92" t="str">
+        <f>IF(MIN(Class_0!AN58,Class_1!AN58,Class_2!AN58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ92" t="str">
+        <f>IF(MIN(Class_0!AO58,Class_1!AO58,Class_2!AO58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR92" t="str">
+        <f>IF(MIN(Class_0!AP58,Class_1!AP58,Class_2!AP58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AS92" t="str">
+        <f>IF(MIN(Class_0!AQ58,Class_1!AQ58,Class_2!AQ58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AT92" t="str">
+        <f>IF(MIN(Class_0!AR58,Class_1!AR58,Class_2!AR58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AU92" t="str">
+        <f>IF(MIN(Class_0!AS58,Class_1!AS58,Class_2!AS58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV92" t="str">
+        <f>IF(MIN(Class_0!AT58,Class_1!AT58,Class_2!AT58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW92" t="str">
+        <f>IF(MIN(Class_0!AU58,Class_1!AU58,Class_2!AU58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AX92" t="str">
+        <f>IF(MIN(Class_0!AV58,Class_1!AV58,Class_2!AV58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AY92" t="str">
+        <f>IF(MIN(Class_0!AW58,Class_1!AW58,Class_2!AW58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AZ92" t="str">
+        <f>IF(MIN(Class_0!AX58,Class_1!AX58,Class_2!AX58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BA92" t="str">
+        <f>IF(MIN(Class_0!AY58,Class_1!AY58,Class_2!AY58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BB92" t="str">
+        <f>IF(MIN(Class_0!AZ58,Class_1!AZ58,Class_2!AZ58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BC92" t="str">
+        <f>IF(MIN(Class_0!BA58,Class_1!BA58,Class_2!BA58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BD92" t="str">
+        <f>IF(MIN(Class_0!BB58,Class_1!BB58,Class_2!BB58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BE92" t="str">
+        <f>IF(MIN(Class_0!BC58,Class_1!BC58,Class_2!BC58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BF92" t="str">
+        <f>IF(MIN(Class_0!BD58,Class_1!BD58,Class_2!BD58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BG92" t="str">
+        <f>IF(MIN(Class_0!BE58,Class_1!BE58,Class_2!BE58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BH92" t="str">
+        <f>IF(MIN(Class_0!BF58,Class_1!BF58,Class_2!BF58)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="93" spans="2:64" x14ac:dyDescent="0.35">
+      <c r="B93" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C93">
+        <f t="shared" si="7"/>
+        <v>57</v>
+      </c>
+      <c r="D93" t="str">
+        <f>IF(MIN(Class_0!B59,Class_1!B59,Class_2!B59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E93" t="str">
+        <f>IF(MIN(Class_0!C59,Class_1!C59,Class_2!C59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F93" t="str">
+        <f>IF(MIN(Class_0!D59,Class_1!D59,Class_2!D59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G93" t="str">
+        <f>IF(MIN(Class_0!E59,Class_1!E59,Class_2!E59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H93" t="str">
+        <f>IF(MIN(Class_0!F59,Class_1!F59,Class_2!F59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I93" t="str">
+        <f>IF(MIN(Class_0!G59,Class_1!G59,Class_2!G59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J93" t="str">
+        <f>IF(MIN(Class_0!H59,Class_1!H59,Class_2!H59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K93" t="str">
+        <f>IF(MIN(Class_0!I59,Class_1!I59,Class_2!I59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L93" t="str">
+        <f>IF(MIN(Class_0!J59,Class_1!J59,Class_2!J59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M93" t="str">
+        <f>IF(MIN(Class_0!K59,Class_1!K59,Class_2!K59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N93" t="str">
+        <f>IF(MIN(Class_0!L59,Class_1!L59,Class_2!L59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O93" t="str">
+        <f>IF(MIN(Class_0!M59,Class_1!M59,Class_2!M59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P93" t="str">
+        <f>IF(MIN(Class_0!N59,Class_1!N59,Class_2!N59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q93" t="str">
+        <f>IF(MIN(Class_0!O59,Class_1!O59,Class_2!O59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R93" t="str">
+        <f>IF(MIN(Class_0!P59,Class_1!P59,Class_2!P59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S93" t="str">
+        <f>IF(MIN(Class_0!Q59,Class_1!Q59,Class_2!Q59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T93" t="str">
+        <f>IF(MIN(Class_0!R59,Class_1!R59,Class_2!R59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U93" t="str">
+        <f>IF(MIN(Class_0!S59,Class_1!S59,Class_2!S59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V93" t="str">
+        <f>IF(MIN(Class_0!T59,Class_1!T59,Class_2!T59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W93" t="str">
+        <f>IF(MIN(Class_0!U59,Class_1!U59,Class_2!U59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X93" t="str">
+        <f>IF(MIN(Class_0!V59,Class_1!V59,Class_2!V59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y93" t="str">
+        <f>IF(MIN(Class_0!W59,Class_1!W59,Class_2!W59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z93" t="str">
+        <f>IF(MIN(Class_0!X59,Class_1!X59,Class_2!X59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA93" t="str">
+        <f>IF(MIN(Class_0!Y59,Class_1!Y59,Class_2!Y59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB93" t="str">
+        <f>IF(MIN(Class_0!Z59,Class_1!Z59,Class_2!Z59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC93" t="str">
+        <f>IF(MIN(Class_0!AA59,Class_1!AA59,Class_2!AA59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD93" t="str">
+        <f>IF(MIN(Class_0!AB59,Class_1!AB59,Class_2!AB59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE93" t="str">
+        <f>IF(MIN(Class_0!AC59,Class_1!AC59,Class_2!AC59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF93" t="str">
+        <f>IF(MIN(Class_0!AD59,Class_1!AD59,Class_2!AD59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG93" t="str">
+        <f>IF(MIN(Class_0!AE59,Class_1!AE59,Class_2!AE59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH93" t="str">
+        <f>IF(MIN(Class_0!AF59,Class_1!AF59,Class_2!AF59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI93" t="str">
+        <f>IF(MIN(Class_0!AG59,Class_1!AG59,Class_2!AG59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ93" t="str">
+        <f>IF(MIN(Class_0!AH59,Class_1!AH59,Class_2!AH59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK93" t="str">
+        <f>IF(MIN(Class_0!AI59,Class_1!AI59,Class_2!AI59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL93" t="str">
+        <f>IF(MIN(Class_0!AJ59,Class_1!AJ59,Class_2!AJ59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM93" t="str">
+        <f>IF(MIN(Class_0!AK59,Class_1!AK59,Class_2!AK59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN93" t="str">
+        <f>IF(MIN(Class_0!AL59,Class_1!AL59,Class_2!AL59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO93" t="str">
+        <f>IF(MIN(Class_0!AM59,Class_1!AM59,Class_2!AM59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP93" t="str">
+        <f>IF(MIN(Class_0!AN59,Class_1!AN59,Class_2!AN59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ93" t="str">
+        <f>IF(MIN(Class_0!AO59,Class_1!AO59,Class_2!AO59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR93" t="str">
+        <f>IF(MIN(Class_0!AP59,Class_1!AP59,Class_2!AP59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AS93" t="str">
+        <f>IF(MIN(Class_0!AQ59,Class_1!AQ59,Class_2!AQ59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AT93" t="str">
+        <f>IF(MIN(Class_0!AR59,Class_1!AR59,Class_2!AR59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AU93" t="str">
+        <f>IF(MIN(Class_0!AS59,Class_1!AS59,Class_2!AS59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV93" t="str">
+        <f>IF(MIN(Class_0!AT59,Class_1!AT59,Class_2!AT59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW93" t="str">
+        <f>IF(MIN(Class_0!AU59,Class_1!AU59,Class_2!AU59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AX93" t="str">
+        <f>IF(MIN(Class_0!AV59,Class_1!AV59,Class_2!AV59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AY93" t="str">
+        <f>IF(MIN(Class_0!AW59,Class_1!AW59,Class_2!AW59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AZ93" t="str">
+        <f>IF(MIN(Class_0!AX59,Class_1!AX59,Class_2!AX59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BA93" t="str">
+        <f>IF(MIN(Class_0!AY59,Class_1!AY59,Class_2!AY59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BB93" t="str">
+        <f>IF(MIN(Class_0!AZ59,Class_1!AZ59,Class_2!AZ59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BC93" t="str">
+        <f>IF(MIN(Class_0!BA59,Class_1!BA59,Class_2!BA59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BD93" t="str">
+        <f>IF(MIN(Class_0!BB59,Class_1!BB59,Class_2!BB59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BE93" t="str">
+        <f>IF(MIN(Class_0!BC59,Class_1!BC59,Class_2!BC59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BF93" t="str">
+        <f>IF(MIN(Class_0!BD59,Class_1!BD59,Class_2!BD59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BG93" t="str">
+        <f>IF(MIN(Class_0!BE59,Class_1!BE59,Class_2!BE59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BH93" t="str">
+        <f>IF(MIN(Class_0!BF59,Class_1!BF59,Class_2!BF59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BI93" t="str">
+        <f>IF(MIN(Class_0!BG59,Class_1!BG59,Class_2!BG59)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="94" spans="2:64" x14ac:dyDescent="0.35">
+      <c r="B94" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C94">
+        <f t="shared" si="7"/>
+        <v>58</v>
+      </c>
+      <c r="D94" t="str">
+        <f>IF(MIN(Class_0!B60,Class_1!B60,Class_2!B60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E94" t="str">
+        <f>IF(MIN(Class_0!C60,Class_1!C60,Class_2!C60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F94" t="str">
+        <f>IF(MIN(Class_0!D60,Class_1!D60,Class_2!D60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G94" t="str">
+        <f>IF(MIN(Class_0!E60,Class_1!E60,Class_2!E60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H94" t="str">
+        <f>IF(MIN(Class_0!F60,Class_1!F60,Class_2!F60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I94" t="str">
+        <f>IF(MIN(Class_0!G60,Class_1!G60,Class_2!G60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J94" t="str">
+        <f>IF(MIN(Class_0!H60,Class_1!H60,Class_2!H60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K94" t="str">
+        <f>IF(MIN(Class_0!I60,Class_1!I60,Class_2!I60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="L94" t="str">
+        <f>IF(MIN(Class_0!J60,Class_1!J60,Class_2!J60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M94" t="str">
+        <f>IF(MIN(Class_0!K60,Class_1!K60,Class_2!K60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N94" t="str">
+        <f>IF(MIN(Class_0!L60,Class_1!L60,Class_2!L60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O94" t="str">
+        <f>IF(MIN(Class_0!M60,Class_1!M60,Class_2!M60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P94" t="str">
+        <f>IF(MIN(Class_0!N60,Class_1!N60,Class_2!N60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q94" t="str">
+        <f>IF(MIN(Class_0!O60,Class_1!O60,Class_2!O60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R94" t="str">
+        <f>IF(MIN(Class_0!P60,Class_1!P60,Class_2!P60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S94" t="str">
+        <f>IF(MIN(Class_0!Q60,Class_1!Q60,Class_2!Q60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T94" t="str">
+        <f>IF(MIN(Class_0!R60,Class_1!R60,Class_2!R60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U94" t="str">
+        <f>IF(MIN(Class_0!S60,Class_1!S60,Class_2!S60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V94" t="str">
+        <f>IF(MIN(Class_0!T60,Class_1!T60,Class_2!T60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W94" t="str">
+        <f>IF(MIN(Class_0!U60,Class_1!U60,Class_2!U60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="X94" t="str">
+        <f>IF(MIN(Class_0!V60,Class_1!V60,Class_2!V60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y94" t="str">
+        <f>IF(MIN(Class_0!W60,Class_1!W60,Class_2!W60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z94" t="str">
+        <f>IF(MIN(Class_0!X60,Class_1!X60,Class_2!X60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA94" t="str">
+        <f>IF(MIN(Class_0!Y60,Class_1!Y60,Class_2!Y60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB94" t="str">
+        <f>IF(MIN(Class_0!Z60,Class_1!Z60,Class_2!Z60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC94" t="str">
+        <f>IF(MIN(Class_0!AA60,Class_1!AA60,Class_2!AA60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD94" t="str">
+        <f>IF(MIN(Class_0!AB60,Class_1!AB60,Class_2!AB60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE94" t="str">
+        <f>IF(MIN(Class_0!AC60,Class_1!AC60,Class_2!AC60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF94" t="str">
+        <f>IF(MIN(Class_0!AD60,Class_1!AD60,Class_2!AD60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG94" t="str">
+        <f>IF(MIN(Class_0!AE60,Class_1!AE60,Class_2!AE60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH94" t="str">
+        <f>IF(MIN(Class_0!AF60,Class_1!AF60,Class_2!AF60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI94" t="str">
+        <f>IF(MIN(Class_0!AG60,Class_1!AG60,Class_2!AG60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ94" t="str">
+        <f>IF(MIN(Class_0!AH60,Class_1!AH60,Class_2!AH60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK94" t="str">
+        <f>IF(MIN(Class_0!AI60,Class_1!AI60,Class_2!AI60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL94" t="str">
+        <f>IF(MIN(Class_0!AJ60,Class_1!AJ60,Class_2!AJ60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM94" t="str">
+        <f>IF(MIN(Class_0!AK60,Class_1!AK60,Class_2!AK60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN94" t="str">
+        <f>IF(MIN(Class_0!AL60,Class_1!AL60,Class_2!AL60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO94" t="str">
+        <f>IF(MIN(Class_0!AM60,Class_1!AM60,Class_2!AM60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AP94" t="str">
+        <f>IF(MIN(Class_0!AN60,Class_1!AN60,Class_2!AN60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ94" t="str">
+        <f>IF(MIN(Class_0!AO60,Class_1!AO60,Class_2!AO60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR94" t="str">
+        <f>IF(MIN(Class_0!AP60,Class_1!AP60,Class_2!AP60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS94" t="str">
+        <f>IF(MIN(Class_0!AQ60,Class_1!AQ60,Class_2!AQ60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT94" t="str">
+        <f>IF(MIN(Class_0!AR60,Class_1!AR60,Class_2!AR60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AU94" t="str">
+        <f>IF(MIN(Class_0!AS60,Class_1!AS60,Class_2!AS60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV94" t="str">
+        <f>IF(MIN(Class_0!AT60,Class_1!AT60,Class_2!AT60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AW94" t="str">
+        <f>IF(MIN(Class_0!AU60,Class_1!AU60,Class_2!AU60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AX94" t="str">
+        <f>IF(MIN(Class_0!AV60,Class_1!AV60,Class_2!AV60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AY94" t="str">
+        <f>IF(MIN(Class_0!AW60,Class_1!AW60,Class_2!AW60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AZ94" t="str">
+        <f>IF(MIN(Class_0!AX60,Class_1!AX60,Class_2!AX60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BA94" t="str">
+        <f>IF(MIN(Class_0!AY60,Class_1!AY60,Class_2!AY60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BB94" t="str">
+        <f>IF(MIN(Class_0!AZ60,Class_1!AZ60,Class_2!AZ60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BC94" t="str">
+        <f>IF(MIN(Class_0!BA60,Class_1!BA60,Class_2!BA60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BD94" t="str">
+        <f>IF(MIN(Class_0!BB60,Class_1!BB60,Class_2!BB60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BE94" t="str">
+        <f>IF(MIN(Class_0!BC60,Class_1!BC60,Class_2!BC60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BF94" t="str">
+        <f>IF(MIN(Class_0!BD60,Class_1!BD60,Class_2!BD60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BG94" t="str">
+        <f>IF(MIN(Class_0!BE60,Class_1!BE60,Class_2!BE60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BH94" t="str">
+        <f>IF(MIN(Class_0!BF60,Class_1!BF60,Class_2!BF60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BI94" t="str">
+        <f>IF(MIN(Class_0!BG60,Class_1!BG60,Class_2!BG60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BJ94" t="str">
+        <f>IF(MIN(Class_0!BH60,Class_1!BH60,Class_2!BH60)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="95" spans="2:64" x14ac:dyDescent="0.35">
+      <c r="B95" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C95">
+        <f t="shared" si="7"/>
+        <v>59</v>
+      </c>
+      <c r="D95" t="str">
+        <f>IF(MIN(Class_0!B61,Class_1!B61,Class_2!B61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E95" t="str">
+        <f>IF(MIN(Class_0!C61,Class_1!C61,Class_2!C61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F95" t="str">
+        <f>IF(MIN(Class_0!D61,Class_1!D61,Class_2!D61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G95" t="str">
+        <f>IF(MIN(Class_0!E61,Class_1!E61,Class_2!E61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H95" t="str">
+        <f>IF(MIN(Class_0!F61,Class_1!F61,Class_2!F61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I95" t="str">
+        <f>IF(MIN(Class_0!G61,Class_1!G61,Class_2!G61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J95" t="str">
+        <f>IF(MIN(Class_0!H61,Class_1!H61,Class_2!H61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K95" t="str">
+        <f>IF(MIN(Class_0!I61,Class_1!I61,Class_2!I61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L95" t="str">
+        <f>IF(MIN(Class_0!J61,Class_1!J61,Class_2!J61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M95" t="str">
+        <f>IF(MIN(Class_0!K61,Class_1!K61,Class_2!K61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N95" t="str">
+        <f>IF(MIN(Class_0!L61,Class_1!L61,Class_2!L61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O95" t="str">
+        <f>IF(MIN(Class_0!M61,Class_1!M61,Class_2!M61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P95" t="str">
+        <f>IF(MIN(Class_0!N61,Class_1!N61,Class_2!N61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q95" t="str">
+        <f>IF(MIN(Class_0!O61,Class_1!O61,Class_2!O61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R95" t="str">
+        <f>IF(MIN(Class_0!P61,Class_1!P61,Class_2!P61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S95" t="str">
+        <f>IF(MIN(Class_0!Q61,Class_1!Q61,Class_2!Q61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T95" t="str">
+        <f>IF(MIN(Class_0!R61,Class_1!R61,Class_2!R61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U95" t="str">
+        <f>IF(MIN(Class_0!S61,Class_1!S61,Class_2!S61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V95" t="str">
+        <f>IF(MIN(Class_0!T61,Class_1!T61,Class_2!T61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W95" t="str">
+        <f>IF(MIN(Class_0!U61,Class_1!U61,Class_2!U61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="X95" t="str">
+        <f>IF(MIN(Class_0!V61,Class_1!V61,Class_2!V61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y95" t="str">
+        <f>IF(MIN(Class_0!W61,Class_1!W61,Class_2!W61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z95" t="str">
+        <f>IF(MIN(Class_0!X61,Class_1!X61,Class_2!X61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA95" t="str">
+        <f>IF(MIN(Class_0!Y61,Class_1!Y61,Class_2!Y61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB95" t="str">
+        <f>IF(MIN(Class_0!Z61,Class_1!Z61,Class_2!Z61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC95" t="str">
+        <f>IF(MIN(Class_0!AA61,Class_1!AA61,Class_2!AA61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD95" t="str">
+        <f>IF(MIN(Class_0!AB61,Class_1!AB61,Class_2!AB61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE95" t="str">
+        <f>IF(MIN(Class_0!AC61,Class_1!AC61,Class_2!AC61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF95" t="str">
+        <f>IF(MIN(Class_0!AD61,Class_1!AD61,Class_2!AD61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG95" t="str">
+        <f>IF(MIN(Class_0!AE61,Class_1!AE61,Class_2!AE61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH95" t="str">
+        <f>IF(MIN(Class_0!AF61,Class_1!AF61,Class_2!AF61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI95" t="str">
+        <f>IF(MIN(Class_0!AG61,Class_1!AG61,Class_2!AG61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ95" t="str">
+        <f>IF(MIN(Class_0!AH61,Class_1!AH61,Class_2!AH61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK95" t="str">
+        <f>IF(MIN(Class_0!AI61,Class_1!AI61,Class_2!AI61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL95" t="str">
+        <f>IF(MIN(Class_0!AJ61,Class_1!AJ61,Class_2!AJ61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM95" t="str">
+        <f>IF(MIN(Class_0!AK61,Class_1!AK61,Class_2!AK61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN95" t="str">
+        <f>IF(MIN(Class_0!AL61,Class_1!AL61,Class_2!AL61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO95" t="str">
+        <f>IF(MIN(Class_0!AM61,Class_1!AM61,Class_2!AM61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AP95" t="str">
+        <f>IF(MIN(Class_0!AN61,Class_1!AN61,Class_2!AN61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ95" t="str">
+        <f>IF(MIN(Class_0!AO61,Class_1!AO61,Class_2!AO61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR95" t="str">
+        <f>IF(MIN(Class_0!AP61,Class_1!AP61,Class_2!AP61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS95" t="str">
+        <f>IF(MIN(Class_0!AQ61,Class_1!AQ61,Class_2!AQ61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT95" t="str">
+        <f>IF(MIN(Class_0!AR61,Class_1!AR61,Class_2!AR61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AU95" t="str">
+        <f>IF(MIN(Class_0!AS61,Class_1!AS61,Class_2!AS61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV95" t="str">
+        <f>IF(MIN(Class_0!AT61,Class_1!AT61,Class_2!AT61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW95" t="str">
+        <f>IF(MIN(Class_0!AU61,Class_1!AU61,Class_2!AU61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AX95" t="str">
+        <f>IF(MIN(Class_0!AV61,Class_1!AV61,Class_2!AV61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AY95" t="str">
+        <f>IF(MIN(Class_0!AW61,Class_1!AW61,Class_2!AW61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AZ95" t="str">
+        <f>IF(MIN(Class_0!AX61,Class_1!AX61,Class_2!AX61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BA95" t="str">
+        <f>IF(MIN(Class_0!AY61,Class_1!AY61,Class_2!AY61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BB95" t="str">
+        <f>IF(MIN(Class_0!AZ61,Class_1!AZ61,Class_2!AZ61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BC95" t="str">
+        <f>IF(MIN(Class_0!BA61,Class_1!BA61,Class_2!BA61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BD95" t="str">
+        <f>IF(MIN(Class_0!BB61,Class_1!BB61,Class_2!BB61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BE95" t="str">
+        <f>IF(MIN(Class_0!BC61,Class_1!BC61,Class_2!BC61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BF95" t="str">
+        <f>IF(MIN(Class_0!BD61,Class_1!BD61,Class_2!BD61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BG95" t="str">
+        <f>IF(MIN(Class_0!BE61,Class_1!BE61,Class_2!BE61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BH95" t="str">
+        <f>IF(MIN(Class_0!BF61,Class_1!BF61,Class_2!BF61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BI95" t="str">
+        <f>IF(MIN(Class_0!BG61,Class_1!BG61,Class_2!BG61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BJ95" t="str">
+        <f>IF(MIN(Class_0!BH61,Class_1!BH61,Class_2!BH61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BK95" t="str">
+        <f>IF(MIN(Class_0!BI61,Class_1!BI61,Class_2!BI61)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="96" spans="2:64" x14ac:dyDescent="0.35">
+      <c r="B96" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C96">
+        <f t="shared" si="7"/>
+        <v>60</v>
+      </c>
+      <c r="D96" t="str">
+        <f>IF(MIN(Class_0!B62,Class_1!B62,Class_2!B62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E96" t="str">
+        <f>IF(MIN(Class_0!C62,Class_1!C62,Class_2!C62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F96" t="str">
+        <f>IF(MIN(Class_0!D62,Class_1!D62,Class_2!D62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G96" t="str">
+        <f>IF(MIN(Class_0!E62,Class_1!E62,Class_2!E62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H96" t="str">
+        <f>IF(MIN(Class_0!F62,Class_1!F62,Class_2!F62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I96" t="str">
+        <f>IF(MIN(Class_0!G62,Class_1!G62,Class_2!G62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J96" t="str">
+        <f>IF(MIN(Class_0!H62,Class_1!H62,Class_2!H62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K96" t="str">
+        <f>IF(MIN(Class_0!I62,Class_1!I62,Class_2!I62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L96" t="str">
+        <f>IF(MIN(Class_0!J62,Class_1!J62,Class_2!J62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M96" t="str">
+        <f>IF(MIN(Class_0!K62,Class_1!K62,Class_2!K62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N96" t="str">
+        <f>IF(MIN(Class_0!L62,Class_1!L62,Class_2!L62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O96" t="str">
+        <f>IF(MIN(Class_0!M62,Class_1!M62,Class_2!M62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P96" t="str">
+        <f>IF(MIN(Class_0!N62,Class_1!N62,Class_2!N62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q96" t="str">
+        <f>IF(MIN(Class_0!O62,Class_1!O62,Class_2!O62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R96" t="str">
+        <f>IF(MIN(Class_0!P62,Class_1!P62,Class_2!P62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S96" t="str">
+        <f>IF(MIN(Class_0!Q62,Class_1!Q62,Class_2!Q62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T96" t="str">
+        <f>IF(MIN(Class_0!R62,Class_1!R62,Class_2!R62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="U96" t="str">
+        <f>IF(MIN(Class_0!S62,Class_1!S62,Class_2!S62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="V96" t="str">
+        <f>IF(MIN(Class_0!T62,Class_1!T62,Class_2!T62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="W96" t="str">
+        <f>IF(MIN(Class_0!U62,Class_1!U62,Class_2!U62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X96" t="str">
+        <f>IF(MIN(Class_0!V62,Class_1!V62,Class_2!V62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y96" t="str">
+        <f>IF(MIN(Class_0!W62,Class_1!W62,Class_2!W62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z96" t="str">
+        <f>IF(MIN(Class_0!X62,Class_1!X62,Class_2!X62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA96" t="str">
+        <f>IF(MIN(Class_0!Y62,Class_1!Y62,Class_2!Y62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB96" t="str">
+        <f>IF(MIN(Class_0!Z62,Class_1!Z62,Class_2!Z62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC96" t="str">
+        <f>IF(MIN(Class_0!AA62,Class_1!AA62,Class_2!AA62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD96" t="str">
+        <f>IF(MIN(Class_0!AB62,Class_1!AB62,Class_2!AB62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE96" t="str">
+        <f>IF(MIN(Class_0!AC62,Class_1!AC62,Class_2!AC62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF96" t="str">
+        <f>IF(MIN(Class_0!AD62,Class_1!AD62,Class_2!AD62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG96" t="str">
+        <f>IF(MIN(Class_0!AE62,Class_1!AE62,Class_2!AE62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH96" t="str">
+        <f>IF(MIN(Class_0!AF62,Class_1!AF62,Class_2!AF62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI96" t="str">
+        <f>IF(MIN(Class_0!AG62,Class_1!AG62,Class_2!AG62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ96" t="str">
+        <f>IF(MIN(Class_0!AH62,Class_1!AH62,Class_2!AH62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK96" t="str">
+        <f>IF(MIN(Class_0!AI62,Class_1!AI62,Class_2!AI62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL96" t="str">
+        <f>IF(MIN(Class_0!AJ62,Class_1!AJ62,Class_2!AJ62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM96" t="str">
+        <f>IF(MIN(Class_0!AK62,Class_1!AK62,Class_2!AK62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN96" t="str">
+        <f>IF(MIN(Class_0!AL62,Class_1!AL62,Class_2!AL62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO96" t="str">
+        <f>IF(MIN(Class_0!AM62,Class_1!AM62,Class_2!AM62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AP96" t="str">
+        <f>IF(MIN(Class_0!AN62,Class_1!AN62,Class_2!AN62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ96" t="str">
+        <f>IF(MIN(Class_0!AO62,Class_1!AO62,Class_2!AO62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR96" t="str">
+        <f>IF(MIN(Class_0!AP62,Class_1!AP62,Class_2!AP62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS96" t="str">
+        <f>IF(MIN(Class_0!AQ62,Class_1!AQ62,Class_2!AQ62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT96" t="str">
+        <f>IF(MIN(Class_0!AR62,Class_1!AR62,Class_2!AR62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AU96" t="str">
+        <f>IF(MIN(Class_0!AS62,Class_1!AS62,Class_2!AS62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV96" t="str">
+        <f>IF(MIN(Class_0!AT62,Class_1!AT62,Class_2!AT62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW96" t="str">
+        <f>IF(MIN(Class_0!AU62,Class_1!AU62,Class_2!AU62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AX96" t="str">
+        <f>IF(MIN(Class_0!AV62,Class_1!AV62,Class_2!AV62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AY96" t="str">
+        <f>IF(MIN(Class_0!AW62,Class_1!AW62,Class_2!AW62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AZ96" t="str">
+        <f>IF(MIN(Class_0!AX62,Class_1!AX62,Class_2!AX62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BA96" t="str">
+        <f>IF(MIN(Class_0!AY62,Class_1!AY62,Class_2!AY62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BB96" t="str">
+        <f>IF(MIN(Class_0!AZ62,Class_1!AZ62,Class_2!AZ62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BC96" t="str">
+        <f>IF(MIN(Class_0!BA62,Class_1!BA62,Class_2!BA62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BD96" t="str">
+        <f>IF(MIN(Class_0!BB62,Class_1!BB62,Class_2!BB62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BE96" t="str">
+        <f>IF(MIN(Class_0!BC62,Class_1!BC62,Class_2!BC62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BF96" t="str">
+        <f>IF(MIN(Class_0!BD62,Class_1!BD62,Class_2!BD62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BG96" t="str">
+        <f>IF(MIN(Class_0!BE62,Class_1!BE62,Class_2!BE62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BH96" t="str">
+        <f>IF(MIN(Class_0!BF62,Class_1!BF62,Class_2!BF62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BI96" t="str">
+        <f>IF(MIN(Class_0!BG62,Class_1!BG62,Class_2!BG62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BJ96" t="str">
+        <f>IF(MIN(Class_0!BH62,Class_1!BH62,Class_2!BH62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BK96" t="str">
+        <f>IF(MIN(Class_0!BI62,Class_1!BI62,Class_2!BI62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BL96" t="str">
+        <f>IF(MIN(Class_0!BJ62,Class_1!BJ62,Class_2!BJ62)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="97" spans="2:65" x14ac:dyDescent="0.35">
+      <c r="B97" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C97">
+        <f t="shared" si="7"/>
+        <v>61</v>
+      </c>
+      <c r="D97" t="str">
+        <f>IF(MIN(Class_0!B63,Class_1!B63,Class_2!B63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="E97" t="str">
+        <f>IF(MIN(Class_0!C63,Class_1!C63,Class_2!C63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F97" t="str">
+        <f>IF(MIN(Class_0!D63,Class_1!D63,Class_2!D63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G97" t="str">
+        <f>IF(MIN(Class_0!E63,Class_1!E63,Class_2!E63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H97" t="str">
+        <f>IF(MIN(Class_0!F63,Class_1!F63,Class_2!F63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I97" t="str">
+        <f>IF(MIN(Class_0!G63,Class_1!G63,Class_2!G63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J97" t="str">
+        <f>IF(MIN(Class_0!H63,Class_1!H63,Class_2!H63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K97" t="str">
+        <f>IF(MIN(Class_0!I63,Class_1!I63,Class_2!I63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L97" t="str">
+        <f>IF(MIN(Class_0!J63,Class_1!J63,Class_2!J63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M97" t="str">
+        <f>IF(MIN(Class_0!K63,Class_1!K63,Class_2!K63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N97" t="str">
+        <f>IF(MIN(Class_0!L63,Class_1!L63,Class_2!L63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O97" t="str">
+        <f>IF(MIN(Class_0!M63,Class_1!M63,Class_2!M63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P97" t="str">
+        <f>IF(MIN(Class_0!N63,Class_1!N63,Class_2!N63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q97" t="str">
+        <f>IF(MIN(Class_0!O63,Class_1!O63,Class_2!O63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R97" t="str">
+        <f>IF(MIN(Class_0!P63,Class_1!P63,Class_2!P63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S97" t="str">
+        <f>IF(MIN(Class_0!Q63,Class_1!Q63,Class_2!Q63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T97" t="str">
+        <f>IF(MIN(Class_0!R63,Class_1!R63,Class_2!R63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="U97" t="str">
+        <f>IF(MIN(Class_0!S63,Class_1!S63,Class_2!S63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="V97" t="str">
+        <f>IF(MIN(Class_0!T63,Class_1!T63,Class_2!T63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W97" t="str">
+        <f>IF(MIN(Class_0!U63,Class_1!U63,Class_2!U63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X97" t="str">
+        <f>IF(MIN(Class_0!V63,Class_1!V63,Class_2!V63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y97" t="str">
+        <f>IF(MIN(Class_0!W63,Class_1!W63,Class_2!W63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Z97" t="str">
+        <f>IF(MIN(Class_0!X63,Class_1!X63,Class_2!X63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA97" t="str">
+        <f>IF(MIN(Class_0!Y63,Class_1!Y63,Class_2!Y63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB97" t="str">
+        <f>IF(MIN(Class_0!Z63,Class_1!Z63,Class_2!Z63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC97" t="str">
+        <f>IF(MIN(Class_0!AA63,Class_1!AA63,Class_2!AA63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD97" t="str">
+        <f>IF(MIN(Class_0!AB63,Class_1!AB63,Class_2!AB63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE97" t="str">
+        <f>IF(MIN(Class_0!AC63,Class_1!AC63,Class_2!AC63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF97" t="str">
+        <f>IF(MIN(Class_0!AD63,Class_1!AD63,Class_2!AD63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG97" t="str">
+        <f>IF(MIN(Class_0!AE63,Class_1!AE63,Class_2!AE63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH97" t="str">
+        <f>IF(MIN(Class_0!AF63,Class_1!AF63,Class_2!AF63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI97" t="str">
+        <f>IF(MIN(Class_0!AG63,Class_1!AG63,Class_2!AG63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ97" t="str">
+        <f>IF(MIN(Class_0!AH63,Class_1!AH63,Class_2!AH63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AK97" t="str">
+        <f>IF(MIN(Class_0!AI63,Class_1!AI63,Class_2!AI63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL97" t="str">
+        <f>IF(MIN(Class_0!AJ63,Class_1!AJ63,Class_2!AJ63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM97" t="str">
+        <f>IF(MIN(Class_0!AK63,Class_1!AK63,Class_2!AK63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN97" t="str">
+        <f>IF(MIN(Class_0!AL63,Class_1!AL63,Class_2!AL63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO97" t="str">
+        <f>IF(MIN(Class_0!AM63,Class_1!AM63,Class_2!AM63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AP97" t="str">
+        <f>IF(MIN(Class_0!AN63,Class_1!AN63,Class_2!AN63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ97" t="str">
+        <f>IF(MIN(Class_0!AO63,Class_1!AO63,Class_2!AO63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR97" t="str">
+        <f>IF(MIN(Class_0!AP63,Class_1!AP63,Class_2!AP63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AS97" t="str">
+        <f>IF(MIN(Class_0!AQ63,Class_1!AQ63,Class_2!AQ63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AT97" t="str">
+        <f>IF(MIN(Class_0!AR63,Class_1!AR63,Class_2!AR63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AU97" t="str">
+        <f>IF(MIN(Class_0!AS63,Class_1!AS63,Class_2!AS63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV97" t="str">
+        <f>IF(MIN(Class_0!AT63,Class_1!AT63,Class_2!AT63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW97" t="str">
+        <f>IF(MIN(Class_0!AU63,Class_1!AU63,Class_2!AU63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AX97" t="str">
+        <f>IF(MIN(Class_0!AV63,Class_1!AV63,Class_2!AV63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AY97" t="str">
+        <f>IF(MIN(Class_0!AW63,Class_1!AW63,Class_2!AW63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AZ97" t="str">
+        <f>IF(MIN(Class_0!AX63,Class_1!AX63,Class_2!AX63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BA97" t="str">
+        <f>IF(MIN(Class_0!AY63,Class_1!AY63,Class_2!AY63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BB97" t="str">
+        <f>IF(MIN(Class_0!AZ63,Class_1!AZ63,Class_2!AZ63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BC97" t="str">
+        <f>IF(MIN(Class_0!BA63,Class_1!BA63,Class_2!BA63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BD97" t="str">
+        <f>IF(MIN(Class_0!BB63,Class_1!BB63,Class_2!BB63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BE97" t="str">
+        <f>IF(MIN(Class_0!BC63,Class_1!BC63,Class_2!BC63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BF97" t="str">
+        <f>IF(MIN(Class_0!BD63,Class_1!BD63,Class_2!BD63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BG97" t="str">
+        <f>IF(MIN(Class_0!BE63,Class_1!BE63,Class_2!BE63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BH97" t="str">
+        <f>IF(MIN(Class_0!BF63,Class_1!BF63,Class_2!BF63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BI97" t="str">
+        <f>IF(MIN(Class_0!BG63,Class_1!BG63,Class_2!BG63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BJ97" t="str">
+        <f>IF(MIN(Class_0!BH63,Class_1!BH63,Class_2!BH63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BK97" t="str">
+        <f>IF(MIN(Class_0!BI63,Class_1!BI63,Class_2!BI63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BL97" t="str">
+        <f>IF(MIN(Class_0!BJ63,Class_1!BJ63,Class_2!BJ63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BM97" t="str">
+        <f>IF(MIN(Class_0!BK63,Class_1!BK63,Class_2!BK63)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B6:BJ6">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B9:BJ9">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+  <conditionalFormatting sqref="B7:BJ7">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B7:BJ7">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+  <conditionalFormatting sqref="B9:BJ9">
+    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
       <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D36">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>ROW()-COLUMN()-32=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D37:BM97">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>ROW()-COLUMN()-32=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
